--- a/src/main/resources/datasets/Import_Chartres_Projet.xlsx
+++ b/src/main/resources/datasets/Import_Chartres_Projet.xlsx
@@ -3062,19 +3062,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultColWidth="12.6667" defaultRowHeight="15.75" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="18" style="1" customWidth="1"/>
-    <col min="2" max="2" width="37.8516" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.6719" style="1" customWidth="1"/>
-    <col min="4" max="4" width="115.352" style="1" customWidth="1"/>
-    <col min="5" max="6" width="12.6719" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="12.6719" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6719" style="1" customWidth="1"/>
+    <col min="3" max="3" width="115.352" style="1" customWidth="1"/>
+    <col min="4" max="5" width="12.6719" style="1" customWidth="1"/>
+    <col min="6" max="16383" width="12.6719" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="13.65" customHeight="1">
@@ -3082,16 +3081,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C1" t="s" s="2">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s" s="2">
         <v>3</v>
       </c>
-      <c r="E1" s="3"/>
-      <c r="F1" t="s" s="4">
+      <c r="D1" s="3"/>
+      <c r="E1" t="s" s="4">
         <v>4</v>
       </c>
     </row>
@@ -3099,13 +3095,12 @@
       <c r="A2" t="s" s="2">
         <v>5</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" t="s" s="6">
-        <v>6</v>
-      </c>
-      <c r="D2" s="7"/>
-      <c r="E2" s="8"/>
-      <c r="F2" t="s" s="9">
+      <c r="B2" t="s" s="6">
+        <v>6</v>
+      </c>
+      <c r="C2" s="7"/>
+      <c r="D2" s="8"/>
+      <c r="E2" t="s" s="9">
         <v>7</v>
       </c>
     </row>
@@ -3113,13 +3108,12 @@
       <c r="A3" t="s" s="2">
         <v>8</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="C3" t="s" s="6">
-        <v>6</v>
-      </c>
-      <c r="D3" s="7"/>
-      <c r="E3" s="8"/>
-      <c r="F3" t="s" s="9">
+      <c r="B3" t="s" s="6">
+        <v>6</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="8"/>
+      <c r="E3" t="s" s="9">
         <v>7</v>
       </c>
     </row>
@@ -3127,13 +3121,12 @@
       <c r="A4" t="s" s="2">
         <v>9</v>
       </c>
-      <c r="B4" s="5"/>
-      <c r="C4" t="s" s="6">
-        <v>6</v>
-      </c>
-      <c r="D4" s="7"/>
-      <c r="E4" s="8"/>
-      <c r="F4" t="s" s="9">
+      <c r="B4" t="s" s="6">
+        <v>6</v>
+      </c>
+      <c r="C4" s="7"/>
+      <c r="D4" s="8"/>
+      <c r="E4" t="s" s="9">
         <v>7</v>
       </c>
     </row>
@@ -3141,13 +3134,12 @@
       <c r="A5" t="s" s="2">
         <v>10</v>
       </c>
-      <c r="B5" s="5"/>
-      <c r="C5" t="s" s="6">
-        <v>6</v>
-      </c>
-      <c r="D5" s="7"/>
-      <c r="E5" s="8"/>
-      <c r="F5" t="s" s="9">
+      <c r="B5" t="s" s="6">
+        <v>6</v>
+      </c>
+      <c r="C5" s="7"/>
+      <c r="D5" s="8"/>
+      <c r="E5" t="s" s="9">
         <v>7</v>
       </c>
     </row>
@@ -3155,13 +3147,12 @@
       <c r="A6" t="s" s="2">
         <v>11</v>
       </c>
-      <c r="B6" s="5"/>
-      <c r="C6" t="s" s="6">
-        <v>6</v>
-      </c>
-      <c r="D6" s="7"/>
-      <c r="E6" s="8"/>
-      <c r="F6" t="s" s="9">
+      <c r="B6" t="s" s="6">
+        <v>6</v>
+      </c>
+      <c r="C6" s="7"/>
+      <c r="D6" s="8"/>
+      <c r="E6" t="s" s="9">
         <v>7</v>
       </c>
     </row>
@@ -3169,13 +3160,12 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" s="5"/>
-      <c r="C7" t="s" s="6">
-        <v>6</v>
-      </c>
-      <c r="D7" s="7"/>
-      <c r="E7" s="8"/>
-      <c r="F7" t="s" s="9">
+      <c r="B7" t="s" s="6">
+        <v>6</v>
+      </c>
+      <c r="C7" s="7"/>
+      <c r="D7" s="8"/>
+      <c r="E7" t="s" s="9">
         <v>7</v>
       </c>
     </row>
@@ -3183,13 +3173,12 @@
       <c r="A8" t="s" s="2">
         <v>13</v>
       </c>
-      <c r="B8" s="5"/>
-      <c r="C8" t="s" s="6">
-        <v>6</v>
-      </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="8"/>
-      <c r="F8" t="s" s="9">
+      <c r="B8" t="s" s="6">
+        <v>6</v>
+      </c>
+      <c r="C8" s="7"/>
+      <c r="D8" s="8"/>
+      <c r="E8" t="s" s="9">
         <v>7</v>
       </c>
     </row>
@@ -3197,13 +3186,12 @@
       <c r="A9" t="s" s="2">
         <v>14</v>
       </c>
-      <c r="B9" s="5"/>
-      <c r="C9" t="s" s="6">
-        <v>6</v>
-      </c>
-      <c r="D9" s="7"/>
-      <c r="E9" s="8"/>
-      <c r="F9" t="s" s="9">
+      <c r="B9" t="s" s="6">
+        <v>6</v>
+      </c>
+      <c r="C9" s="7"/>
+      <c r="D9" s="8"/>
+      <c r="E9" t="s" s="9">
         <v>7</v>
       </c>
     </row>
@@ -3211,13 +3199,12 @@
       <c r="A10" t="s" s="2">
         <v>15</v>
       </c>
-      <c r="B10" s="5"/>
-      <c r="C10" t="s" s="6">
-        <v>6</v>
-      </c>
-      <c r="D10" s="7"/>
-      <c r="E10" s="8"/>
-      <c r="F10" t="s" s="9">
+      <c r="B10" t="s" s="6">
+        <v>6</v>
+      </c>
+      <c r="C10" s="7"/>
+      <c r="D10" s="8"/>
+      <c r="E10" t="s" s="9">
         <v>7</v>
       </c>
     </row>
@@ -3225,13 +3212,12 @@
       <c r="A11" t="s" s="2">
         <v>16</v>
       </c>
-      <c r="B11" s="5"/>
-      <c r="C11" t="s" s="6">
-        <v>6</v>
-      </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="8"/>
-      <c r="F11" t="s" s="9">
+      <c r="B11" t="s" s="6">
+        <v>6</v>
+      </c>
+      <c r="C11" s="7"/>
+      <c r="D11" s="8"/>
+      <c r="E11" t="s" s="9">
         <v>7</v>
       </c>
     </row>
@@ -3239,13 +3225,12 @@
       <c r="A12" t="s" s="2">
         <v>17</v>
       </c>
-      <c r="B12" s="5"/>
-      <c r="C12" t="s" s="6">
-        <v>6</v>
-      </c>
-      <c r="D12" s="7"/>
-      <c r="E12" s="8"/>
-      <c r="F12" t="s" s="9">
+      <c r="B12" t="s" s="6">
+        <v>6</v>
+      </c>
+      <c r="C12" s="7"/>
+      <c r="D12" s="8"/>
+      <c r="E12" t="s" s="9">
         <v>7</v>
       </c>
     </row>
@@ -3253,13 +3238,12 @@
       <c r="A13" t="s" s="2">
         <v>18</v>
       </c>
-      <c r="B13" s="5"/>
-      <c r="C13" t="s" s="6">
-        <v>6</v>
-      </c>
-      <c r="D13" s="7"/>
-      <c r="E13" s="8"/>
-      <c r="F13" t="s" s="9">
+      <c r="B13" t="s" s="6">
+        <v>6</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="8"/>
+      <c r="E13" t="s" s="9">
         <v>7</v>
       </c>
     </row>
@@ -3267,13 +3251,12 @@
       <c r="A14" t="s" s="2">
         <v>19</v>
       </c>
-      <c r="B14" s="5"/>
-      <c r="C14" t="s" s="6">
-        <v>6</v>
-      </c>
-      <c r="D14" s="7"/>
-      <c r="E14" s="8"/>
-      <c r="F14" t="s" s="9">
+      <c r="B14" t="s" s="6">
+        <v>6</v>
+      </c>
+      <c r="C14" s="7"/>
+      <c r="D14" s="8"/>
+      <c r="E14" t="s" s="9">
         <v>7</v>
       </c>
     </row>
@@ -3281,13 +3264,12 @@
       <c r="A15" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="B15" s="5"/>
-      <c r="C15" t="s" s="6">
-        <v>6</v>
-      </c>
-      <c r="D15" s="7"/>
-      <c r="E15" s="8"/>
-      <c r="F15" t="s" s="9">
+      <c r="B15" t="s" s="6">
+        <v>6</v>
+      </c>
+      <c r="C15" s="7"/>
+      <c r="D15" s="8"/>
+      <c r="E15" t="s" s="9">
         <v>7</v>
       </c>
     </row>
@@ -3295,13 +3277,12 @@
       <c r="A16" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="B16" s="5"/>
-      <c r="C16" t="s" s="6">
-        <v>6</v>
-      </c>
-      <c r="D16" s="7"/>
-      <c r="E16" s="8"/>
-      <c r="F16" t="s" s="9">
+      <c r="B16" t="s" s="6">
+        <v>6</v>
+      </c>
+      <c r="C16" s="7"/>
+      <c r="D16" s="8"/>
+      <c r="E16" t="s" s="9">
         <v>7</v>
       </c>
     </row>
@@ -3309,13 +3290,12 @@
       <c r="A17" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="B17" s="5"/>
-      <c r="C17" t="s" s="6">
-        <v>6</v>
-      </c>
-      <c r="D17" s="7"/>
-      <c r="E17" s="8"/>
-      <c r="F17" t="s" s="9">
+      <c r="B17" t="s" s="6">
+        <v>6</v>
+      </c>
+      <c r="C17" s="7"/>
+      <c r="D17" s="8"/>
+      <c r="E17" t="s" s="9">
         <v>7</v>
       </c>
     </row>
@@ -3323,13 +3303,12 @@
       <c r="A18" t="s" s="2">
         <v>23</v>
       </c>
-      <c r="B18" s="5"/>
-      <c r="C18" t="s" s="6">
-        <v>6</v>
-      </c>
-      <c r="D18" s="7"/>
-      <c r="E18" s="8"/>
-      <c r="F18" t="s" s="9">
+      <c r="B18" t="s" s="6">
+        <v>6</v>
+      </c>
+      <c r="C18" s="7"/>
+      <c r="D18" s="8"/>
+      <c r="E18" t="s" s="9">
         <v>7</v>
       </c>
     </row>
@@ -3337,13 +3316,12 @@
       <c r="A19" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="B19" s="5"/>
-      <c r="C19" t="s" s="6">
-        <v>6</v>
-      </c>
-      <c r="D19" s="7"/>
-      <c r="E19" s="8"/>
-      <c r="F19" t="s" s="9">
+      <c r="B19" t="s" s="6">
+        <v>6</v>
+      </c>
+      <c r="C19" s="7"/>
+      <c r="D19" s="8"/>
+      <c r="E19" t="s" s="9">
         <v>7</v>
       </c>
     </row>
@@ -3351,15 +3329,14 @@
       <c r="A20" t="s" s="2">
         <v>25</v>
       </c>
-      <c r="B20" s="5"/>
-      <c r="C20" t="s" s="6">
-        <v>6</v>
-      </c>
-      <c r="D20" t="s" s="2">
+      <c r="B20" t="s" s="6">
+        <v>6</v>
+      </c>
+      <c r="C20" t="s" s="2">
         <v>26</v>
       </c>
-      <c r="E20" s="10"/>
-      <c r="F20" t="s" s="11">
+      <c r="D20" s="10"/>
+      <c r="E20" t="s" s="11">
         <v>27</v>
       </c>
     </row>
@@ -3588,26 +3565,22 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC80"/>
+  <dimension ref="A1:U80"/>
   <sheetFormatPr defaultColWidth="12.6667" defaultRowHeight="15.75" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="12.6719" style="32" customWidth="1"/>
     <col min="2" max="2" width="35.3516" style="32" customWidth="1"/>
-    <col min="3" max="3" width="53.1719" style="32" customWidth="1"/>
-    <col min="4" max="4" width="44.8516" style="32" customWidth="1"/>
+    <col min="3" max="3" width="44.8516" style="32" customWidth="1"/>
+    <col min="4" max="4" width="40.3516" style="32" customWidth="1"/>
     <col min="5" max="5" width="12.6719" style="32" customWidth="1"/>
-    <col min="6" max="6" width="40.3516" style="32" customWidth="1"/>
-    <col min="7" max="7" width="23.5" style="32" customWidth="1"/>
-    <col min="8" max="8" width="12.6719" style="32" customWidth="1"/>
-    <col min="9" max="9" width="45.6719" style="32" customWidth="1"/>
-    <col min="10" max="10" width="14.8516" style="32" customWidth="1"/>
-    <col min="11" max="11" width="15.5" style="32" customWidth="1"/>
-    <col min="12" max="29" width="12.6719" style="32" customWidth="1"/>
-    <col min="30" max="16384" width="12.6719" style="32" customWidth="1"/>
+    <col min="6" max="6" width="14.8516" style="32" customWidth="1"/>
+    <col min="7" max="7" width="15.5" style="32" customWidth="1"/>
+    <col min="8" max="21" width="12.6719" style="32" customWidth="1"/>
+    <col min="22" max="16376" width="12.6719" style="32" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="13.65" customHeight="1">
@@ -3617,85 +3590,63 @@
       <c r="B1" t="s" s="2">
         <v>36</v>
       </c>
-      <c r="C1" t="s" s="2">
-        <v>41</v>
-      </c>
-      <c r="D1" t="s" s="4">
+      <c r="C1" t="s" s="4">
         <v>4</v>
       </c>
-      <c r="E1" t="s" s="2">
-        <v>42</v>
+      <c r="D1" t="inlineStr" s="4">
+        <is>
+          <t>Nature Label</t>
+        </is>
+      </c>
+      <c r="E1" t="s" s="4">
+        <v>45</v>
       </c>
       <c r="F1" t="s" s="4">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G1" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="H1" t="s" s="4">
-        <v>45</v>
-      </c>
-      <c r="I1" t="s" s="33">
-        <v>46</v>
-      </c>
-      <c r="J1" t="s" s="4">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="H1" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="I1" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="J1" t="s" s="2">
+        <v>51</v>
       </c>
       <c r="K1" t="s" s="2">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L1" t="s" s="2">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="M1" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="N1" t="s" s="2">
-        <v>51</v>
+        <v>54</v>
+      </c>
+      <c r="N1" t="s" s="4">
+        <v>55</v>
       </c>
       <c r="O1" t="s" s="2">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="P1" t="s" s="2">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="Q1" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="R1" t="s" s="4">
-        <v>55</v>
+        <v>58</v>
+      </c>
+      <c r="R1" t="s" s="2">
+        <v>60</v>
       </c>
       <c r="S1" t="s" s="2">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="T1" t="s" s="2">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="U1" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="V1" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="W1" t="s" s="2">
-        <v>60</v>
-      </c>
-      <c r="X1" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="Y1" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="Z1" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AA1" t="s" s="2">
-        <v>64</v>
-      </c>
-      <c r="AB1" t="s" s="2">
-        <v>65</v>
-      </c>
-      <c r="AC1" t="s" s="2">
         <v>66</v>
       </c>
     </row>
@@ -3706,51 +3657,47 @@
       <c r="B2" t="s" s="2">
         <v>68</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" t="s" s="34">
-        <v>69</v>
-      </c>
-      <c r="E2" s="35"/>
-      <c r="F2" t="s" s="36">
-        <v>70</v>
-      </c>
-      <c r="G2" s="35"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="38"/>
-      <c r="J2" t="s" s="39">
+      <c r="C2" t="inlineStr" s="34">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr" s="36">
+        <is>
+          <t>Dépôt naturel</t>
+        </is>
+      </c>
+      <c r="E2" s="37"/>
+      <c r="F2" t="s" s="39">
         <v>71</v>
       </c>
-      <c r="K2" t="s" s="6">
-        <v>72</v>
-      </c>
-      <c r="L2" t="s" s="2">
-        <v>6</v>
-      </c>
+      <c r="G2" t="s" s="6">
+        <v>72</v>
+      </c>
+      <c r="H2" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I2" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J2" s="40">
+        <v>41081</v>
+      </c>
+      <c r="K2" s="41"/>
+      <c r="L2" s="42"/>
       <c r="M2" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="N2" s="40">
-        <v>41081</v>
+        <v>74</v>
+      </c>
+      <c r="N2" s="43">
+        <v>9</v>
       </c>
       <c r="O2" s="41"/>
-      <c r="P2" s="42"/>
-      <c r="Q2" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R2" s="43">
-        <v>9</v>
-      </c>
-      <c r="S2" s="41"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
       <c r="T2" s="35"/>
-      <c r="U2" s="35"/>
-      <c r="V2" s="35"/>
-      <c r="W2" s="35"/>
-      <c r="X2" s="35"/>
-      <c r="Y2" s="35"/>
-      <c r="Z2" s="35"/>
-      <c r="AA2" s="35"/>
-      <c r="AB2" s="35"/>
-      <c r="AC2" s="42"/>
+      <c r="U2" s="42"/>
     </row>
     <row r="3" ht="13.75" customHeight="1">
       <c r="A3" t="s" s="2">
@@ -3759,51 +3706,47 @@
       <c r="B3" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" t="s" s="34">
-        <v>69</v>
+      <c r="C3" t="inlineStr" s="34">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr" s="36">
+        <is>
+          <t>Dépôt naturel</t>
+        </is>
       </c>
       <c r="E3" s="37"/>
-      <c r="F3" t="s" s="36">
-        <v>70</v>
-      </c>
-      <c r="G3" s="37"/>
-      <c r="H3" s="37"/>
-      <c r="I3" s="37"/>
-      <c r="J3" t="s" s="39">
+      <c r="F3" t="s" s="39">
         <v>71</v>
       </c>
-      <c r="K3" t="s" s="6">
-        <v>72</v>
-      </c>
-      <c r="L3" t="s" s="2">
-        <v>6</v>
-      </c>
+      <c r="G3" t="s" s="6">
+        <v>72</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J3" s="40">
+        <v>41082</v>
+      </c>
+      <c r="K3" s="44"/>
+      <c r="L3" s="45"/>
       <c r="M3" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="N3" s="40">
-        <v>41082</v>
+        <v>74</v>
+      </c>
+      <c r="N3" s="43">
+        <v>8</v>
       </c>
       <c r="O3" s="44"/>
-      <c r="P3" s="45"/>
-      <c r="Q3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R3" s="43">
-        <v>8</v>
-      </c>
-      <c r="S3" s="44"/>
+      <c r="P3" s="37"/>
+      <c r="Q3" s="37"/>
+      <c r="R3" s="37"/>
+      <c r="S3" s="37"/>
       <c r="T3" s="37"/>
-      <c r="U3" s="37"/>
-      <c r="V3" s="37"/>
-      <c r="W3" s="37"/>
-      <c r="X3" s="37"/>
-      <c r="Y3" s="37"/>
-      <c r="Z3" s="37"/>
-      <c r="AA3" s="37"/>
-      <c r="AB3" s="37"/>
-      <c r="AC3" s="45"/>
+      <c r="U3" s="45"/>
     </row>
     <row r="4" ht="13.75" customHeight="1">
       <c r="A4" t="s" s="2">
@@ -3812,51 +3755,47 @@
       <c r="B4" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="C4" s="8"/>
-      <c r="D4" t="s" s="34">
-        <v>69</v>
+      <c r="C4" t="inlineStr" s="34">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr" s="36">
+        <is>
+          <t>Dépôt naturel</t>
+        </is>
       </c>
       <c r="E4" s="37"/>
-      <c r="F4" t="s" s="36">
-        <v>70</v>
-      </c>
-      <c r="G4" s="37"/>
-      <c r="H4" s="37"/>
-      <c r="I4" s="37"/>
-      <c r="J4" t="s" s="39">
+      <c r="F4" t="s" s="39">
         <v>71</v>
       </c>
-      <c r="K4" t="s" s="6">
-        <v>72</v>
-      </c>
-      <c r="L4" t="s" s="2">
-        <v>6</v>
-      </c>
+      <c r="G4" t="s" s="6">
+        <v>72</v>
+      </c>
+      <c r="H4" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I4" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J4" s="40">
+        <v>41082</v>
+      </c>
+      <c r="K4" s="44"/>
+      <c r="L4" s="45"/>
       <c r="M4" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="N4" s="40">
-        <v>41082</v>
+        <v>74</v>
+      </c>
+      <c r="N4" s="43">
+        <v>9</v>
       </c>
       <c r="O4" s="44"/>
-      <c r="P4" s="45"/>
-      <c r="Q4" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R4" s="43">
-        <v>9</v>
-      </c>
-      <c r="S4" s="44"/>
+      <c r="P4" s="37"/>
+      <c r="Q4" s="37"/>
+      <c r="R4" s="37"/>
+      <c r="S4" s="37"/>
       <c r="T4" s="37"/>
-      <c r="U4" s="37"/>
-      <c r="V4" s="37"/>
-      <c r="W4" s="37"/>
-      <c r="X4" s="37"/>
-      <c r="Y4" s="37"/>
-      <c r="Z4" s="37"/>
-      <c r="AA4" s="37"/>
-      <c r="AB4" s="37"/>
-      <c r="AC4" s="45"/>
+      <c r="U4" s="45"/>
     </row>
     <row r="5" ht="13.75" customHeight="1">
       <c r="A5" t="s" s="2">
@@ -3865,51 +3804,47 @@
       <c r="B5" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="C5" s="8"/>
-      <c r="D5" t="s" s="34">
-        <v>69</v>
+      <c r="C5" t="inlineStr" s="34">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr" s="36">
+        <is>
+          <t>Dépôt naturel</t>
+        </is>
       </c>
       <c r="E5" s="37"/>
-      <c r="F5" t="s" s="36">
-        <v>70</v>
-      </c>
-      <c r="G5" s="37"/>
-      <c r="H5" s="37"/>
-      <c r="I5" s="37"/>
-      <c r="J5" t="s" s="39">
+      <c r="F5" t="s" s="39">
         <v>81</v>
       </c>
-      <c r="K5" t="s" s="6">
-        <v>72</v>
-      </c>
-      <c r="L5" t="s" s="2">
-        <v>6</v>
-      </c>
+      <c r="G5" t="s" s="6">
+        <v>72</v>
+      </c>
+      <c r="H5" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I5" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J5" s="40">
+        <v>41082</v>
+      </c>
+      <c r="K5" s="44"/>
+      <c r="L5" s="45"/>
       <c r="M5" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="N5" s="40">
-        <v>41082</v>
+        <v>74</v>
+      </c>
+      <c r="N5" s="43">
+        <v>9</v>
       </c>
       <c r="O5" s="44"/>
-      <c r="P5" s="45"/>
-      <c r="Q5" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R5" s="43">
-        <v>9</v>
-      </c>
-      <c r="S5" s="44"/>
+      <c r="P5" s="37"/>
+      <c r="Q5" s="37"/>
+      <c r="R5" s="37"/>
+      <c r="S5" s="37"/>
       <c r="T5" s="37"/>
-      <c r="U5" s="37"/>
-      <c r="V5" s="37"/>
-      <c r="W5" s="37"/>
-      <c r="X5" s="37"/>
-      <c r="Y5" s="37"/>
-      <c r="Z5" s="37"/>
-      <c r="AA5" s="37"/>
-      <c r="AB5" s="37"/>
-      <c r="AC5" s="45"/>
+      <c r="U5" s="45"/>
     </row>
     <row r="6" ht="13.75" customHeight="1">
       <c r="A6" t="s" s="2">
@@ -3918,51 +3853,47 @@
       <c r="B6" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="C6" s="8"/>
-      <c r="D6" t="s" s="34">
-        <v>69</v>
+      <c r="C6" t="inlineStr" s="34">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr" s="36">
+        <is>
+          <t>Dépôt naturel</t>
+        </is>
       </c>
       <c r="E6" s="37"/>
-      <c r="F6" t="s" s="36">
-        <v>70</v>
-      </c>
-      <c r="G6" s="37"/>
-      <c r="H6" s="37"/>
-      <c r="I6" s="37"/>
-      <c r="J6" t="s" s="39">
+      <c r="F6" t="s" s="39">
         <v>84</v>
       </c>
-      <c r="K6" t="s" s="6">
-        <v>72</v>
-      </c>
-      <c r="L6" t="s" s="2">
-        <v>6</v>
-      </c>
+      <c r="G6" t="s" s="6">
+        <v>72</v>
+      </c>
+      <c r="H6" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I6" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J6" s="40">
+        <v>41091</v>
+      </c>
+      <c r="K6" s="44"/>
+      <c r="L6" s="45"/>
       <c r="M6" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="N6" s="40">
-        <v>41091</v>
+        <v>74</v>
+      </c>
+      <c r="N6" s="43">
+        <v>9</v>
       </c>
       <c r="O6" s="44"/>
-      <c r="P6" s="45"/>
-      <c r="Q6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R6" s="43">
-        <v>9</v>
-      </c>
-      <c r="S6" s="44"/>
+      <c r="P6" s="37"/>
+      <c r="Q6" s="37"/>
+      <c r="R6" s="37"/>
+      <c r="S6" s="37"/>
       <c r="T6" s="37"/>
-      <c r="U6" s="37"/>
-      <c r="V6" s="37"/>
-      <c r="W6" s="37"/>
-      <c r="X6" s="37"/>
-      <c r="Y6" s="37"/>
-      <c r="Z6" s="37"/>
-      <c r="AA6" s="37"/>
-      <c r="AB6" s="37"/>
-      <c r="AC6" s="45"/>
+      <c r="U6" s="45"/>
     </row>
     <row r="7" ht="13.75" customHeight="1">
       <c r="A7" t="s" s="2">
@@ -3971,51 +3902,47 @@
       <c r="B7" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="C7" s="8"/>
-      <c r="D7" t="s" s="34">
-        <v>69</v>
+      <c r="C7" t="inlineStr" s="34">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr" s="36">
+        <is>
+          <t>Dépôt naturel</t>
+        </is>
       </c>
       <c r="E7" s="37"/>
-      <c r="F7" t="s" s="36">
-        <v>70</v>
-      </c>
-      <c r="G7" s="37"/>
-      <c r="H7" s="37"/>
-      <c r="I7" s="37"/>
-      <c r="J7" t="s" s="39">
+      <c r="F7" t="s" s="39">
         <v>88</v>
       </c>
-      <c r="K7" t="s" s="6">
-        <v>72</v>
-      </c>
-      <c r="L7" t="s" s="2">
-        <v>6</v>
-      </c>
+      <c r="G7" t="s" s="6">
+        <v>72</v>
+      </c>
+      <c r="H7" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I7" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J7" s="40">
+        <v>41091</v>
+      </c>
+      <c r="K7" s="44"/>
+      <c r="L7" s="45"/>
       <c r="M7" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="N7" s="40">
-        <v>41091</v>
+        <v>74</v>
+      </c>
+      <c r="N7" s="43">
+        <v>9</v>
       </c>
       <c r="O7" s="44"/>
-      <c r="P7" s="45"/>
-      <c r="Q7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R7" s="43">
-        <v>9</v>
-      </c>
-      <c r="S7" s="44"/>
+      <c r="P7" s="37"/>
+      <c r="Q7" s="37"/>
+      <c r="R7" s="37"/>
+      <c r="S7" s="37"/>
       <c r="T7" s="37"/>
-      <c r="U7" s="37"/>
-      <c r="V7" s="37"/>
-      <c r="W7" s="37"/>
-      <c r="X7" s="37"/>
-      <c r="Y7" s="37"/>
-      <c r="Z7" s="37"/>
-      <c r="AA7" s="37"/>
-      <c r="AB7" s="37"/>
-      <c r="AC7" s="45"/>
+      <c r="U7" s="45"/>
     </row>
     <row r="8" ht="13.75" customHeight="1">
       <c r="A8" t="s" s="2">
@@ -4024,51 +3951,47 @@
       <c r="B8" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="C8" s="8"/>
-      <c r="D8" t="s" s="34">
-        <v>69</v>
+      <c r="C8" t="inlineStr" s="34">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr" s="36">
+        <is>
+          <t>Dépôt naturel</t>
+        </is>
       </c>
       <c r="E8" s="37"/>
-      <c r="F8" t="s" s="36">
-        <v>70</v>
-      </c>
-      <c r="G8" s="37"/>
-      <c r="H8" s="37"/>
-      <c r="I8" s="37"/>
-      <c r="J8" t="s" s="39">
+      <c r="F8" t="s" s="39">
         <v>88</v>
       </c>
-      <c r="K8" t="s" s="6">
-        <v>72</v>
-      </c>
-      <c r="L8" t="s" s="2">
-        <v>6</v>
-      </c>
+      <c r="G8" t="s" s="6">
+        <v>72</v>
+      </c>
+      <c r="H8" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J8" s="40">
+        <v>41091</v>
+      </c>
+      <c r="K8" s="44"/>
+      <c r="L8" s="45"/>
       <c r="M8" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="N8" s="40">
-        <v>41091</v>
+        <v>74</v>
+      </c>
+      <c r="N8" s="43">
+        <v>9</v>
       </c>
       <c r="O8" s="44"/>
-      <c r="P8" s="45"/>
-      <c r="Q8" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R8" s="43">
-        <v>9</v>
-      </c>
-      <c r="S8" s="44"/>
+      <c r="P8" s="37"/>
+      <c r="Q8" s="37"/>
+      <c r="R8" s="37"/>
+      <c r="S8" s="37"/>
       <c r="T8" s="37"/>
-      <c r="U8" s="37"/>
-      <c r="V8" s="37"/>
-      <c r="W8" s="37"/>
-      <c r="X8" s="37"/>
-      <c r="Y8" s="37"/>
-      <c r="Z8" s="37"/>
-      <c r="AA8" s="37"/>
-      <c r="AB8" s="37"/>
-      <c r="AC8" s="45"/>
+      <c r="U8" s="45"/>
     </row>
     <row r="9" ht="13.75" customHeight="1">
       <c r="A9" t="s" s="2">
@@ -4077,51 +4000,47 @@
       <c r="B9" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="C9" s="8"/>
-      <c r="D9" t="s" s="34">
-        <v>69</v>
+      <c r="C9" t="inlineStr" s="34">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr" s="36">
+        <is>
+          <t>Dépôt naturel</t>
+        </is>
       </c>
       <c r="E9" s="37"/>
-      <c r="F9" t="s" s="36">
-        <v>70</v>
-      </c>
-      <c r="G9" s="37"/>
-      <c r="H9" s="37"/>
-      <c r="I9" s="37"/>
-      <c r="J9" t="s" s="39">
+      <c r="F9" t="s" s="39">
         <v>84</v>
       </c>
-      <c r="K9" t="s" s="6">
-        <v>72</v>
-      </c>
-      <c r="L9" t="s" s="2">
-        <v>6</v>
-      </c>
+      <c r="G9" t="s" s="6">
+        <v>72</v>
+      </c>
+      <c r="H9" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J9" s="40">
+        <v>41091</v>
+      </c>
+      <c r="K9" s="44"/>
+      <c r="L9" s="45"/>
       <c r="M9" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="N9" s="40">
-        <v>41091</v>
+        <v>74</v>
+      </c>
+      <c r="N9" s="43">
+        <v>9</v>
       </c>
       <c r="O9" s="44"/>
-      <c r="P9" s="45"/>
-      <c r="Q9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R9" s="43">
-        <v>9</v>
-      </c>
-      <c r="S9" s="44"/>
+      <c r="P9" s="37"/>
+      <c r="Q9" s="37"/>
+      <c r="R9" s="37"/>
+      <c r="S9" s="37"/>
       <c r="T9" s="37"/>
-      <c r="U9" s="37"/>
-      <c r="V9" s="37"/>
-      <c r="W9" s="37"/>
-      <c r="X9" s="37"/>
-      <c r="Y9" s="37"/>
-      <c r="Z9" s="37"/>
-      <c r="AA9" s="37"/>
-      <c r="AB9" s="37"/>
-      <c r="AC9" s="45"/>
+      <c r="U9" s="45"/>
     </row>
     <row r="10" ht="13.75" customHeight="1">
       <c r="A10" t="s" s="2">
@@ -4130,51 +4049,47 @@
       <c r="B10" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="C10" s="8"/>
-      <c r="D10" t="s" s="34">
-        <v>69</v>
+      <c r="C10" t="inlineStr" s="34">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr" s="36">
+        <is>
+          <t>Dépôt naturel</t>
+        </is>
       </c>
       <c r="E10" s="37"/>
-      <c r="F10" t="s" s="36">
-        <v>70</v>
-      </c>
-      <c r="G10" s="37"/>
-      <c r="H10" s="37"/>
-      <c r="I10" s="37"/>
-      <c r="J10" t="s" s="39">
+      <c r="F10" t="s" s="39">
         <v>95</v>
       </c>
-      <c r="K10" t="s" s="6">
-        <v>72</v>
-      </c>
-      <c r="L10" t="s" s="2">
-        <v>6</v>
-      </c>
+      <c r="G10" t="s" s="6">
+        <v>72</v>
+      </c>
+      <c r="H10" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J10" s="40">
+        <v>41091</v>
+      </c>
+      <c r="K10" s="44"/>
+      <c r="L10" s="45"/>
       <c r="M10" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="N10" s="40">
-        <v>41091</v>
+        <v>74</v>
+      </c>
+      <c r="N10" s="43">
+        <v>9</v>
       </c>
       <c r="O10" s="44"/>
-      <c r="P10" s="45"/>
-      <c r="Q10" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R10" s="43">
-        <v>9</v>
-      </c>
-      <c r="S10" s="44"/>
+      <c r="P10" s="37"/>
+      <c r="Q10" s="37"/>
+      <c r="R10" s="37"/>
+      <c r="S10" s="37"/>
       <c r="T10" s="37"/>
-      <c r="U10" s="37"/>
-      <c r="V10" s="37"/>
-      <c r="W10" s="37"/>
-      <c r="X10" s="37"/>
-      <c r="Y10" s="37"/>
-      <c r="Z10" s="37"/>
-      <c r="AA10" s="37"/>
-      <c r="AB10" s="37"/>
-      <c r="AC10" s="45"/>
+      <c r="U10" s="45"/>
     </row>
     <row r="11" ht="13.75" customHeight="1">
       <c r="A11" t="s" s="2">
@@ -4183,51 +4098,47 @@
       <c r="B11" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="C11" s="8"/>
-      <c r="D11" t="s" s="34">
-        <v>69</v>
+      <c r="C11" t="inlineStr" s="34">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr" s="36">
+        <is>
+          <t>Dépôt naturel</t>
+        </is>
       </c>
       <c r="E11" s="37"/>
-      <c r="F11" t="s" s="36">
-        <v>70</v>
-      </c>
-      <c r="G11" s="37"/>
-      <c r="H11" s="37"/>
-      <c r="I11" s="37"/>
-      <c r="J11" t="s" s="39">
+      <c r="F11" t="s" s="39">
         <v>84</v>
       </c>
-      <c r="K11" t="s" s="6">
-        <v>72</v>
-      </c>
-      <c r="L11" t="s" s="2">
-        <v>6</v>
-      </c>
+      <c r="G11" t="s" s="6">
+        <v>72</v>
+      </c>
+      <c r="H11" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I11" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J11" s="40">
+        <v>41091</v>
+      </c>
+      <c r="K11" s="44"/>
+      <c r="L11" s="45"/>
       <c r="M11" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="N11" s="40">
-        <v>41091</v>
+        <v>74</v>
+      </c>
+      <c r="N11" s="43">
+        <v>9</v>
       </c>
       <c r="O11" s="44"/>
-      <c r="P11" s="45"/>
-      <c r="Q11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R11" s="43">
-        <v>9</v>
-      </c>
-      <c r="S11" s="44"/>
+      <c r="P11" s="37"/>
+      <c r="Q11" s="37"/>
+      <c r="R11" s="37"/>
+      <c r="S11" s="37"/>
       <c r="T11" s="37"/>
-      <c r="U11" s="37"/>
-      <c r="V11" s="37"/>
-      <c r="W11" s="37"/>
-      <c r="X11" s="37"/>
-      <c r="Y11" s="37"/>
-      <c r="Z11" s="37"/>
-      <c r="AA11" s="37"/>
-      <c r="AB11" s="37"/>
-      <c r="AC11" s="45"/>
+      <c r="U11" s="45"/>
     </row>
     <row r="12" ht="13.75" customHeight="1">
       <c r="A12" t="s" s="2">
@@ -4236,51 +4147,47 @@
       <c r="B12" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="C12" s="8"/>
-      <c r="D12" t="s" s="34">
-        <v>69</v>
+      <c r="C12" t="inlineStr" s="34">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr" s="36">
+        <is>
+          <t>Dépôt naturel</t>
+        </is>
       </c>
       <c r="E12" s="37"/>
-      <c r="F12" t="s" s="36">
-        <v>70</v>
-      </c>
-      <c r="G12" s="37"/>
-      <c r="H12" s="37"/>
-      <c r="I12" s="37"/>
-      <c r="J12" t="s" s="39">
+      <c r="F12" t="s" s="39">
         <v>71</v>
       </c>
-      <c r="K12" t="s" s="6">
-        <v>72</v>
-      </c>
-      <c r="L12" t="s" s="2">
-        <v>6</v>
-      </c>
+      <c r="G12" t="s" s="6">
+        <v>72</v>
+      </c>
+      <c r="H12" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J12" s="40">
+        <v>41091</v>
+      </c>
+      <c r="K12" s="44"/>
+      <c r="L12" s="45"/>
       <c r="M12" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="N12" s="40">
-        <v>41091</v>
+        <v>74</v>
+      </c>
+      <c r="N12" s="43">
+        <v>9</v>
       </c>
       <c r="O12" s="44"/>
-      <c r="P12" s="45"/>
-      <c r="Q12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R12" s="43">
-        <v>9</v>
-      </c>
-      <c r="S12" s="44"/>
+      <c r="P12" s="37"/>
+      <c r="Q12" s="37"/>
+      <c r="R12" s="37"/>
+      <c r="S12" s="37"/>
       <c r="T12" s="37"/>
-      <c r="U12" s="37"/>
-      <c r="V12" s="37"/>
-      <c r="W12" s="37"/>
-      <c r="X12" s="37"/>
-      <c r="Y12" s="37"/>
-      <c r="Z12" s="37"/>
-      <c r="AA12" s="37"/>
-      <c r="AB12" s="37"/>
-      <c r="AC12" s="45"/>
+      <c r="U12" s="45"/>
     </row>
     <row r="13" ht="13.75" customHeight="1">
       <c r="A13" t="s" s="2">
@@ -4289,51 +4196,47 @@
       <c r="B13" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="C13" s="8"/>
-      <c r="D13" t="s" s="34">
-        <v>69</v>
+      <c r="C13" t="inlineStr" s="34">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr" s="36">
+        <is>
+          <t>Dépôt naturel</t>
+        </is>
       </c>
       <c r="E13" s="37"/>
-      <c r="F13" t="s" s="36">
-        <v>70</v>
-      </c>
-      <c r="G13" s="37"/>
-      <c r="H13" s="37"/>
-      <c r="I13" s="37"/>
-      <c r="J13" t="s" s="39">
+      <c r="F13" t="s" s="39">
         <v>84</v>
       </c>
-      <c r="K13" t="s" s="6">
-        <v>72</v>
-      </c>
-      <c r="L13" t="s" s="2">
-        <v>6</v>
-      </c>
+      <c r="G13" t="s" s="6">
+        <v>72</v>
+      </c>
+      <c r="H13" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J13" s="40">
+        <v>41091</v>
+      </c>
+      <c r="K13" s="44"/>
+      <c r="L13" s="45"/>
       <c r="M13" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="N13" s="40">
-        <v>41091</v>
+        <v>74</v>
+      </c>
+      <c r="N13" s="43">
+        <v>9</v>
       </c>
       <c r="O13" s="44"/>
-      <c r="P13" s="45"/>
-      <c r="Q13" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R13" s="43">
-        <v>9</v>
-      </c>
-      <c r="S13" s="44"/>
+      <c r="P13" s="37"/>
+      <c r="Q13" s="37"/>
+      <c r="R13" s="37"/>
+      <c r="S13" s="37"/>
       <c r="T13" s="37"/>
-      <c r="U13" s="37"/>
-      <c r="V13" s="37"/>
-      <c r="W13" s="37"/>
-      <c r="X13" s="37"/>
-      <c r="Y13" s="37"/>
-      <c r="Z13" s="37"/>
-      <c r="AA13" s="37"/>
-      <c r="AB13" s="37"/>
-      <c r="AC13" s="45"/>
+      <c r="U13" s="45"/>
     </row>
     <row r="14" ht="13.75" customHeight="1">
       <c r="A14" t="s" s="2">
@@ -4342,51 +4245,45 @@
       <c r="B14" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="C14" s="8"/>
-      <c r="D14" t="s" s="34">
-        <v>69</v>
+      <c r="C14" t="inlineStr" s="34">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr" s="36">
+        <is>
+          <t>Négative</t>
+        </is>
       </c>
       <c r="E14" s="37"/>
-      <c r="F14" t="s" s="36">
-        <v>104</v>
-      </c>
-      <c r="G14" s="37"/>
-      <c r="H14" s="37"/>
-      <c r="I14" s="37"/>
-      <c r="J14" t="s" s="39">
-        <v>105</v>
-      </c>
-      <c r="K14" t="s" s="6">
-        <v>72</v>
-      </c>
-      <c r="L14" t="s" s="2">
-        <v>6</v>
-      </c>
+      <c r="F14" s="39"/>
+      <c r="G14" t="s" s="6">
+        <v>72</v>
+      </c>
+      <c r="H14" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I14" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J14" s="40">
+        <v>41091</v>
+      </c>
+      <c r="K14" s="44"/>
+      <c r="L14" s="45"/>
       <c r="M14" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="N14" s="40">
-        <v>41091</v>
+        <v>74</v>
+      </c>
+      <c r="N14" s="43">
+        <v>9</v>
       </c>
       <c r="O14" s="44"/>
-      <c r="P14" s="45"/>
-      <c r="Q14" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R14" s="43">
-        <v>9</v>
-      </c>
-      <c r="S14" s="44"/>
+      <c r="P14" s="37"/>
+      <c r="Q14" s="37"/>
+      <c r="R14" s="37"/>
+      <c r="S14" s="37"/>
       <c r="T14" s="37"/>
-      <c r="U14" s="37"/>
-      <c r="V14" s="37"/>
-      <c r="W14" s="37"/>
-      <c r="X14" s="37"/>
-      <c r="Y14" s="37"/>
-      <c r="Z14" s="37"/>
-      <c r="AA14" s="37"/>
-      <c r="AB14" s="37"/>
-      <c r="AC14" s="45"/>
+      <c r="U14" s="45"/>
     </row>
     <row r="15" ht="13.75" customHeight="1">
       <c r="A15" t="s" s="2">
@@ -4395,51 +4292,47 @@
       <c r="B15" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="C15" s="8"/>
-      <c r="D15" t="s" s="34">
-        <v>69</v>
+      <c r="C15" t="inlineStr" s="34">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr" s="36">
+        <is>
+          <t>Dépôt naturel</t>
+        </is>
       </c>
       <c r="E15" s="37"/>
-      <c r="F15" t="s" s="36">
-        <v>70</v>
-      </c>
-      <c r="G15" s="37"/>
-      <c r="H15" s="37"/>
-      <c r="I15" s="37"/>
-      <c r="J15" t="s" s="39">
+      <c r="F15" t="s" s="39">
         <v>108</v>
       </c>
-      <c r="K15" t="s" s="6">
-        <v>72</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>6</v>
-      </c>
+      <c r="G15" t="s" s="6">
+        <v>72</v>
+      </c>
+      <c r="H15" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I15" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J15" s="40">
+        <v>41091</v>
+      </c>
+      <c r="K15" s="44"/>
+      <c r="L15" s="45"/>
       <c r="M15" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="N15" s="40">
-        <v>41091</v>
+        <v>74</v>
+      </c>
+      <c r="N15" s="43">
+        <v>9</v>
       </c>
       <c r="O15" s="44"/>
-      <c r="P15" s="45"/>
-      <c r="Q15" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R15" s="43">
-        <v>9</v>
-      </c>
-      <c r="S15" s="44"/>
+      <c r="P15" s="37"/>
+      <c r="Q15" s="37"/>
+      <c r="R15" s="37"/>
+      <c r="S15" s="37"/>
       <c r="T15" s="37"/>
-      <c r="U15" s="37"/>
-      <c r="V15" s="37"/>
-      <c r="W15" s="37"/>
-      <c r="X15" s="37"/>
-      <c r="Y15" s="37"/>
-      <c r="Z15" s="37"/>
-      <c r="AA15" s="37"/>
-      <c r="AB15" s="37"/>
-      <c r="AC15" s="45"/>
+      <c r="U15" s="45"/>
     </row>
     <row r="16" ht="13.75" customHeight="1">
       <c r="A16" t="s" s="2">
@@ -4448,51 +4341,45 @@
       <c r="B16" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="C16" s="8"/>
-      <c r="D16" t="s" s="34">
-        <v>69</v>
+      <c r="C16" t="inlineStr" s="34">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr" s="36">
+        <is>
+          <t>Négative</t>
+        </is>
       </c>
       <c r="E16" s="37"/>
-      <c r="F16" t="s" s="36">
-        <v>104</v>
-      </c>
-      <c r="G16" s="37"/>
-      <c r="H16" s="37"/>
-      <c r="I16" s="37"/>
-      <c r="J16" t="s" s="39">
-        <v>105</v>
-      </c>
-      <c r="K16" t="s" s="6">
-        <v>72</v>
-      </c>
-      <c r="L16" t="s" s="2">
-        <v>6</v>
-      </c>
+      <c r="F16" s="39"/>
+      <c r="G16" t="s" s="6">
+        <v>72</v>
+      </c>
+      <c r="H16" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I16" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J16" s="40">
+        <v>41091</v>
+      </c>
+      <c r="K16" s="44"/>
+      <c r="L16" s="45"/>
       <c r="M16" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="N16" s="40">
-        <v>41091</v>
+        <v>74</v>
+      </c>
+      <c r="N16" s="43">
+        <v>9</v>
       </c>
       <c r="O16" s="44"/>
-      <c r="P16" s="45"/>
-      <c r="Q16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R16" s="43">
-        <v>9</v>
-      </c>
-      <c r="S16" s="44"/>
+      <c r="P16" s="37"/>
+      <c r="Q16" s="37"/>
+      <c r="R16" s="37"/>
+      <c r="S16" s="37"/>
       <c r="T16" s="37"/>
-      <c r="U16" s="37"/>
-      <c r="V16" s="37"/>
-      <c r="W16" s="37"/>
-      <c r="X16" s="37"/>
-      <c r="Y16" s="37"/>
-      <c r="Z16" s="37"/>
-      <c r="AA16" s="37"/>
-      <c r="AB16" s="37"/>
-      <c r="AC16" s="45"/>
+      <c r="U16" s="45"/>
     </row>
     <row r="17" ht="13.75" customHeight="1">
       <c r="A17" t="s" s="2">
@@ -4501,51 +4388,45 @@
       <c r="B17" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="C17" s="8"/>
-      <c r="D17" t="s" s="34">
-        <v>69</v>
+      <c r="C17" t="inlineStr" s="34">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr" s="36">
+        <is>
+          <t>Négative</t>
+        </is>
       </c>
       <c r="E17" s="37"/>
-      <c r="F17" t="s" s="36">
-        <v>104</v>
-      </c>
-      <c r="G17" s="37"/>
-      <c r="H17" s="37"/>
-      <c r="I17" s="37"/>
-      <c r="J17" t="s" s="39">
-        <v>105</v>
-      </c>
-      <c r="K17" t="s" s="6">
-        <v>72</v>
-      </c>
-      <c r="L17" t="s" s="2">
-        <v>6</v>
-      </c>
+      <c r="F17" s="39"/>
+      <c r="G17" t="s" s="6">
+        <v>72</v>
+      </c>
+      <c r="H17" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J17" s="40">
+        <v>41095</v>
+      </c>
+      <c r="K17" s="44"/>
+      <c r="L17" s="45"/>
       <c r="M17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="N17" s="40">
-        <v>41095</v>
+        <v>74</v>
+      </c>
+      <c r="N17" s="43">
+        <v>9</v>
       </c>
       <c r="O17" s="44"/>
-      <c r="P17" s="45"/>
-      <c r="Q17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R17" s="43">
-        <v>9</v>
-      </c>
-      <c r="S17" s="44"/>
+      <c r="P17" s="37"/>
+      <c r="Q17" s="37"/>
+      <c r="R17" s="37"/>
+      <c r="S17" s="37"/>
       <c r="T17" s="37"/>
-      <c r="U17" s="37"/>
-      <c r="V17" s="37"/>
-      <c r="W17" s="37"/>
-      <c r="X17" s="37"/>
-      <c r="Y17" s="37"/>
-      <c r="Z17" s="37"/>
-      <c r="AA17" s="37"/>
-      <c r="AB17" s="37"/>
-      <c r="AC17" s="45"/>
+      <c r="U17" s="45"/>
     </row>
     <row r="18" ht="13.75" customHeight="1">
       <c r="A18" t="s" s="2">
@@ -4554,51 +4435,47 @@
       <c r="B18" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="C18" s="8"/>
-      <c r="D18" t="s" s="34">
-        <v>69</v>
+      <c r="C18" t="inlineStr" s="34">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr" s="36">
+        <is>
+          <t>Dépôt naturel</t>
+        </is>
       </c>
       <c r="E18" s="37"/>
-      <c r="F18" t="s" s="36">
-        <v>70</v>
-      </c>
-      <c r="G18" s="37"/>
-      <c r="H18" s="37"/>
-      <c r="I18" s="37"/>
-      <c r="J18" t="s" s="39">
+      <c r="F18" t="s" s="39">
         <v>81</v>
       </c>
-      <c r="K18" t="s" s="6">
-        <v>72</v>
-      </c>
-      <c r="L18" t="s" s="2">
-        <v>6</v>
-      </c>
+      <c r="G18" t="s" s="6">
+        <v>72</v>
+      </c>
+      <c r="H18" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J18" s="40">
+        <v>41095</v>
+      </c>
+      <c r="K18" s="44"/>
+      <c r="L18" s="45"/>
       <c r="M18" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="N18" s="40">
-        <v>41095</v>
+        <v>74</v>
+      </c>
+      <c r="N18" s="43">
+        <v>9</v>
       </c>
       <c r="O18" s="44"/>
-      <c r="P18" s="45"/>
-      <c r="Q18" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R18" s="43">
-        <v>9</v>
-      </c>
-      <c r="S18" s="44"/>
+      <c r="P18" s="37"/>
+      <c r="Q18" s="37"/>
+      <c r="R18" s="37"/>
+      <c r="S18" s="37"/>
       <c r="T18" s="37"/>
-      <c r="U18" s="37"/>
-      <c r="V18" s="37"/>
-      <c r="W18" s="37"/>
-      <c r="X18" s="37"/>
-      <c r="Y18" s="37"/>
-      <c r="Z18" s="37"/>
-      <c r="AA18" s="37"/>
-      <c r="AB18" s="37"/>
-      <c r="AC18" s="45"/>
+      <c r="U18" s="45"/>
     </row>
     <row r="19" ht="13.75" customHeight="1">
       <c r="A19" t="s" s="2">
@@ -4607,51 +4484,47 @@
       <c r="B19" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="C19" s="8"/>
-      <c r="D19" t="s" s="34">
-        <v>69</v>
+      <c r="C19" t="inlineStr" s="34">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr" s="36">
+        <is>
+          <t>Dépôt naturel</t>
+        </is>
       </c>
       <c r="E19" s="37"/>
-      <c r="F19" t="s" s="36">
-        <v>70</v>
-      </c>
-      <c r="G19" s="37"/>
-      <c r="H19" s="37"/>
-      <c r="I19" s="37"/>
-      <c r="J19" t="s" s="39">
+      <c r="F19" t="s" s="39">
         <v>81</v>
       </c>
-      <c r="K19" t="s" s="6">
-        <v>72</v>
-      </c>
-      <c r="L19" t="s" s="2">
-        <v>6</v>
-      </c>
+      <c r="G19" t="s" s="6">
+        <v>72</v>
+      </c>
+      <c r="H19" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J19" s="40">
+        <v>41095</v>
+      </c>
+      <c r="K19" s="44"/>
+      <c r="L19" s="45"/>
       <c r="M19" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="N19" s="40">
-        <v>41095</v>
+        <v>74</v>
+      </c>
+      <c r="N19" s="43">
+        <v>9</v>
       </c>
       <c r="O19" s="44"/>
-      <c r="P19" s="45"/>
-      <c r="Q19" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R19" s="43">
-        <v>9</v>
-      </c>
-      <c r="S19" s="44"/>
+      <c r="P19" s="37"/>
+      <c r="Q19" s="37"/>
+      <c r="R19" s="37"/>
+      <c r="S19" s="37"/>
       <c r="T19" s="37"/>
-      <c r="U19" s="37"/>
-      <c r="V19" s="37"/>
-      <c r="W19" s="37"/>
-      <c r="X19" s="37"/>
-      <c r="Y19" s="37"/>
-      <c r="Z19" s="37"/>
-      <c r="AA19" s="37"/>
-      <c r="AB19" s="37"/>
-      <c r="AC19" s="45"/>
+      <c r="U19" s="45"/>
     </row>
     <row r="20" ht="13.75" customHeight="1">
       <c r="A20" t="s" s="2">
@@ -4660,51 +4533,47 @@
       <c r="B20" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="C20" s="8"/>
-      <c r="D20" t="s" s="34">
-        <v>69</v>
+      <c r="C20" t="inlineStr" s="34">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr" s="36">
+        <is>
+          <t>Dépôt naturel</t>
+        </is>
       </c>
       <c r="E20" s="37"/>
-      <c r="F20" t="s" s="36">
-        <v>70</v>
-      </c>
-      <c r="G20" s="37"/>
-      <c r="H20" s="37"/>
-      <c r="I20" s="37"/>
-      <c r="J20" t="s" s="39">
+      <c r="F20" t="s" s="39">
         <v>119</v>
       </c>
-      <c r="K20" t="s" s="6">
-        <v>72</v>
-      </c>
-      <c r="L20" t="s" s="2">
-        <v>6</v>
-      </c>
+      <c r="G20" t="s" s="6">
+        <v>72</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J20" s="40">
+        <v>41095</v>
+      </c>
+      <c r="K20" s="44"/>
+      <c r="L20" s="45"/>
       <c r="M20" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="N20" s="40">
-        <v>41095</v>
+        <v>74</v>
+      </c>
+      <c r="N20" s="43">
+        <v>9</v>
       </c>
       <c r="O20" s="44"/>
-      <c r="P20" s="45"/>
-      <c r="Q20" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R20" s="43">
-        <v>9</v>
-      </c>
-      <c r="S20" s="44"/>
+      <c r="P20" s="37"/>
+      <c r="Q20" s="37"/>
+      <c r="R20" s="37"/>
+      <c r="S20" s="37"/>
       <c r="T20" s="37"/>
-      <c r="U20" s="37"/>
-      <c r="V20" s="37"/>
-      <c r="W20" s="37"/>
-      <c r="X20" s="37"/>
-      <c r="Y20" s="37"/>
-      <c r="Z20" s="37"/>
-      <c r="AA20" s="37"/>
-      <c r="AB20" s="37"/>
-      <c r="AC20" s="45"/>
+      <c r="U20" s="45"/>
     </row>
     <row r="21" ht="13.75" customHeight="1">
       <c r="A21" t="s" s="2">
@@ -4713,51 +4582,47 @@
       <c r="B21" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="C21" s="8"/>
-      <c r="D21" t="s" s="34">
-        <v>69</v>
+      <c r="C21" t="inlineStr" s="34">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr" s="36">
+        <is>
+          <t>Dépôt naturel</t>
+        </is>
       </c>
       <c r="E21" s="37"/>
-      <c r="F21" t="s" s="36">
-        <v>70</v>
-      </c>
-      <c r="G21" s="37"/>
-      <c r="H21" s="37"/>
-      <c r="I21" s="37"/>
-      <c r="J21" t="s" s="39">
+      <c r="F21" t="s" s="39">
         <v>108</v>
       </c>
-      <c r="K21" t="s" s="6">
-        <v>72</v>
-      </c>
-      <c r="L21" t="s" s="2">
-        <v>6</v>
-      </c>
+      <c r="G21" t="s" s="6">
+        <v>72</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J21" s="40">
+        <v>41095</v>
+      </c>
+      <c r="K21" s="44"/>
+      <c r="L21" s="45"/>
       <c r="M21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="N21" s="40">
-        <v>41095</v>
+        <v>74</v>
+      </c>
+      <c r="N21" s="43">
+        <v>9</v>
       </c>
       <c r="O21" s="44"/>
-      <c r="P21" s="45"/>
-      <c r="Q21" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R21" s="43">
-        <v>9</v>
-      </c>
-      <c r="S21" s="44"/>
+      <c r="P21" s="37"/>
+      <c r="Q21" s="37"/>
+      <c r="R21" s="37"/>
+      <c r="S21" s="37"/>
       <c r="T21" s="37"/>
-      <c r="U21" s="37"/>
-      <c r="V21" s="37"/>
-      <c r="W21" s="37"/>
-      <c r="X21" s="37"/>
-      <c r="Y21" s="37"/>
-      <c r="Z21" s="37"/>
-      <c r="AA21" s="37"/>
-      <c r="AB21" s="37"/>
-      <c r="AC21" s="45"/>
+      <c r="U21" s="45"/>
     </row>
     <row r="22" ht="13.75" customHeight="1">
       <c r="A22" t="s" s="2">
@@ -4766,51 +4631,47 @@
       <c r="B22" t="s" s="2">
         <v>123</v>
       </c>
-      <c r="C22" s="8"/>
-      <c r="D22" t="s" s="34">
-        <v>69</v>
+      <c r="C22" t="inlineStr" s="34">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr" s="36">
+        <is>
+          <t>Dépôt naturel</t>
+        </is>
       </c>
       <c r="E22" s="37"/>
-      <c r="F22" t="s" s="36">
-        <v>70</v>
-      </c>
-      <c r="G22" s="37"/>
-      <c r="H22" s="37"/>
-      <c r="I22" s="37"/>
-      <c r="J22" t="s" s="39">
+      <c r="F22" t="s" s="39">
         <v>88</v>
       </c>
-      <c r="K22" t="s" s="6">
-        <v>72</v>
-      </c>
-      <c r="L22" t="s" s="2">
-        <v>6</v>
-      </c>
+      <c r="G22" t="s" s="6">
+        <v>72</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J22" s="40">
+        <v>41095</v>
+      </c>
+      <c r="K22" s="44"/>
+      <c r="L22" s="45"/>
       <c r="M22" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="N22" s="40">
-        <v>41095</v>
+        <v>74</v>
+      </c>
+      <c r="N22" s="43">
+        <v>9</v>
       </c>
       <c r="O22" s="44"/>
-      <c r="P22" s="45"/>
-      <c r="Q22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R22" s="43">
-        <v>9</v>
-      </c>
-      <c r="S22" s="44"/>
+      <c r="P22" s="37"/>
+      <c r="Q22" s="37"/>
+      <c r="R22" s="37"/>
+      <c r="S22" s="37"/>
       <c r="T22" s="37"/>
-      <c r="U22" s="37"/>
-      <c r="V22" s="37"/>
-      <c r="W22" s="37"/>
-      <c r="X22" s="37"/>
-      <c r="Y22" s="37"/>
-      <c r="Z22" s="37"/>
-      <c r="AA22" s="37"/>
-      <c r="AB22" s="37"/>
-      <c r="AC22" s="45"/>
+      <c r="U22" s="45"/>
     </row>
     <row r="23" ht="13.75" customHeight="1">
       <c r="A23" t="s" s="2">
@@ -4819,51 +4680,47 @@
       <c r="B23" t="s" s="2">
         <v>125</v>
       </c>
-      <c r="C23" s="8"/>
-      <c r="D23" t="s" s="34">
-        <v>69</v>
+      <c r="C23" t="inlineStr" s="34">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr" s="36">
+        <is>
+          <t>Dépôt naturel</t>
+        </is>
       </c>
       <c r="E23" s="37"/>
-      <c r="F23" t="s" s="36">
-        <v>70</v>
-      </c>
-      <c r="G23" s="37"/>
-      <c r="H23" s="37"/>
-      <c r="I23" s="37"/>
-      <c r="J23" t="s" s="39">
+      <c r="F23" t="s" s="39">
         <v>126</v>
       </c>
-      <c r="K23" t="s" s="6">
-        <v>72</v>
-      </c>
-      <c r="L23" t="s" s="2">
-        <v>6</v>
-      </c>
+      <c r="G23" t="s" s="6">
+        <v>72</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J23" s="40">
+        <v>41095</v>
+      </c>
+      <c r="K23" s="44"/>
+      <c r="L23" s="45"/>
       <c r="M23" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="N23" s="40">
-        <v>41095</v>
+        <v>74</v>
+      </c>
+      <c r="N23" s="43">
+        <v>9</v>
       </c>
       <c r="O23" s="44"/>
-      <c r="P23" s="45"/>
-      <c r="Q23" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R23" s="43">
-        <v>9</v>
-      </c>
-      <c r="S23" s="44"/>
+      <c r="P23" s="37"/>
+      <c r="Q23" s="37"/>
+      <c r="R23" s="37"/>
+      <c r="S23" s="37"/>
       <c r="T23" s="37"/>
-      <c r="U23" s="37"/>
-      <c r="V23" s="37"/>
-      <c r="W23" s="37"/>
-      <c r="X23" s="37"/>
-      <c r="Y23" s="37"/>
-      <c r="Z23" s="37"/>
-      <c r="AA23" s="37"/>
-      <c r="AB23" s="37"/>
-      <c r="AC23" s="45"/>
+      <c r="U23" s="45"/>
     </row>
     <row r="24" ht="13.75" customHeight="1">
       <c r="A24" t="s" s="2">
@@ -4872,51 +4729,45 @@
       <c r="B24" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="C24" s="8"/>
-      <c r="D24" t="s" s="34">
-        <v>69</v>
+      <c r="C24" t="inlineStr" s="34">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr" s="36">
+        <is>
+          <t>Négative</t>
+        </is>
       </c>
       <c r="E24" s="37"/>
-      <c r="F24" t="s" s="36">
-        <v>104</v>
-      </c>
-      <c r="G24" s="37"/>
-      <c r="H24" s="37"/>
-      <c r="I24" s="37"/>
-      <c r="J24" t="s" s="39">
-        <v>105</v>
-      </c>
-      <c r="K24" t="s" s="6">
-        <v>72</v>
-      </c>
-      <c r="L24" t="s" s="2">
-        <v>6</v>
-      </c>
+      <c r="F24" s="39"/>
+      <c r="G24" t="s" s="6">
+        <v>72</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J24" s="40">
+        <v>41099</v>
+      </c>
+      <c r="K24" s="44"/>
+      <c r="L24" s="45"/>
       <c r="M24" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="N24" s="40">
-        <v>41099</v>
+        <v>74</v>
+      </c>
+      <c r="N24" s="43">
+        <v>9</v>
       </c>
       <c r="O24" s="44"/>
-      <c r="P24" s="45"/>
-      <c r="Q24" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R24" s="43">
-        <v>9</v>
-      </c>
-      <c r="S24" s="44"/>
+      <c r="P24" s="37"/>
+      <c r="Q24" s="37"/>
+      <c r="R24" s="37"/>
+      <c r="S24" s="37"/>
       <c r="T24" s="37"/>
-      <c r="U24" s="37"/>
-      <c r="V24" s="37"/>
-      <c r="W24" s="37"/>
-      <c r="X24" s="37"/>
-      <c r="Y24" s="37"/>
-      <c r="Z24" s="37"/>
-      <c r="AA24" s="37"/>
-      <c r="AB24" s="37"/>
-      <c r="AC24" s="45"/>
+      <c r="U24" s="45"/>
     </row>
     <row r="25" ht="13.75" customHeight="1">
       <c r="A25" t="s" s="2">
@@ -4925,51 +4776,45 @@
       <c r="B25" t="s" s="2">
         <v>130</v>
       </c>
-      <c r="C25" s="8"/>
-      <c r="D25" t="s" s="34">
-        <v>69</v>
+      <c r="C25" t="inlineStr" s="34">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr" s="36">
+        <is>
+          <t>Dépôt naturel</t>
+        </is>
       </c>
       <c r="E25" s="37"/>
-      <c r="F25" t="s" s="36">
-        <v>70</v>
-      </c>
-      <c r="G25" s="37"/>
-      <c r="H25" s="37"/>
-      <c r="I25" s="37"/>
-      <c r="J25" t="s" s="39">
-        <v>105</v>
-      </c>
-      <c r="K25" t="s" s="6">
-        <v>72</v>
-      </c>
-      <c r="L25" t="s" s="2">
-        <v>6</v>
-      </c>
+      <c r="F25" s="39"/>
+      <c r="G25" t="s" s="6">
+        <v>72</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J25" s="40">
+        <v>41099</v>
+      </c>
+      <c r="K25" s="44"/>
+      <c r="L25" s="45"/>
       <c r="M25" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="N25" s="40">
-        <v>41099</v>
+        <v>74</v>
+      </c>
+      <c r="N25" s="43">
+        <v>9</v>
       </c>
       <c r="O25" s="44"/>
-      <c r="P25" s="45"/>
-      <c r="Q25" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R25" s="43">
-        <v>9</v>
-      </c>
-      <c r="S25" s="44"/>
+      <c r="P25" s="37"/>
+      <c r="Q25" s="37"/>
+      <c r="R25" s="37"/>
+      <c r="S25" s="37"/>
       <c r="T25" s="37"/>
-      <c r="U25" s="37"/>
-      <c r="V25" s="37"/>
-      <c r="W25" s="37"/>
-      <c r="X25" s="37"/>
-      <c r="Y25" s="37"/>
-      <c r="Z25" s="37"/>
-      <c r="AA25" s="37"/>
-      <c r="AB25" s="37"/>
-      <c r="AC25" s="45"/>
+      <c r="U25" s="45"/>
     </row>
     <row r="26" ht="13.75" customHeight="1">
       <c r="A26" t="s" s="2">
@@ -4978,51 +4823,47 @@
       <c r="B26" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="C26" s="8"/>
-      <c r="D26" t="s" s="34">
-        <v>69</v>
+      <c r="C26" t="inlineStr" s="34">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr" s="36">
+        <is>
+          <t>Dépôt naturel</t>
+        </is>
       </c>
       <c r="E26" s="37"/>
-      <c r="F26" t="s" s="36">
-        <v>70</v>
-      </c>
-      <c r="G26" s="37"/>
-      <c r="H26" s="37"/>
-      <c r="I26" s="37"/>
-      <c r="J26" t="s" s="39">
+      <c r="F26" t="s" s="39">
         <v>95</v>
       </c>
-      <c r="K26" t="s" s="6">
-        <v>72</v>
-      </c>
-      <c r="L26" t="s" s="2">
-        <v>6</v>
-      </c>
+      <c r="G26" t="s" s="6">
+        <v>72</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J26" s="40">
+        <v>41099</v>
+      </c>
+      <c r="K26" s="44"/>
+      <c r="L26" s="45"/>
       <c r="M26" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="N26" s="40">
-        <v>41099</v>
+        <v>74</v>
+      </c>
+      <c r="N26" s="43">
+        <v>9</v>
       </c>
       <c r="O26" s="44"/>
-      <c r="P26" s="45"/>
-      <c r="Q26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R26" s="43">
-        <v>9</v>
-      </c>
-      <c r="S26" s="44"/>
+      <c r="P26" s="37"/>
+      <c r="Q26" s="37"/>
+      <c r="R26" s="37"/>
+      <c r="S26" s="37"/>
       <c r="T26" s="37"/>
-      <c r="U26" s="37"/>
-      <c r="V26" s="37"/>
-      <c r="W26" s="37"/>
-      <c r="X26" s="37"/>
-      <c r="Y26" s="37"/>
-      <c r="Z26" s="37"/>
-      <c r="AA26" s="37"/>
-      <c r="AB26" s="37"/>
-      <c r="AC26" s="45"/>
+      <c r="U26" s="45"/>
     </row>
     <row r="27" ht="13.75" customHeight="1">
       <c r="A27" t="s" s="2">
@@ -5031,51 +4872,47 @@
       <c r="B27" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="C27" s="8"/>
-      <c r="D27" t="s" s="34">
-        <v>69</v>
+      <c r="C27" t="inlineStr" s="34">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr" s="36">
+        <is>
+          <t>Dépôt naturel</t>
+        </is>
       </c>
       <c r="E27" s="37"/>
-      <c r="F27" t="s" s="36">
-        <v>70</v>
-      </c>
-      <c r="G27" s="37"/>
-      <c r="H27" s="37"/>
-      <c r="I27" s="37"/>
-      <c r="J27" t="s" s="39">
+      <c r="F27" t="s" s="39">
         <v>126</v>
       </c>
-      <c r="K27" t="s" s="6">
-        <v>72</v>
-      </c>
-      <c r="L27" t="s" s="2">
-        <v>6</v>
-      </c>
+      <c r="G27" t="s" s="6">
+        <v>72</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J27" s="40">
+        <v>41099</v>
+      </c>
+      <c r="K27" s="44"/>
+      <c r="L27" s="45"/>
       <c r="M27" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="N27" s="40">
-        <v>41099</v>
+        <v>74</v>
+      </c>
+      <c r="N27" s="43">
+        <v>9</v>
       </c>
       <c r="O27" s="44"/>
-      <c r="P27" s="45"/>
-      <c r="Q27" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R27" s="43">
-        <v>9</v>
-      </c>
-      <c r="S27" s="44"/>
+      <c r="P27" s="37"/>
+      <c r="Q27" s="37"/>
+      <c r="R27" s="37"/>
+      <c r="S27" s="37"/>
       <c r="T27" s="37"/>
-      <c r="U27" s="37"/>
-      <c r="V27" s="37"/>
-      <c r="W27" s="37"/>
-      <c r="X27" s="37"/>
-      <c r="Y27" s="37"/>
-      <c r="Z27" s="37"/>
-      <c r="AA27" s="37"/>
-      <c r="AB27" s="37"/>
-      <c r="AC27" s="45"/>
+      <c r="U27" s="45"/>
     </row>
     <row r="28" ht="13.75" customHeight="1">
       <c r="A28" t="s" s="2">
@@ -5084,51 +4921,47 @@
       <c r="B28" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="C28" s="8"/>
-      <c r="D28" t="s" s="34">
-        <v>69</v>
+      <c r="C28" t="inlineStr" s="34">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr" s="36">
+        <is>
+          <t>Dépôt naturel</t>
+        </is>
       </c>
       <c r="E28" s="37"/>
-      <c r="F28" t="s" s="36">
-        <v>70</v>
-      </c>
-      <c r="G28" s="37"/>
-      <c r="H28" s="37"/>
-      <c r="I28" s="37"/>
-      <c r="J28" t="s" s="39">
+      <c r="F28" t="s" s="39">
         <v>81</v>
       </c>
-      <c r="K28" t="s" s="6">
-        <v>72</v>
-      </c>
-      <c r="L28" t="s" s="2">
-        <v>6</v>
-      </c>
+      <c r="G28" t="s" s="6">
+        <v>72</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J28" s="40">
+        <v>41099</v>
+      </c>
+      <c r="K28" s="44"/>
+      <c r="L28" s="45"/>
       <c r="M28" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="N28" s="40">
-        <v>41099</v>
+        <v>74</v>
+      </c>
+      <c r="N28" s="43">
+        <v>9</v>
       </c>
       <c r="O28" s="44"/>
-      <c r="P28" s="45"/>
-      <c r="Q28" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R28" s="43">
-        <v>9</v>
-      </c>
-      <c r="S28" s="44"/>
+      <c r="P28" s="37"/>
+      <c r="Q28" s="37"/>
+      <c r="R28" s="37"/>
+      <c r="S28" s="37"/>
       <c r="T28" s="37"/>
-      <c r="U28" s="37"/>
-      <c r="V28" s="37"/>
-      <c r="W28" s="37"/>
-      <c r="X28" s="37"/>
-      <c r="Y28" s="37"/>
-      <c r="Z28" s="37"/>
-      <c r="AA28" s="37"/>
-      <c r="AB28" s="37"/>
-      <c r="AC28" s="45"/>
+      <c r="U28" s="45"/>
     </row>
     <row r="29" ht="13.75" customHeight="1">
       <c r="A29" t="s" s="2">
@@ -5137,51 +4970,45 @@
       <c r="B29" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="C29" s="8"/>
-      <c r="D29" t="s" s="34">
-        <v>69</v>
+      <c r="C29" t="inlineStr" s="34">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr" s="36">
+        <is>
+          <t>Négative</t>
+        </is>
       </c>
       <c r="E29" s="37"/>
-      <c r="F29" t="s" s="36">
-        <v>104</v>
-      </c>
-      <c r="G29" s="37"/>
-      <c r="H29" s="37"/>
-      <c r="I29" s="37"/>
-      <c r="J29" t="s" s="39">
-        <v>105</v>
-      </c>
-      <c r="K29" t="s" s="6">
-        <v>72</v>
-      </c>
-      <c r="L29" t="s" s="2">
-        <v>6</v>
-      </c>
+      <c r="F29" s="39"/>
+      <c r="G29" t="s" s="6">
+        <v>72</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J29" s="40">
+        <v>41099</v>
+      </c>
+      <c r="K29" s="44"/>
+      <c r="L29" s="45"/>
       <c r="M29" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="N29" s="40">
-        <v>41099</v>
+        <v>74</v>
+      </c>
+      <c r="N29" s="43">
+        <v>3</v>
       </c>
       <c r="O29" s="44"/>
-      <c r="P29" s="45"/>
-      <c r="Q29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R29" s="43">
-        <v>3</v>
-      </c>
-      <c r="S29" s="44"/>
+      <c r="P29" s="37"/>
+      <c r="Q29" s="37"/>
+      <c r="R29" s="37"/>
+      <c r="S29" s="37"/>
       <c r="T29" s="37"/>
-      <c r="U29" s="37"/>
-      <c r="V29" s="37"/>
-      <c r="W29" s="37"/>
-      <c r="X29" s="37"/>
-      <c r="Y29" s="37"/>
-      <c r="Z29" s="37"/>
-      <c r="AA29" s="37"/>
-      <c r="AB29" s="37"/>
-      <c r="AC29" s="45"/>
+      <c r="U29" s="45"/>
     </row>
     <row r="30" ht="13.75" customHeight="1">
       <c r="A30" t="s" s="2">
@@ -5190,51 +5017,47 @@
       <c r="B30" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="C30" s="8"/>
-      <c r="D30" t="s" s="34">
-        <v>69</v>
+      <c r="C30" t="inlineStr" s="34">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr" s="36">
+        <is>
+          <t>Dépôt naturel</t>
+        </is>
       </c>
       <c r="E30" s="37"/>
-      <c r="F30" t="s" s="36">
-        <v>70</v>
-      </c>
-      <c r="G30" s="37"/>
-      <c r="H30" s="37"/>
-      <c r="I30" s="37"/>
-      <c r="J30" t="s" s="39">
+      <c r="F30" t="s" s="39">
         <v>126</v>
       </c>
-      <c r="K30" t="s" s="6">
-        <v>72</v>
-      </c>
-      <c r="L30" t="s" s="2">
-        <v>6</v>
-      </c>
+      <c r="G30" t="s" s="6">
+        <v>72</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J30" s="40">
+        <v>41099</v>
+      </c>
+      <c r="K30" s="44"/>
+      <c r="L30" s="45"/>
       <c r="M30" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="N30" s="40">
-        <v>41099</v>
+        <v>74</v>
+      </c>
+      <c r="N30" s="43">
+        <v>9</v>
       </c>
       <c r="O30" s="44"/>
-      <c r="P30" s="45"/>
-      <c r="Q30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R30" s="43">
-        <v>9</v>
-      </c>
-      <c r="S30" s="44"/>
+      <c r="P30" s="37"/>
+      <c r="Q30" s="37"/>
+      <c r="R30" s="37"/>
+      <c r="S30" s="37"/>
       <c r="T30" s="37"/>
-      <c r="U30" s="37"/>
-      <c r="V30" s="37"/>
-      <c r="W30" s="37"/>
-      <c r="X30" s="37"/>
-      <c r="Y30" s="37"/>
-      <c r="Z30" s="37"/>
-      <c r="AA30" s="37"/>
-      <c r="AB30" s="37"/>
-      <c r="AC30" s="45"/>
+      <c r="U30" s="45"/>
     </row>
     <row r="31" ht="13.75" customHeight="1">
       <c r="A31" t="s" s="2">
@@ -5243,51 +5066,47 @@
       <c r="B31" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="C31" s="8"/>
-      <c r="D31" t="s" s="34">
-        <v>69</v>
+      <c r="C31" t="inlineStr" s="34">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr" s="36">
+        <is>
+          <t>Dépôt naturel</t>
+        </is>
       </c>
       <c r="E31" s="37"/>
-      <c r="F31" t="s" s="36">
-        <v>70</v>
-      </c>
-      <c r="G31" s="37"/>
-      <c r="H31" s="37"/>
-      <c r="I31" s="37"/>
-      <c r="J31" t="s" s="39">
+      <c r="F31" t="s" s="39">
         <v>126</v>
       </c>
-      <c r="K31" t="s" s="6">
-        <v>72</v>
-      </c>
-      <c r="L31" t="s" s="2">
-        <v>6</v>
-      </c>
+      <c r="G31" t="s" s="6">
+        <v>72</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J31" s="40">
+        <v>41099</v>
+      </c>
+      <c r="K31" s="44"/>
+      <c r="L31" s="45"/>
       <c r="M31" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="N31" s="40">
-        <v>41099</v>
+        <v>74</v>
+      </c>
+      <c r="N31" s="43">
+        <v>9</v>
       </c>
       <c r="O31" s="44"/>
-      <c r="P31" s="45"/>
-      <c r="Q31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R31" s="43">
-        <v>9</v>
-      </c>
-      <c r="S31" s="44"/>
+      <c r="P31" s="37"/>
+      <c r="Q31" s="37"/>
+      <c r="R31" s="37"/>
+      <c r="S31" s="37"/>
       <c r="T31" s="37"/>
-      <c r="U31" s="37"/>
-      <c r="V31" s="37"/>
-      <c r="W31" s="37"/>
-      <c r="X31" s="37"/>
-      <c r="Y31" s="37"/>
-      <c r="Z31" s="37"/>
-      <c r="AA31" s="37"/>
-      <c r="AB31" s="37"/>
-      <c r="AC31" s="45"/>
+      <c r="U31" s="45"/>
     </row>
     <row r="32" ht="13.75" customHeight="1">
       <c r="A32" t="s" s="2">
@@ -5296,51 +5115,47 @@
       <c r="B32" t="s" s="2">
         <v>144</v>
       </c>
-      <c r="C32" s="8"/>
-      <c r="D32" t="s" s="34">
-        <v>69</v>
+      <c r="C32" t="inlineStr" s="34">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr" s="36">
+        <is>
+          <t>Dépôt naturel</t>
+        </is>
       </c>
       <c r="E32" s="37"/>
-      <c r="F32" t="s" s="36">
-        <v>70</v>
-      </c>
-      <c r="G32" s="37"/>
-      <c r="H32" s="37"/>
-      <c r="I32" s="37"/>
-      <c r="J32" t="s" s="39">
+      <c r="F32" t="s" s="39">
         <v>126</v>
       </c>
-      <c r="K32" t="s" s="6">
-        <v>72</v>
-      </c>
-      <c r="L32" t="s" s="2">
-        <v>6</v>
-      </c>
+      <c r="G32" t="s" s="6">
+        <v>72</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J32" s="40">
+        <v>41099</v>
+      </c>
+      <c r="K32" s="44"/>
+      <c r="L32" s="45"/>
       <c r="M32" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="N32" s="40">
-        <v>41099</v>
+        <v>74</v>
+      </c>
+      <c r="N32" s="43">
+        <v>9</v>
       </c>
       <c r="O32" s="44"/>
-      <c r="P32" s="45"/>
-      <c r="Q32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R32" s="43">
-        <v>9</v>
-      </c>
-      <c r="S32" s="44"/>
+      <c r="P32" s="37"/>
+      <c r="Q32" s="37"/>
+      <c r="R32" s="37"/>
+      <c r="S32" s="37"/>
       <c r="T32" s="37"/>
-      <c r="U32" s="37"/>
-      <c r="V32" s="37"/>
-      <c r="W32" s="37"/>
-      <c r="X32" s="37"/>
-      <c r="Y32" s="37"/>
-      <c r="Z32" s="37"/>
-      <c r="AA32" s="37"/>
-      <c r="AB32" s="37"/>
-      <c r="AC32" s="45"/>
+      <c r="U32" s="45"/>
     </row>
     <row r="33" ht="13.75" customHeight="1">
       <c r="A33" t="s" s="2">
@@ -5349,51 +5164,45 @@
       <c r="B33" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="C33" s="8"/>
-      <c r="D33" t="s" s="34">
-        <v>69</v>
+      <c r="C33" t="inlineStr" s="34">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr" s="36">
+        <is>
+          <t>Dépôt naturel</t>
+        </is>
       </c>
       <c r="E33" s="37"/>
-      <c r="F33" t="s" s="36">
-        <v>70</v>
-      </c>
-      <c r="G33" s="37"/>
-      <c r="H33" s="37"/>
-      <c r="I33" s="37"/>
-      <c r="J33" t="s" s="39">
-        <v>105</v>
-      </c>
-      <c r="K33" t="s" s="6">
-        <v>72</v>
-      </c>
-      <c r="L33" t="s" s="2">
-        <v>6</v>
-      </c>
+      <c r="F33" s="39"/>
+      <c r="G33" t="s" s="6">
+        <v>72</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J33" s="40">
+        <v>41099</v>
+      </c>
+      <c r="K33" s="44"/>
+      <c r="L33" s="45"/>
       <c r="M33" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="N33" s="40">
-        <v>41099</v>
+        <v>74</v>
+      </c>
+      <c r="N33" s="43">
+        <v>9</v>
       </c>
       <c r="O33" s="44"/>
-      <c r="P33" s="45"/>
-      <c r="Q33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R33" s="43">
-        <v>9</v>
-      </c>
-      <c r="S33" s="44"/>
+      <c r="P33" s="37"/>
+      <c r="Q33" s="37"/>
+      <c r="R33" s="37"/>
+      <c r="S33" s="37"/>
       <c r="T33" s="37"/>
-      <c r="U33" s="37"/>
-      <c r="V33" s="37"/>
-      <c r="W33" s="37"/>
-      <c r="X33" s="37"/>
-      <c r="Y33" s="37"/>
-      <c r="Z33" s="37"/>
-      <c r="AA33" s="37"/>
-      <c r="AB33" s="37"/>
-      <c r="AC33" s="45"/>
+      <c r="U33" s="45"/>
     </row>
     <row r="34" ht="13.75" customHeight="1">
       <c r="A34" t="s" s="2">
@@ -5402,51 +5211,47 @@
       <c r="B34" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="C34" s="8"/>
-      <c r="D34" t="s" s="34">
-        <v>69</v>
+      <c r="C34" t="inlineStr" s="34">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr" s="36">
+        <is>
+          <t>Dépôt naturel</t>
+        </is>
       </c>
       <c r="E34" s="37"/>
-      <c r="F34" t="s" s="36">
-        <v>70</v>
-      </c>
-      <c r="G34" s="37"/>
-      <c r="H34" s="37"/>
-      <c r="I34" s="37"/>
-      <c r="J34" t="s" s="39">
+      <c r="F34" t="s" s="39">
         <v>149</v>
       </c>
-      <c r="K34" t="s" s="6">
-        <v>72</v>
-      </c>
-      <c r="L34" t="s" s="2">
-        <v>6</v>
-      </c>
+      <c r="G34" t="s" s="6">
+        <v>72</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J34" s="40">
+        <v>41099</v>
+      </c>
+      <c r="K34" s="44"/>
+      <c r="L34" s="45"/>
       <c r="M34" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="N34" s="40">
-        <v>41099</v>
+        <v>74</v>
+      </c>
+      <c r="N34" s="43">
+        <v>9</v>
       </c>
       <c r="O34" s="44"/>
-      <c r="P34" s="45"/>
-      <c r="Q34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R34" s="43">
-        <v>9</v>
-      </c>
-      <c r="S34" s="44"/>
+      <c r="P34" s="37"/>
+      <c r="Q34" s="37"/>
+      <c r="R34" s="37"/>
+      <c r="S34" s="37"/>
       <c r="T34" s="37"/>
-      <c r="U34" s="37"/>
-      <c r="V34" s="37"/>
-      <c r="W34" s="37"/>
-      <c r="X34" s="37"/>
-      <c r="Y34" s="37"/>
-      <c r="Z34" s="37"/>
-      <c r="AA34" s="37"/>
-      <c r="AB34" s="37"/>
-      <c r="AC34" s="45"/>
+      <c r="U34" s="45"/>
     </row>
     <row r="35" ht="13.75" customHeight="1">
       <c r="A35" t="s" s="2">
@@ -5455,51 +5260,47 @@
       <c r="B35" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="C35" s="8"/>
-      <c r="D35" t="s" s="34">
-        <v>69</v>
+      <c r="C35" t="inlineStr" s="34">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr" s="36">
+        <is>
+          <t>Dépôt naturel</t>
+        </is>
       </c>
       <c r="E35" s="37"/>
-      <c r="F35" t="s" s="36">
-        <v>70</v>
-      </c>
-      <c r="G35" s="37"/>
-      <c r="H35" s="37"/>
-      <c r="I35" s="37"/>
-      <c r="J35" t="s" s="39">
+      <c r="F35" t="s" s="39">
         <v>126</v>
       </c>
-      <c r="K35" t="s" s="6">
-        <v>72</v>
-      </c>
-      <c r="L35" t="s" s="2">
-        <v>6</v>
-      </c>
+      <c r="G35" t="s" s="6">
+        <v>72</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J35" s="40">
+        <v>41099</v>
+      </c>
+      <c r="K35" s="44"/>
+      <c r="L35" s="45"/>
       <c r="M35" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="N35" s="40">
-        <v>41099</v>
+        <v>74</v>
+      </c>
+      <c r="N35" s="43">
+        <v>9</v>
       </c>
       <c r="O35" s="44"/>
-      <c r="P35" s="45"/>
-      <c r="Q35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R35" s="43">
-        <v>9</v>
-      </c>
-      <c r="S35" s="44"/>
+      <c r="P35" s="37"/>
+      <c r="Q35" s="37"/>
+      <c r="R35" s="37"/>
+      <c r="S35" s="37"/>
       <c r="T35" s="37"/>
-      <c r="U35" s="37"/>
-      <c r="V35" s="37"/>
-      <c r="W35" s="37"/>
-      <c r="X35" s="37"/>
-      <c r="Y35" s="37"/>
-      <c r="Z35" s="37"/>
-      <c r="AA35" s="37"/>
-      <c r="AB35" s="37"/>
-      <c r="AC35" s="45"/>
+      <c r="U35" s="45"/>
     </row>
     <row r="36" ht="13.75" customHeight="1">
       <c r="A36" t="s" s="2">
@@ -5508,51 +5309,47 @@
       <c r="B36" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="C36" s="8"/>
-      <c r="D36" t="s" s="34">
-        <v>69</v>
+      <c r="C36" t="inlineStr" s="34">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr" s="36">
+        <is>
+          <t>Dépôt naturel</t>
+        </is>
       </c>
       <c r="E36" s="37"/>
-      <c r="F36" t="s" s="36">
-        <v>70</v>
-      </c>
-      <c r="G36" s="37"/>
-      <c r="H36" s="37"/>
-      <c r="I36" s="37"/>
-      <c r="J36" t="s" s="39">
+      <c r="F36" t="s" s="39">
         <v>149</v>
       </c>
-      <c r="K36" t="s" s="6">
-        <v>72</v>
-      </c>
-      <c r="L36" t="s" s="2">
-        <v>6</v>
-      </c>
+      <c r="G36" t="s" s="6">
+        <v>72</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J36" s="40">
+        <v>41099</v>
+      </c>
+      <c r="K36" s="44"/>
+      <c r="L36" s="45"/>
       <c r="M36" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="N36" s="40">
-        <v>41099</v>
+        <v>74</v>
+      </c>
+      <c r="N36" s="43">
+        <v>9</v>
       </c>
       <c r="O36" s="44"/>
-      <c r="P36" s="45"/>
-      <c r="Q36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R36" s="43">
-        <v>9</v>
-      </c>
-      <c r="S36" s="44"/>
+      <c r="P36" s="37"/>
+      <c r="Q36" s="37"/>
+      <c r="R36" s="37"/>
+      <c r="S36" s="37"/>
       <c r="T36" s="37"/>
-      <c r="U36" s="37"/>
-      <c r="V36" s="37"/>
-      <c r="W36" s="37"/>
-      <c r="X36" s="37"/>
-      <c r="Y36" s="37"/>
-      <c r="Z36" s="37"/>
-      <c r="AA36" s="37"/>
-      <c r="AB36" s="37"/>
-      <c r="AC36" s="45"/>
+      <c r="U36" s="45"/>
     </row>
     <row r="37" ht="13.75" customHeight="1">
       <c r="A37" t="s" s="2">
@@ -5561,51 +5358,47 @@
       <c r="B37" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="C37" s="8"/>
-      <c r="D37" t="s" s="34">
-        <v>69</v>
+      <c r="C37" t="inlineStr" s="34">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr" s="36">
+        <is>
+          <t>Dépôt naturel</t>
+        </is>
       </c>
       <c r="E37" s="37"/>
-      <c r="F37" t="s" s="36">
-        <v>70</v>
-      </c>
-      <c r="G37" s="37"/>
-      <c r="H37" s="37"/>
-      <c r="I37" s="37"/>
-      <c r="J37" t="s" s="39">
+      <c r="F37" t="s" s="39">
         <v>126</v>
       </c>
-      <c r="K37" t="s" s="6">
-        <v>72</v>
-      </c>
-      <c r="L37" t="s" s="2">
-        <v>6</v>
-      </c>
+      <c r="G37" t="s" s="6">
+        <v>72</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J37" s="40">
+        <v>41099</v>
+      </c>
+      <c r="K37" s="44"/>
+      <c r="L37" s="45"/>
       <c r="M37" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="N37" s="40">
-        <v>41099</v>
+        <v>74</v>
+      </c>
+      <c r="N37" s="43">
+        <v>9</v>
       </c>
       <c r="O37" s="44"/>
-      <c r="P37" s="45"/>
-      <c r="Q37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R37" s="43">
-        <v>9</v>
-      </c>
-      <c r="S37" s="44"/>
+      <c r="P37" s="37"/>
+      <c r="Q37" s="37"/>
+      <c r="R37" s="37"/>
+      <c r="S37" s="37"/>
       <c r="T37" s="37"/>
-      <c r="U37" s="37"/>
-      <c r="V37" s="37"/>
-      <c r="W37" s="37"/>
-      <c r="X37" s="37"/>
-      <c r="Y37" s="37"/>
-      <c r="Z37" s="37"/>
-      <c r="AA37" s="37"/>
-      <c r="AB37" s="37"/>
-      <c r="AC37" s="45"/>
+      <c r="U37" s="45"/>
     </row>
     <row r="38" ht="13.75" customHeight="1">
       <c r="A38" t="s" s="2">
@@ -5614,51 +5407,47 @@
       <c r="B38" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="C38" s="8"/>
-      <c r="D38" t="s" s="34">
-        <v>69</v>
+      <c r="C38" t="inlineStr" s="34">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr" s="36">
+        <is>
+          <t>Dépôt naturel</t>
+        </is>
       </c>
       <c r="E38" s="37"/>
-      <c r="F38" t="s" s="36">
-        <v>70</v>
-      </c>
-      <c r="G38" s="37"/>
-      <c r="H38" s="37"/>
-      <c r="I38" s="37"/>
-      <c r="J38" t="s" s="39">
+      <c r="F38" t="s" s="39">
         <v>126</v>
       </c>
-      <c r="K38" t="s" s="6">
-        <v>72</v>
-      </c>
-      <c r="L38" t="s" s="2">
-        <v>6</v>
-      </c>
+      <c r="G38" t="s" s="6">
+        <v>72</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J38" s="40">
+        <v>41099</v>
+      </c>
+      <c r="K38" s="44"/>
+      <c r="L38" s="45"/>
       <c r="M38" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="N38" s="40">
-        <v>41099</v>
+        <v>74</v>
+      </c>
+      <c r="N38" s="43">
+        <v>9</v>
       </c>
       <c r="O38" s="44"/>
-      <c r="P38" s="45"/>
-      <c r="Q38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R38" s="43">
-        <v>9</v>
-      </c>
-      <c r="S38" s="44"/>
+      <c r="P38" s="37"/>
+      <c r="Q38" s="37"/>
+      <c r="R38" s="37"/>
+      <c r="S38" s="37"/>
       <c r="T38" s="37"/>
-      <c r="U38" s="37"/>
-      <c r="V38" s="37"/>
-      <c r="W38" s="37"/>
-      <c r="X38" s="37"/>
-      <c r="Y38" s="37"/>
-      <c r="Z38" s="37"/>
-      <c r="AA38" s="37"/>
-      <c r="AB38" s="37"/>
-      <c r="AC38" s="45"/>
+      <c r="U38" s="45"/>
     </row>
     <row r="39" ht="13.75" customHeight="1">
       <c r="A39" t="s" s="2">
@@ -5667,51 +5456,47 @@
       <c r="B39" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="C39" s="8"/>
-      <c r="D39" t="s" s="34">
-        <v>69</v>
+      <c r="C39" t="inlineStr" s="34">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr" s="36">
+        <is>
+          <t>Dépôt naturel</t>
+        </is>
       </c>
       <c r="E39" s="37"/>
-      <c r="F39" t="s" s="36">
-        <v>70</v>
-      </c>
-      <c r="G39" s="37"/>
-      <c r="H39" s="37"/>
-      <c r="I39" s="37"/>
-      <c r="J39" t="s" s="39">
+      <c r="F39" t="s" s="39">
         <v>149</v>
       </c>
-      <c r="K39" t="s" s="6">
-        <v>72</v>
-      </c>
-      <c r="L39" t="s" s="2">
-        <v>6</v>
-      </c>
+      <c r="G39" t="s" s="6">
+        <v>72</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J39" s="40">
+        <v>41099</v>
+      </c>
+      <c r="K39" s="44"/>
+      <c r="L39" s="45"/>
       <c r="M39" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="N39" s="40">
-        <v>41099</v>
+        <v>74</v>
+      </c>
+      <c r="N39" s="43">
+        <v>9</v>
       </c>
       <c r="O39" s="44"/>
-      <c r="P39" s="45"/>
-      <c r="Q39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R39" s="43">
-        <v>9</v>
-      </c>
-      <c r="S39" s="44"/>
+      <c r="P39" s="37"/>
+      <c r="Q39" s="37"/>
+      <c r="R39" s="37"/>
+      <c r="S39" s="37"/>
       <c r="T39" s="37"/>
-      <c r="U39" s="37"/>
-      <c r="V39" s="37"/>
-      <c r="W39" s="37"/>
-      <c r="X39" s="37"/>
-      <c r="Y39" s="37"/>
-      <c r="Z39" s="37"/>
-      <c r="AA39" s="37"/>
-      <c r="AB39" s="37"/>
-      <c r="AC39" s="45"/>
+      <c r="U39" s="45"/>
     </row>
     <row r="40" ht="13.75" customHeight="1">
       <c r="A40" t="s" s="2">
@@ -5720,51 +5505,47 @@
       <c r="B40" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="C40" s="8"/>
-      <c r="D40" t="s" s="34">
-        <v>69</v>
+      <c r="C40" t="inlineStr" s="34">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr" s="36">
+        <is>
+          <t>Dépôt naturel</t>
+        </is>
       </c>
       <c r="E40" s="37"/>
-      <c r="F40" t="s" s="36">
-        <v>70</v>
-      </c>
-      <c r="G40" s="37"/>
-      <c r="H40" s="37"/>
-      <c r="I40" s="37"/>
-      <c r="J40" t="s" s="39">
+      <c r="F40" t="s" s="39">
         <v>126</v>
       </c>
-      <c r="K40" t="s" s="6">
-        <v>72</v>
-      </c>
-      <c r="L40" t="s" s="2">
-        <v>6</v>
-      </c>
+      <c r="G40" t="s" s="6">
+        <v>72</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J40" s="40">
+        <v>41099</v>
+      </c>
+      <c r="K40" s="44"/>
+      <c r="L40" s="45"/>
       <c r="M40" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="N40" s="40">
-        <v>41099</v>
+        <v>74</v>
+      </c>
+      <c r="N40" s="43">
+        <v>9</v>
       </c>
       <c r="O40" s="44"/>
-      <c r="P40" s="45"/>
-      <c r="Q40" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R40" s="43">
-        <v>9</v>
-      </c>
-      <c r="S40" s="44"/>
+      <c r="P40" s="37"/>
+      <c r="Q40" s="37"/>
+      <c r="R40" s="37"/>
+      <c r="S40" s="37"/>
       <c r="T40" s="37"/>
-      <c r="U40" s="37"/>
-      <c r="V40" s="37"/>
-      <c r="W40" s="37"/>
-      <c r="X40" s="37"/>
-      <c r="Y40" s="37"/>
-      <c r="Z40" s="37"/>
-      <c r="AA40" s="37"/>
-      <c r="AB40" s="37"/>
-      <c r="AC40" s="45"/>
+      <c r="U40" s="45"/>
     </row>
     <row r="41" ht="13.75" customHeight="1">
       <c r="A41" t="s" s="2">
@@ -5773,51 +5554,47 @@
       <c r="B41" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="C41" s="8"/>
-      <c r="D41" t="s" s="34">
-        <v>69</v>
+      <c r="C41" t="inlineStr" s="34">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr" s="36">
+        <is>
+          <t>Dépôt naturel</t>
+        </is>
       </c>
       <c r="E41" s="37"/>
-      <c r="F41" t="s" s="36">
-        <v>70</v>
-      </c>
-      <c r="G41" s="37"/>
-      <c r="H41" s="37"/>
-      <c r="I41" s="37"/>
-      <c r="J41" t="s" s="39">
+      <c r="F41" t="s" s="39">
         <v>108</v>
       </c>
-      <c r="K41" t="s" s="6">
-        <v>72</v>
-      </c>
-      <c r="L41" t="s" s="2">
-        <v>6</v>
-      </c>
+      <c r="G41" t="s" s="6">
+        <v>72</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J41" s="40">
+        <v>41099</v>
+      </c>
+      <c r="K41" s="44"/>
+      <c r="L41" s="45"/>
       <c r="M41" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="N41" s="40">
-        <v>41099</v>
+        <v>74</v>
+      </c>
+      <c r="N41" s="43">
+        <v>9</v>
       </c>
       <c r="O41" s="44"/>
-      <c r="P41" s="45"/>
-      <c r="Q41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R41" s="43">
-        <v>9</v>
-      </c>
-      <c r="S41" s="44"/>
+      <c r="P41" s="37"/>
+      <c r="Q41" s="37"/>
+      <c r="R41" s="37"/>
+      <c r="S41" s="37"/>
       <c r="T41" s="37"/>
-      <c r="U41" s="37"/>
-      <c r="V41" s="37"/>
-      <c r="W41" s="37"/>
-      <c r="X41" s="37"/>
-      <c r="Y41" s="37"/>
-      <c r="Z41" s="37"/>
-      <c r="AA41" s="37"/>
-      <c r="AB41" s="37"/>
-      <c r="AC41" s="45"/>
+      <c r="U41" s="45"/>
     </row>
     <row r="42" ht="13.75" customHeight="1">
       <c r="A42" t="s" s="2">
@@ -5826,51 +5603,47 @@
       <c r="B42" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="C42" s="8"/>
-      <c r="D42" t="s" s="34">
-        <v>69</v>
+      <c r="C42" t="inlineStr" s="34">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr" s="36">
+        <is>
+          <t>Dépôt naturel</t>
+        </is>
       </c>
       <c r="E42" s="37"/>
-      <c r="F42" t="s" s="36">
-        <v>70</v>
-      </c>
-      <c r="G42" s="37"/>
-      <c r="H42" s="37"/>
-      <c r="I42" s="37"/>
-      <c r="J42" t="s" s="39">
+      <c r="F42" t="s" s="39">
         <v>126</v>
       </c>
-      <c r="K42" t="s" s="6">
-        <v>72</v>
-      </c>
-      <c r="L42" t="s" s="2">
-        <v>6</v>
-      </c>
+      <c r="G42" t="s" s="6">
+        <v>72</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J42" s="40">
+        <v>41100</v>
+      </c>
+      <c r="K42" s="44"/>
+      <c r="L42" s="45"/>
       <c r="M42" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="N42" s="40">
-        <v>41100</v>
+        <v>74</v>
+      </c>
+      <c r="N42" s="43">
+        <v>9</v>
       </c>
       <c r="O42" s="44"/>
-      <c r="P42" s="45"/>
-      <c r="Q42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R42" s="43">
-        <v>9</v>
-      </c>
-      <c r="S42" s="44"/>
+      <c r="P42" s="37"/>
+      <c r="Q42" s="37"/>
+      <c r="R42" s="37"/>
+      <c r="S42" s="37"/>
       <c r="T42" s="37"/>
-      <c r="U42" s="37"/>
-      <c r="V42" s="37"/>
-      <c r="W42" s="37"/>
-      <c r="X42" s="37"/>
-      <c r="Y42" s="37"/>
-      <c r="Z42" s="37"/>
-      <c r="AA42" s="37"/>
-      <c r="AB42" s="37"/>
-      <c r="AC42" s="45"/>
+      <c r="U42" s="45"/>
     </row>
     <row r="43" ht="13.75" customHeight="1">
       <c r="A43" t="s" s="2">
@@ -5879,51 +5652,47 @@
       <c r="B43" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="C43" s="8"/>
-      <c r="D43" t="s" s="34">
-        <v>69</v>
+      <c r="C43" t="inlineStr" s="34">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr" s="36">
+        <is>
+          <t>Dépôt naturel</t>
+        </is>
       </c>
       <c r="E43" s="37"/>
-      <c r="F43" t="s" s="36">
-        <v>70</v>
-      </c>
-      <c r="G43" s="37"/>
-      <c r="H43" s="37"/>
-      <c r="I43" s="37"/>
-      <c r="J43" t="s" s="39">
+      <c r="F43" t="s" s="39">
         <v>84</v>
       </c>
-      <c r="K43" t="s" s="6">
-        <v>72</v>
-      </c>
-      <c r="L43" t="s" s="2">
-        <v>6</v>
-      </c>
+      <c r="G43" t="s" s="6">
+        <v>72</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J43" s="40">
+        <v>41100</v>
+      </c>
+      <c r="K43" s="44"/>
+      <c r="L43" s="45"/>
       <c r="M43" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="N43" s="40">
-        <v>41100</v>
+        <v>74</v>
+      </c>
+      <c r="N43" s="43">
+        <v>9</v>
       </c>
       <c r="O43" s="44"/>
-      <c r="P43" s="45"/>
-      <c r="Q43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R43" s="43">
-        <v>9</v>
-      </c>
-      <c r="S43" s="44"/>
+      <c r="P43" s="37"/>
+      <c r="Q43" s="37"/>
+      <c r="R43" s="37"/>
+      <c r="S43" s="37"/>
       <c r="T43" s="37"/>
-      <c r="U43" s="37"/>
-      <c r="V43" s="37"/>
-      <c r="W43" s="37"/>
-      <c r="X43" s="37"/>
-      <c r="Y43" s="37"/>
-      <c r="Z43" s="37"/>
-      <c r="AA43" s="37"/>
-      <c r="AB43" s="37"/>
-      <c r="AC43" s="45"/>
+      <c r="U43" s="45"/>
     </row>
     <row r="44" ht="13.75" customHeight="1">
       <c r="A44" t="s" s="2">
@@ -5932,51 +5701,47 @@
       <c r="B44" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="C44" s="8"/>
-      <c r="D44" t="s" s="34">
-        <v>69</v>
+      <c r="C44" t="inlineStr" s="34">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr" s="36">
+        <is>
+          <t>Dépôt naturel</t>
+        </is>
       </c>
       <c r="E44" s="37"/>
-      <c r="F44" t="s" s="36">
-        <v>70</v>
-      </c>
-      <c r="G44" s="37"/>
-      <c r="H44" s="37"/>
-      <c r="I44" s="37"/>
-      <c r="J44" t="s" s="39">
+      <c r="F44" t="s" s="39">
         <v>88</v>
       </c>
-      <c r="K44" t="s" s="6">
-        <v>72</v>
-      </c>
-      <c r="L44" t="s" s="2">
-        <v>6</v>
-      </c>
+      <c r="G44" t="s" s="6">
+        <v>72</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J44" s="40">
+        <v>41100</v>
+      </c>
+      <c r="K44" s="44"/>
+      <c r="L44" s="45"/>
       <c r="M44" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="N44" s="40">
-        <v>41100</v>
+        <v>74</v>
+      </c>
+      <c r="N44" s="43">
+        <v>3</v>
       </c>
       <c r="O44" s="44"/>
-      <c r="P44" s="45"/>
-      <c r="Q44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R44" s="43">
-        <v>3</v>
-      </c>
-      <c r="S44" s="44"/>
+      <c r="P44" s="37"/>
+      <c r="Q44" s="37"/>
+      <c r="R44" s="37"/>
+      <c r="S44" s="37"/>
       <c r="T44" s="37"/>
-      <c r="U44" s="37"/>
-      <c r="V44" s="37"/>
-      <c r="W44" s="37"/>
-      <c r="X44" s="37"/>
-      <c r="Y44" s="37"/>
-      <c r="Z44" s="37"/>
-      <c r="AA44" s="37"/>
-      <c r="AB44" s="37"/>
-      <c r="AC44" s="45"/>
+      <c r="U44" s="45"/>
     </row>
     <row r="45" ht="13.75" customHeight="1">
       <c r="A45" t="s" s="2">
@@ -5985,51 +5750,47 @@
       <c r="B45" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="C45" s="8"/>
-      <c r="D45" t="s" s="34">
-        <v>69</v>
+      <c r="C45" t="inlineStr" s="34">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr" s="36">
+        <is>
+          <t>Dépôt naturel</t>
+        </is>
       </c>
       <c r="E45" s="37"/>
-      <c r="F45" t="s" s="36">
-        <v>70</v>
-      </c>
-      <c r="G45" s="37"/>
-      <c r="H45" s="37"/>
-      <c r="I45" s="37"/>
-      <c r="J45" t="s" s="39">
+      <c r="F45" t="s" s="39">
         <v>126</v>
       </c>
-      <c r="K45" t="s" s="6">
-        <v>72</v>
-      </c>
-      <c r="L45" t="s" s="2">
-        <v>6</v>
-      </c>
+      <c r="G45" t="s" s="6">
+        <v>72</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J45" s="40">
+        <v>41100</v>
+      </c>
+      <c r="K45" s="44"/>
+      <c r="L45" s="45"/>
       <c r="M45" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="N45" s="40">
-        <v>41100</v>
+        <v>74</v>
+      </c>
+      <c r="N45" s="43">
+        <v>9</v>
       </c>
       <c r="O45" s="44"/>
-      <c r="P45" s="45"/>
-      <c r="Q45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R45" s="43">
-        <v>9</v>
-      </c>
-      <c r="S45" s="44"/>
+      <c r="P45" s="37"/>
+      <c r="Q45" s="37"/>
+      <c r="R45" s="37"/>
+      <c r="S45" s="37"/>
       <c r="T45" s="37"/>
-      <c r="U45" s="37"/>
-      <c r="V45" s="37"/>
-      <c r="W45" s="37"/>
-      <c r="X45" s="37"/>
-      <c r="Y45" s="37"/>
-      <c r="Z45" s="37"/>
-      <c r="AA45" s="37"/>
-      <c r="AB45" s="37"/>
-      <c r="AC45" s="45"/>
+      <c r="U45" s="45"/>
     </row>
     <row r="46" ht="13.75" customHeight="1">
       <c r="A46" t="s" s="2">
@@ -6038,51 +5799,47 @@
       <c r="B46" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="C46" s="8"/>
-      <c r="D46" t="s" s="34">
-        <v>69</v>
+      <c r="C46" t="inlineStr" s="34">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr" s="36">
+        <is>
+          <t>Dépôt naturel</t>
+        </is>
       </c>
       <c r="E46" s="37"/>
-      <c r="F46" t="s" s="36">
-        <v>70</v>
-      </c>
-      <c r="G46" s="37"/>
-      <c r="H46" s="37"/>
-      <c r="I46" s="37"/>
-      <c r="J46" t="s" s="39">
+      <c r="F46" t="s" s="39">
         <v>126</v>
       </c>
-      <c r="K46" t="s" s="6">
-        <v>72</v>
-      </c>
-      <c r="L46" t="s" s="2">
-        <v>6</v>
-      </c>
+      <c r="G46" t="s" s="6">
+        <v>72</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J46" s="40">
+        <v>41100</v>
+      </c>
+      <c r="K46" s="44"/>
+      <c r="L46" s="45"/>
       <c r="M46" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="N46" s="40">
-        <v>41100</v>
+        <v>74</v>
+      </c>
+      <c r="N46" s="43">
+        <v>6</v>
       </c>
       <c r="O46" s="44"/>
-      <c r="P46" s="45"/>
-      <c r="Q46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R46" s="43">
-        <v>6</v>
-      </c>
-      <c r="S46" s="44"/>
+      <c r="P46" s="37"/>
+      <c r="Q46" s="37"/>
+      <c r="R46" s="37"/>
+      <c r="S46" s="37"/>
       <c r="T46" s="37"/>
-      <c r="U46" s="37"/>
-      <c r="V46" s="37"/>
-      <c r="W46" s="37"/>
-      <c r="X46" s="37"/>
-      <c r="Y46" s="37"/>
-      <c r="Z46" s="37"/>
-      <c r="AA46" s="37"/>
-      <c r="AB46" s="37"/>
-      <c r="AC46" s="45"/>
+      <c r="U46" s="45"/>
     </row>
     <row r="47" ht="13.75" customHeight="1">
       <c r="A47" t="s" s="2">
@@ -6091,51 +5848,45 @@
       <c r="B47" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="C47" s="8"/>
-      <c r="D47" t="s" s="34">
-        <v>69</v>
+      <c r="C47" t="inlineStr" s="34">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr" s="36">
+        <is>
+          <t>Négative</t>
+        </is>
       </c>
       <c r="E47" s="37"/>
-      <c r="F47" t="s" s="36">
-        <v>104</v>
-      </c>
-      <c r="G47" s="37"/>
-      <c r="H47" s="37"/>
-      <c r="I47" s="37"/>
-      <c r="J47" t="s" s="39">
-        <v>105</v>
-      </c>
-      <c r="K47" t="s" s="6">
-        <v>72</v>
-      </c>
-      <c r="L47" t="s" s="2">
-        <v>6</v>
-      </c>
+      <c r="F47" s="39"/>
+      <c r="G47" t="s" s="6">
+        <v>72</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J47" s="40">
+        <v>41100</v>
+      </c>
+      <c r="K47" s="44"/>
+      <c r="L47" s="45"/>
       <c r="M47" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="N47" s="40">
-        <v>41100</v>
+        <v>74</v>
+      </c>
+      <c r="N47" s="43">
+        <v>6</v>
       </c>
       <c r="O47" s="44"/>
-      <c r="P47" s="45"/>
-      <c r="Q47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R47" s="43">
-        <v>6</v>
-      </c>
-      <c r="S47" s="44"/>
+      <c r="P47" s="37"/>
+      <c r="Q47" s="37"/>
+      <c r="R47" s="37"/>
+      <c r="S47" s="37"/>
       <c r="T47" s="37"/>
-      <c r="U47" s="37"/>
-      <c r="V47" s="37"/>
-      <c r="W47" s="37"/>
-      <c r="X47" s="37"/>
-      <c r="Y47" s="37"/>
-      <c r="Z47" s="37"/>
-      <c r="AA47" s="37"/>
-      <c r="AB47" s="37"/>
-      <c r="AC47" s="45"/>
+      <c r="U47" s="45"/>
     </row>
     <row r="48" ht="13.75" customHeight="1">
       <c r="A48" t="s" s="46">
@@ -6144,1427 +5895,1231 @@
       <c r="B48" t="s" s="46">
         <v>177</v>
       </c>
-      <c r="C48" s="8"/>
-      <c r="D48" t="s" s="34">
-        <v>69</v>
+      <c r="C48" t="inlineStr" s="34">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr" s="36">
+        <is>
+          <t>Dépôt naturel</t>
+        </is>
       </c>
       <c r="E48" s="37"/>
-      <c r="F48" t="s" s="36">
-        <v>70</v>
-      </c>
-      <c r="G48" s="37"/>
-      <c r="H48" s="37"/>
-      <c r="I48" s="37"/>
-      <c r="J48" t="s" s="39">
+      <c r="F48" t="s" s="39">
         <v>108</v>
       </c>
-      <c r="K48" t="s" s="6">
-        <v>72</v>
-      </c>
-      <c r="L48" t="s" s="2">
-        <v>6</v>
-      </c>
+      <c r="G48" t="s" s="6">
+        <v>72</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J48" s="40">
+        <v>41081</v>
+      </c>
+      <c r="K48" s="44"/>
+      <c r="L48" s="45"/>
       <c r="M48" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="N48" s="40">
-        <v>41081</v>
+        <v>74</v>
+      </c>
+      <c r="N48" s="43">
+        <v>8</v>
       </c>
       <c r="O48" s="44"/>
-      <c r="P48" s="45"/>
-      <c r="Q48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R48" s="43">
-        <v>8</v>
-      </c>
-      <c r="S48" s="44"/>
+      <c r="P48" s="37"/>
+      <c r="Q48" s="37"/>
+      <c r="R48" s="37"/>
+      <c r="S48" s="37"/>
       <c r="T48" s="37"/>
-      <c r="U48" s="37"/>
-      <c r="V48" s="37"/>
-      <c r="W48" s="37"/>
-      <c r="X48" s="37"/>
-      <c r="Y48" s="37"/>
-      <c r="Z48" s="37"/>
-      <c r="AA48" s="37"/>
-      <c r="AB48" s="37"/>
-      <c r="AC48" s="45"/>
+      <c r="U48" s="45"/>
     </row>
     <row r="49" ht="14.7" customHeight="1">
       <c r="A49" t="s" s="47">
         <v>178</v>
       </c>
       <c r="B49" s="48"/>
-      <c r="C49" s="45"/>
-      <c r="D49" t="s" s="34">
-        <v>179</v>
-      </c>
+      <c r="C49" t="inlineStr" s="34">
+        <is>
+          <t>Tranchée</t>
+        </is>
+      </c>
+      <c r="D49" s="37"/>
       <c r="E49" s="37"/>
-      <c r="F49" s="37"/>
-      <c r="G49" s="37"/>
-      <c r="H49" s="37"/>
-      <c r="I49" s="37"/>
-      <c r="J49" s="45"/>
-      <c r="K49" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="L49" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="M49" s="3"/>
-      <c r="N49" s="40">
+      <c r="F49" s="45"/>
+      <c r="G49" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I49" s="3"/>
+      <c r="J49" s="40">
         <v>41081</v>
       </c>
-      <c r="O49" s="44"/>
-      <c r="P49" s="45"/>
-      <c r="Q49" t="s" s="2">
+      <c r="K49" s="44"/>
+      <c r="L49" s="45"/>
+      <c r="M49" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="R49" s="44"/>
+      <c r="N49" s="44"/>
+      <c r="O49" s="37"/>
+      <c r="P49" s="37"/>
+      <c r="Q49" s="37"/>
+      <c r="R49" s="37"/>
       <c r="S49" s="37"/>
       <c r="T49" s="37"/>
-      <c r="U49" s="37"/>
-      <c r="V49" s="37"/>
-      <c r="W49" s="37"/>
-      <c r="X49" s="37"/>
-      <c r="Y49" s="37"/>
-      <c r="Z49" s="37"/>
-      <c r="AA49" s="37"/>
-      <c r="AB49" s="37"/>
-      <c r="AC49" s="45"/>
+      <c r="U49" s="45"/>
     </row>
     <row r="50" ht="14.7" customHeight="1">
       <c r="A50" t="s" s="47">
         <v>180</v>
       </c>
       <c r="B50" s="49"/>
-      <c r="C50" s="45"/>
-      <c r="D50" t="s" s="34">
-        <v>179</v>
-      </c>
+      <c r="C50" t="inlineStr" s="34">
+        <is>
+          <t>Tranchée</t>
+        </is>
+      </c>
+      <c r="D50" s="37"/>
       <c r="E50" s="37"/>
-      <c r="F50" s="37"/>
-      <c r="G50" s="37"/>
-      <c r="H50" s="37"/>
-      <c r="I50" s="37"/>
-      <c r="J50" s="45"/>
-      <c r="K50" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="L50" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="M50" s="8"/>
-      <c r="N50" s="40">
+      <c r="F50" s="45"/>
+      <c r="G50" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I50" s="8"/>
+      <c r="J50" s="40">
         <v>41081</v>
       </c>
-      <c r="O50" s="44"/>
-      <c r="P50" s="45"/>
-      <c r="Q50" t="s" s="2">
+      <c r="K50" s="44"/>
+      <c r="L50" s="45"/>
+      <c r="M50" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="R50" s="44"/>
+      <c r="N50" s="44"/>
+      <c r="O50" s="37"/>
+      <c r="P50" s="37"/>
+      <c r="Q50" s="37"/>
+      <c r="R50" s="37"/>
       <c r="S50" s="37"/>
       <c r="T50" s="37"/>
-      <c r="U50" s="37"/>
-      <c r="V50" s="37"/>
-      <c r="W50" s="37"/>
-      <c r="X50" s="37"/>
-      <c r="Y50" s="37"/>
-      <c r="Z50" s="37"/>
-      <c r="AA50" s="37"/>
-      <c r="AB50" s="37"/>
-      <c r="AC50" s="45"/>
+      <c r="U50" s="45"/>
     </row>
     <row r="51" ht="14.7" customHeight="1">
       <c r="A51" t="s" s="47">
         <v>181</v>
       </c>
       <c r="B51" s="49"/>
-      <c r="C51" s="45"/>
-      <c r="D51" t="s" s="34">
-        <v>179</v>
-      </c>
+      <c r="C51" t="inlineStr" s="34">
+        <is>
+          <t>Tranchée</t>
+        </is>
+      </c>
+      <c r="D51" s="37"/>
       <c r="E51" s="37"/>
-      <c r="F51" s="37"/>
-      <c r="G51" s="37"/>
-      <c r="H51" s="37"/>
-      <c r="I51" s="37"/>
-      <c r="J51" s="45"/>
-      <c r="K51" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="M51" s="8"/>
-      <c r="N51" s="40">
+      <c r="F51" s="45"/>
+      <c r="G51" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I51" s="8"/>
+      <c r="J51" s="40">
         <v>41081</v>
       </c>
-      <c r="O51" s="44"/>
-      <c r="P51" s="45"/>
-      <c r="Q51" t="s" s="2">
+      <c r="K51" s="44"/>
+      <c r="L51" s="45"/>
+      <c r="M51" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="R51" s="44"/>
+      <c r="N51" s="44"/>
+      <c r="O51" s="37"/>
+      <c r="P51" s="37"/>
+      <c r="Q51" s="37"/>
+      <c r="R51" s="37"/>
       <c r="S51" s="37"/>
       <c r="T51" s="37"/>
-      <c r="U51" s="37"/>
-      <c r="V51" s="37"/>
-      <c r="W51" s="37"/>
-      <c r="X51" s="37"/>
-      <c r="Y51" s="37"/>
-      <c r="Z51" s="37"/>
-      <c r="AA51" s="37"/>
-      <c r="AB51" s="37"/>
-      <c r="AC51" s="45"/>
+      <c r="U51" s="45"/>
     </row>
     <row r="52" ht="14.7" customHeight="1">
       <c r="A52" t="s" s="47">
         <v>182</v>
       </c>
       <c r="B52" s="49"/>
-      <c r="C52" s="45"/>
-      <c r="D52" t="s" s="34">
-        <v>179</v>
-      </c>
+      <c r="C52" t="inlineStr" s="34">
+        <is>
+          <t>Tranchée</t>
+        </is>
+      </c>
+      <c r="D52" s="37"/>
       <c r="E52" s="37"/>
-      <c r="F52" s="37"/>
-      <c r="G52" s="37"/>
-      <c r="H52" s="37"/>
-      <c r="I52" s="37"/>
-      <c r="J52" s="45"/>
-      <c r="K52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="L52" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="M52" s="8"/>
-      <c r="N52" s="40">
+      <c r="F52" s="45"/>
+      <c r="G52" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I52" s="8"/>
+      <c r="J52" s="40">
         <v>41081</v>
       </c>
-      <c r="O52" s="44"/>
-      <c r="P52" s="45"/>
-      <c r="Q52" t="s" s="2">
+      <c r="K52" s="44"/>
+      <c r="L52" s="45"/>
+      <c r="M52" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="R52" s="44"/>
+      <c r="N52" s="44"/>
+      <c r="O52" s="37"/>
+      <c r="P52" s="37"/>
+      <c r="Q52" s="37"/>
+      <c r="R52" s="37"/>
       <c r="S52" s="37"/>
       <c r="T52" s="37"/>
-      <c r="U52" s="37"/>
-      <c r="V52" s="37"/>
-      <c r="W52" s="37"/>
-      <c r="X52" s="37"/>
-      <c r="Y52" s="37"/>
-      <c r="Z52" s="37"/>
-      <c r="AA52" s="37"/>
-      <c r="AB52" s="37"/>
-      <c r="AC52" s="45"/>
+      <c r="U52" s="45"/>
     </row>
     <row r="53" ht="14.7" customHeight="1">
       <c r="A53" t="s" s="47">
         <v>183</v>
       </c>
       <c r="B53" s="49"/>
-      <c r="C53" s="45"/>
-      <c r="D53" t="s" s="34">
-        <v>179</v>
-      </c>
+      <c r="C53" t="inlineStr" s="34">
+        <is>
+          <t>Tranchée</t>
+        </is>
+      </c>
+      <c r="D53" s="37"/>
       <c r="E53" s="37"/>
-      <c r="F53" s="37"/>
-      <c r="G53" s="37"/>
-      <c r="H53" s="37"/>
-      <c r="I53" s="37"/>
-      <c r="J53" s="45"/>
-      <c r="K53" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="L53" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="M53" s="8"/>
-      <c r="N53" s="40">
+      <c r="F53" s="45"/>
+      <c r="G53" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I53" s="8"/>
+      <c r="J53" s="40">
         <v>41081</v>
       </c>
-      <c r="O53" s="44"/>
-      <c r="P53" s="45"/>
-      <c r="Q53" t="s" s="2">
+      <c r="K53" s="44"/>
+      <c r="L53" s="45"/>
+      <c r="M53" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="R53" s="44"/>
+      <c r="N53" s="44"/>
+      <c r="O53" s="37"/>
+      <c r="P53" s="37"/>
+      <c r="Q53" s="37"/>
+      <c r="R53" s="37"/>
       <c r="S53" s="37"/>
       <c r="T53" s="37"/>
-      <c r="U53" s="37"/>
-      <c r="V53" s="37"/>
-      <c r="W53" s="37"/>
-      <c r="X53" s="37"/>
-      <c r="Y53" s="37"/>
-      <c r="Z53" s="37"/>
-      <c r="AA53" s="37"/>
-      <c r="AB53" s="37"/>
-      <c r="AC53" s="45"/>
+      <c r="U53" s="45"/>
     </row>
     <row r="54" ht="14.7" customHeight="1">
       <c r="A54" t="s" s="47">
         <v>184</v>
       </c>
       <c r="B54" s="49"/>
-      <c r="C54" s="45"/>
-      <c r="D54" t="s" s="34">
-        <v>179</v>
-      </c>
+      <c r="C54" t="inlineStr" s="34">
+        <is>
+          <t>Tranchée</t>
+        </is>
+      </c>
+      <c r="D54" s="37"/>
       <c r="E54" s="37"/>
-      <c r="F54" s="37"/>
-      <c r="G54" s="37"/>
-      <c r="H54" s="37"/>
-      <c r="I54" s="37"/>
-      <c r="J54" s="45"/>
-      <c r="K54" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="L54" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="M54" s="8"/>
-      <c r="N54" s="40">
+      <c r="F54" s="45"/>
+      <c r="G54" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I54" s="8"/>
+      <c r="J54" s="40">
         <v>41081</v>
       </c>
-      <c r="O54" s="44"/>
-      <c r="P54" s="45"/>
-      <c r="Q54" t="s" s="2">
+      <c r="K54" s="44"/>
+      <c r="L54" s="45"/>
+      <c r="M54" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="R54" s="44"/>
+      <c r="N54" s="44"/>
+      <c r="O54" s="37"/>
+      <c r="P54" s="37"/>
+      <c r="Q54" s="37"/>
+      <c r="R54" s="37"/>
       <c r="S54" s="37"/>
       <c r="T54" s="37"/>
-      <c r="U54" s="37"/>
-      <c r="V54" s="37"/>
-      <c r="W54" s="37"/>
-      <c r="X54" s="37"/>
-      <c r="Y54" s="37"/>
-      <c r="Z54" s="37"/>
-      <c r="AA54" s="37"/>
-      <c r="AB54" s="37"/>
-      <c r="AC54" s="45"/>
+      <c r="U54" s="45"/>
     </row>
     <row r="55" ht="14.7" customHeight="1">
       <c r="A55" t="s" s="47">
         <v>185</v>
       </c>
       <c r="B55" s="49"/>
-      <c r="C55" s="45"/>
-      <c r="D55" t="s" s="34">
-        <v>179</v>
-      </c>
+      <c r="C55" t="inlineStr" s="34">
+        <is>
+          <t>Tranchée</t>
+        </is>
+      </c>
+      <c r="D55" s="37"/>
       <c r="E55" s="37"/>
-      <c r="F55" s="37"/>
-      <c r="G55" s="37"/>
-      <c r="H55" s="37"/>
-      <c r="I55" s="37"/>
-      <c r="J55" s="45"/>
-      <c r="K55" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="L55" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="M55" s="8"/>
-      <c r="N55" s="40">
+      <c r="F55" s="45"/>
+      <c r="G55" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I55" s="8"/>
+      <c r="J55" s="40">
         <v>41081</v>
       </c>
-      <c r="O55" s="44"/>
-      <c r="P55" s="45"/>
-      <c r="Q55" t="s" s="2">
+      <c r="K55" s="44"/>
+      <c r="L55" s="45"/>
+      <c r="M55" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="R55" s="44"/>
+      <c r="N55" s="44"/>
+      <c r="O55" s="37"/>
+      <c r="P55" s="37"/>
+      <c r="Q55" s="37"/>
+      <c r="R55" s="37"/>
       <c r="S55" s="37"/>
       <c r="T55" s="37"/>
-      <c r="U55" s="37"/>
-      <c r="V55" s="37"/>
-      <c r="W55" s="37"/>
-      <c r="X55" s="37"/>
-      <c r="Y55" s="37"/>
-      <c r="Z55" s="37"/>
-      <c r="AA55" s="37"/>
-      <c r="AB55" s="37"/>
-      <c r="AC55" s="45"/>
+      <c r="U55" s="45"/>
     </row>
     <row r="56" ht="14.7" customHeight="1">
       <c r="A56" t="s" s="47">
         <v>186</v>
       </c>
       <c r="B56" s="49"/>
-      <c r="C56" s="45"/>
-      <c r="D56" t="s" s="34">
-        <v>179</v>
-      </c>
+      <c r="C56" t="inlineStr" s="34">
+        <is>
+          <t>Tranchée</t>
+        </is>
+      </c>
+      <c r="D56" s="37"/>
       <c r="E56" s="37"/>
-      <c r="F56" s="37"/>
-      <c r="G56" s="37"/>
-      <c r="H56" s="37"/>
-      <c r="I56" s="37"/>
-      <c r="J56" s="45"/>
-      <c r="K56" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="L56" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="M56" s="8"/>
-      <c r="N56" s="40">
+      <c r="F56" s="45"/>
+      <c r="G56" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I56" s="8"/>
+      <c r="J56" s="40">
         <v>41081</v>
       </c>
-      <c r="O56" s="44"/>
-      <c r="P56" s="45"/>
-      <c r="Q56" t="s" s="2">
+      <c r="K56" s="44"/>
+      <c r="L56" s="45"/>
+      <c r="M56" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="R56" s="44"/>
+      <c r="N56" s="44"/>
+      <c r="O56" s="37"/>
+      <c r="P56" s="37"/>
+      <c r="Q56" s="37"/>
+      <c r="R56" s="37"/>
       <c r="S56" s="37"/>
       <c r="T56" s="37"/>
-      <c r="U56" s="37"/>
-      <c r="V56" s="37"/>
-      <c r="W56" s="37"/>
-      <c r="X56" s="37"/>
-      <c r="Y56" s="37"/>
-      <c r="Z56" s="37"/>
-      <c r="AA56" s="37"/>
-      <c r="AB56" s="37"/>
-      <c r="AC56" s="45"/>
+      <c r="U56" s="45"/>
     </row>
     <row r="57" ht="14.7" customHeight="1">
       <c r="A57" t="s" s="47">
         <v>187</v>
       </c>
       <c r="B57" s="49"/>
-      <c r="C57" s="45"/>
-      <c r="D57" t="s" s="34">
-        <v>179</v>
-      </c>
+      <c r="C57" t="inlineStr" s="34">
+        <is>
+          <t>Tranchée</t>
+        </is>
+      </c>
+      <c r="D57" s="37"/>
       <c r="E57" s="37"/>
-      <c r="F57" s="37"/>
-      <c r="G57" s="37"/>
-      <c r="H57" s="37"/>
-      <c r="I57" s="37"/>
-      <c r="J57" s="45"/>
-      <c r="K57" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="L57" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="M57" s="8"/>
-      <c r="N57" s="40">
+      <c r="F57" s="45"/>
+      <c r="G57" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I57" s="8"/>
+      <c r="J57" s="40">
         <v>41081</v>
       </c>
-      <c r="O57" s="44"/>
-      <c r="P57" s="45"/>
-      <c r="Q57" t="s" s="2">
+      <c r="K57" s="44"/>
+      <c r="L57" s="45"/>
+      <c r="M57" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="R57" s="44"/>
+      <c r="N57" s="44"/>
+      <c r="O57" s="37"/>
+      <c r="P57" s="37"/>
+      <c r="Q57" s="37"/>
+      <c r="R57" s="37"/>
       <c r="S57" s="37"/>
       <c r="T57" s="37"/>
-      <c r="U57" s="37"/>
-      <c r="V57" s="37"/>
-      <c r="W57" s="37"/>
-      <c r="X57" s="37"/>
-      <c r="Y57" s="37"/>
-      <c r="Z57" s="37"/>
-      <c r="AA57" s="37"/>
-      <c r="AB57" s="37"/>
-      <c r="AC57" s="45"/>
+      <c r="U57" s="45"/>
     </row>
     <row r="58" ht="14.7" customHeight="1">
       <c r="A58" t="s" s="47">
         <v>188</v>
       </c>
       <c r="B58" s="49"/>
-      <c r="C58" s="45"/>
-      <c r="D58" t="s" s="34">
-        <v>179</v>
-      </c>
+      <c r="C58" t="inlineStr" s="34">
+        <is>
+          <t>Tranchée</t>
+        </is>
+      </c>
+      <c r="D58" s="37"/>
       <c r="E58" s="37"/>
-      <c r="F58" s="37"/>
-      <c r="G58" s="37"/>
-      <c r="H58" s="37"/>
-      <c r="I58" s="37"/>
-      <c r="J58" s="45"/>
-      <c r="K58" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="M58" s="8"/>
-      <c r="N58" s="40">
+      <c r="F58" s="45"/>
+      <c r="G58" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I58" s="8"/>
+      <c r="J58" s="40">
         <v>41081</v>
       </c>
-      <c r="O58" s="44"/>
-      <c r="P58" s="45"/>
-      <c r="Q58" t="s" s="2">
+      <c r="K58" s="44"/>
+      <c r="L58" s="45"/>
+      <c r="M58" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="R58" s="44"/>
+      <c r="N58" s="44"/>
+      <c r="O58" s="37"/>
+      <c r="P58" s="37"/>
+      <c r="Q58" s="37"/>
+      <c r="R58" s="37"/>
       <c r="S58" s="37"/>
       <c r="T58" s="37"/>
-      <c r="U58" s="37"/>
-      <c r="V58" s="37"/>
-      <c r="W58" s="37"/>
-      <c r="X58" s="37"/>
-      <c r="Y58" s="37"/>
-      <c r="Z58" s="37"/>
-      <c r="AA58" s="37"/>
-      <c r="AB58" s="37"/>
-      <c r="AC58" s="45"/>
+      <c r="U58" s="45"/>
     </row>
     <row r="59" ht="13.65" customHeight="1">
       <c r="A59" t="s" s="47">
         <v>189</v>
       </c>
       <c r="B59" s="49"/>
-      <c r="C59" s="45"/>
-      <c r="D59" t="s" s="34">
-        <v>179</v>
-      </c>
+      <c r="C59" t="inlineStr" s="34">
+        <is>
+          <t>Tranchée</t>
+        </is>
+      </c>
+      <c r="D59" s="37"/>
       <c r="E59" s="37"/>
-      <c r="F59" s="37"/>
-      <c r="G59" s="37"/>
-      <c r="H59" s="37"/>
-      <c r="I59" s="37"/>
-      <c r="J59" s="45"/>
-      <c r="K59" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="M59" s="8"/>
-      <c r="N59" s="40">
+      <c r="F59" s="45"/>
+      <c r="G59" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I59" s="8"/>
+      <c r="J59" s="40">
         <v>41081</v>
       </c>
-      <c r="O59" s="44"/>
-      <c r="P59" s="45"/>
-      <c r="Q59" t="s" s="2">
+      <c r="K59" s="44"/>
+      <c r="L59" s="45"/>
+      <c r="M59" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="R59" s="44"/>
+      <c r="N59" s="44"/>
+      <c r="O59" s="37"/>
+      <c r="P59" s="37"/>
+      <c r="Q59" s="37"/>
+      <c r="R59" s="37"/>
       <c r="S59" s="37"/>
       <c r="T59" s="37"/>
-      <c r="U59" s="37"/>
-      <c r="V59" s="37"/>
-      <c r="W59" s="37"/>
-      <c r="X59" s="37"/>
-      <c r="Y59" s="37"/>
-      <c r="Z59" s="37"/>
-      <c r="AA59" s="37"/>
-      <c r="AB59" s="37"/>
-      <c r="AC59" s="45"/>
+      <c r="U59" s="45"/>
     </row>
     <row r="60" ht="13.65" customHeight="1">
       <c r="A60" t="s" s="47">
         <v>190</v>
       </c>
       <c r="B60" s="49"/>
-      <c r="C60" s="45"/>
-      <c r="D60" t="s" s="34">
-        <v>179</v>
-      </c>
+      <c r="C60" t="inlineStr" s="34">
+        <is>
+          <t>Tranchée</t>
+        </is>
+      </c>
+      <c r="D60" s="37"/>
       <c r="E60" s="37"/>
-      <c r="F60" s="37"/>
-      <c r="G60" s="37"/>
-      <c r="H60" s="37"/>
-      <c r="I60" s="37"/>
-      <c r="J60" s="45"/>
-      <c r="K60" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="M60" s="8"/>
-      <c r="N60" s="40">
+      <c r="F60" s="45"/>
+      <c r="G60" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I60" s="8"/>
+      <c r="J60" s="40">
         <v>41081</v>
       </c>
-      <c r="O60" s="44"/>
-      <c r="P60" s="45"/>
-      <c r="Q60" t="s" s="2">
+      <c r="K60" s="44"/>
+      <c r="L60" s="45"/>
+      <c r="M60" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="R60" s="44"/>
+      <c r="N60" s="44"/>
+      <c r="O60" s="37"/>
+      <c r="P60" s="37"/>
+      <c r="Q60" s="37"/>
+      <c r="R60" s="37"/>
       <c r="S60" s="37"/>
       <c r="T60" s="37"/>
-      <c r="U60" s="37"/>
-      <c r="V60" s="37"/>
-      <c r="W60" s="37"/>
-      <c r="X60" s="37"/>
-      <c r="Y60" s="37"/>
-      <c r="Z60" s="37"/>
-      <c r="AA60" s="37"/>
-      <c r="AB60" s="37"/>
-      <c r="AC60" s="45"/>
+      <c r="U60" s="45"/>
     </row>
     <row r="61" ht="13.65" customHeight="1">
       <c r="A61" t="s" s="50">
         <v>191</v>
       </c>
       <c r="B61" s="44"/>
-      <c r="C61" s="45"/>
-      <c r="D61" t="s" s="34">
-        <v>192</v>
-      </c>
+      <c r="C61" t="inlineStr" s="34">
+        <is>
+          <t>Entité archéologique</t>
+        </is>
+      </c>
+      <c r="D61" s="37"/>
       <c r="E61" s="37"/>
-      <c r="F61" s="37"/>
-      <c r="G61" s="37"/>
-      <c r="H61" s="37"/>
-      <c r="I61" s="37"/>
-      <c r="J61" s="45"/>
-      <c r="K61" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="M61" s="8"/>
-      <c r="N61" s="40">
+      <c r="F61" s="45"/>
+      <c r="G61" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I61" s="8"/>
+      <c r="J61" s="40">
         <v>41081</v>
       </c>
-      <c r="O61" s="44"/>
-      <c r="P61" s="45"/>
-      <c r="Q61" t="s" s="2">
+      <c r="K61" s="44"/>
+      <c r="L61" s="45"/>
+      <c r="M61" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="R61" s="44"/>
+      <c r="N61" s="44"/>
+      <c r="O61" s="37"/>
+      <c r="P61" s="37"/>
+      <c r="Q61" s="37"/>
+      <c r="R61" s="37"/>
       <c r="S61" s="37"/>
       <c r="T61" s="37"/>
-      <c r="U61" s="37"/>
-      <c r="V61" s="37"/>
-      <c r="W61" s="37"/>
-      <c r="X61" s="37"/>
-      <c r="Y61" s="37"/>
-      <c r="Z61" s="37"/>
-      <c r="AA61" s="37"/>
-      <c r="AB61" s="37"/>
-      <c r="AC61" s="45"/>
+      <c r="U61" s="45"/>
     </row>
     <row r="62" ht="13.65" customHeight="1">
       <c r="A62" t="s" s="2">
         <v>193</v>
       </c>
       <c r="B62" s="44"/>
-      <c r="C62" s="45"/>
-      <c r="D62" t="s" s="34">
-        <v>192</v>
-      </c>
+      <c r="C62" t="inlineStr" s="34">
+        <is>
+          <t>Entité archéologique</t>
+        </is>
+      </c>
+      <c r="D62" s="37"/>
       <c r="E62" s="37"/>
-      <c r="F62" s="37"/>
-      <c r="G62" s="37"/>
-      <c r="H62" s="37"/>
-      <c r="I62" s="37"/>
-      <c r="J62" s="45"/>
-      <c r="K62" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="L62" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="M62" s="8"/>
-      <c r="N62" s="40">
+      <c r="F62" s="45"/>
+      <c r="G62" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I62" s="8"/>
+      <c r="J62" s="40">
         <v>41081</v>
       </c>
-      <c r="O62" s="44"/>
-      <c r="P62" s="45"/>
-      <c r="Q62" t="s" s="2">
+      <c r="K62" s="44"/>
+      <c r="L62" s="45"/>
+      <c r="M62" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="R62" s="44"/>
+      <c r="N62" s="44"/>
+      <c r="O62" s="37"/>
+      <c r="P62" s="37"/>
+      <c r="Q62" s="37"/>
+      <c r="R62" s="37"/>
       <c r="S62" s="37"/>
       <c r="T62" s="37"/>
-      <c r="U62" s="37"/>
-      <c r="V62" s="37"/>
-      <c r="W62" s="37"/>
-      <c r="X62" s="37"/>
-      <c r="Y62" s="37"/>
-      <c r="Z62" s="37"/>
-      <c r="AA62" s="37"/>
-      <c r="AB62" s="37"/>
-      <c r="AC62" s="45"/>
+      <c r="U62" s="45"/>
     </row>
     <row r="63" ht="13.65" customHeight="1">
       <c r="A63" t="s" s="2">
         <v>194</v>
       </c>
       <c r="B63" s="44"/>
-      <c r="C63" s="45"/>
-      <c r="D63" t="s" s="34">
-        <v>192</v>
-      </c>
+      <c r="C63" t="inlineStr" s="34">
+        <is>
+          <t>Entité archéologique</t>
+        </is>
+      </c>
+      <c r="D63" s="37"/>
       <c r="E63" s="37"/>
-      <c r="F63" s="37"/>
-      <c r="G63" s="37"/>
-      <c r="H63" s="37"/>
-      <c r="I63" s="37"/>
-      <c r="J63" s="45"/>
-      <c r="K63" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="M63" s="8"/>
-      <c r="N63" s="40">
+      <c r="F63" s="45"/>
+      <c r="G63" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I63" s="8"/>
+      <c r="J63" s="40">
         <v>41081</v>
       </c>
-      <c r="O63" s="44"/>
-      <c r="P63" s="45"/>
-      <c r="Q63" t="s" s="2">
+      <c r="K63" s="44"/>
+      <c r="L63" s="45"/>
+      <c r="M63" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="R63" s="44"/>
+      <c r="N63" s="44"/>
+      <c r="O63" s="37"/>
+      <c r="P63" s="37"/>
+      <c r="Q63" s="37"/>
+      <c r="R63" s="37"/>
       <c r="S63" s="37"/>
       <c r="T63" s="37"/>
-      <c r="U63" s="37"/>
-      <c r="V63" s="37"/>
-      <c r="W63" s="37"/>
-      <c r="X63" s="37"/>
-      <c r="Y63" s="37"/>
-      <c r="Z63" s="37"/>
-      <c r="AA63" s="37"/>
-      <c r="AB63" s="37"/>
-      <c r="AC63" s="45"/>
+      <c r="U63" s="45"/>
     </row>
     <row r="64" ht="13.65" customHeight="1">
       <c r="A64" t="s" s="2">
         <v>195</v>
       </c>
       <c r="B64" s="44"/>
-      <c r="C64" s="45"/>
-      <c r="D64" t="s" s="34">
-        <v>192</v>
-      </c>
+      <c r="C64" t="inlineStr" s="34">
+        <is>
+          <t>Entité archéologique</t>
+        </is>
+      </c>
+      <c r="D64" s="37"/>
       <c r="E64" s="37"/>
-      <c r="F64" s="37"/>
-      <c r="G64" s="37"/>
-      <c r="H64" s="37"/>
-      <c r="I64" s="37"/>
-      <c r="J64" s="45"/>
-      <c r="K64" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="M64" s="8"/>
-      <c r="N64" s="40">
+      <c r="F64" s="45"/>
+      <c r="G64" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I64" s="8"/>
+      <c r="J64" s="40">
         <v>41081</v>
       </c>
-      <c r="O64" s="44"/>
-      <c r="P64" s="45"/>
-      <c r="Q64" t="s" s="2">
+      <c r="K64" s="44"/>
+      <c r="L64" s="45"/>
+      <c r="M64" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="R64" s="44"/>
+      <c r="N64" s="44"/>
+      <c r="O64" s="37"/>
+      <c r="P64" s="37"/>
+      <c r="Q64" s="37"/>
+      <c r="R64" s="37"/>
       <c r="S64" s="37"/>
       <c r="T64" s="37"/>
-      <c r="U64" s="37"/>
-      <c r="V64" s="37"/>
-      <c r="W64" s="37"/>
-      <c r="X64" s="37"/>
-      <c r="Y64" s="37"/>
-      <c r="Z64" s="37"/>
-      <c r="AA64" s="37"/>
-      <c r="AB64" s="37"/>
-      <c r="AC64" s="45"/>
+      <c r="U64" s="45"/>
     </row>
     <row r="65" ht="13.65" customHeight="1">
       <c r="A65" t="s" s="2">
         <v>196</v>
       </c>
       <c r="B65" s="44"/>
-      <c r="C65" s="45"/>
-      <c r="D65" t="s" s="34">
-        <v>192</v>
-      </c>
+      <c r="C65" t="inlineStr" s="34">
+        <is>
+          <t>Entité archéologique</t>
+        </is>
+      </c>
+      <c r="D65" s="37"/>
       <c r="E65" s="37"/>
-      <c r="F65" s="37"/>
-      <c r="G65" s="37"/>
-      <c r="H65" s="37"/>
-      <c r="I65" s="37"/>
-      <c r="J65" s="45"/>
-      <c r="K65" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="M65" s="8"/>
-      <c r="N65" s="40">
+      <c r="F65" s="45"/>
+      <c r="G65" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I65" s="8"/>
+      <c r="J65" s="40">
         <v>41081</v>
       </c>
-      <c r="O65" s="44"/>
-      <c r="P65" s="45"/>
-      <c r="Q65" t="s" s="2">
+      <c r="K65" s="44"/>
+      <c r="L65" s="45"/>
+      <c r="M65" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="R65" s="44"/>
+      <c r="N65" s="44"/>
+      <c r="O65" s="37"/>
+      <c r="P65" s="37"/>
+      <c r="Q65" s="37"/>
+      <c r="R65" s="37"/>
       <c r="S65" s="37"/>
       <c r="T65" s="37"/>
-      <c r="U65" s="37"/>
-      <c r="V65" s="37"/>
-      <c r="W65" s="37"/>
-      <c r="X65" s="37"/>
-      <c r="Y65" s="37"/>
-      <c r="Z65" s="37"/>
-      <c r="AA65" s="37"/>
-      <c r="AB65" s="37"/>
-      <c r="AC65" s="45"/>
+      <c r="U65" s="45"/>
     </row>
     <row r="66" ht="13.65" customHeight="1">
       <c r="A66" t="s" s="2">
         <v>197</v>
       </c>
       <c r="B66" s="44"/>
-      <c r="C66" s="45"/>
-      <c r="D66" t="s" s="34">
-        <v>192</v>
-      </c>
+      <c r="C66" t="inlineStr" s="34">
+        <is>
+          <t>Entité archéologique</t>
+        </is>
+      </c>
+      <c r="D66" s="37"/>
       <c r="E66" s="37"/>
-      <c r="F66" s="37"/>
-      <c r="G66" s="37"/>
-      <c r="H66" s="37"/>
-      <c r="I66" s="37"/>
-      <c r="J66" s="45"/>
-      <c r="K66" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="L66" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="M66" s="8"/>
-      <c r="N66" s="40">
+      <c r="F66" s="45"/>
+      <c r="G66" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I66" s="8"/>
+      <c r="J66" s="40">
         <v>41081</v>
       </c>
-      <c r="O66" s="44"/>
-      <c r="P66" s="45"/>
-      <c r="Q66" t="s" s="2">
+      <c r="K66" s="44"/>
+      <c r="L66" s="45"/>
+      <c r="M66" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="R66" s="44"/>
+      <c r="N66" s="44"/>
+      <c r="O66" s="37"/>
+      <c r="P66" s="37"/>
+      <c r="Q66" s="37"/>
+      <c r="R66" s="37"/>
       <c r="S66" s="37"/>
       <c r="T66" s="37"/>
-      <c r="U66" s="37"/>
-      <c r="V66" s="37"/>
-      <c r="W66" s="37"/>
-      <c r="X66" s="37"/>
-      <c r="Y66" s="37"/>
-      <c r="Z66" s="37"/>
-      <c r="AA66" s="37"/>
-      <c r="AB66" s="37"/>
-      <c r="AC66" s="45"/>
+      <c r="U66" s="45"/>
     </row>
     <row r="67" ht="13.65" customHeight="1">
       <c r="A67" t="s" s="2">
         <v>198</v>
       </c>
       <c r="B67" s="44"/>
-      <c r="C67" s="45"/>
-      <c r="D67" t="s" s="34">
-        <v>192</v>
-      </c>
+      <c r="C67" t="inlineStr" s="34">
+        <is>
+          <t>Entité archéologique</t>
+        </is>
+      </c>
+      <c r="D67" s="37"/>
       <c r="E67" s="37"/>
-      <c r="F67" s="37"/>
-      <c r="G67" s="37"/>
-      <c r="H67" s="37"/>
-      <c r="I67" s="37"/>
-      <c r="J67" s="45"/>
-      <c r="K67" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="L67" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="M67" s="8"/>
-      <c r="N67" s="40">
+      <c r="F67" s="45"/>
+      <c r="G67" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I67" s="8"/>
+      <c r="J67" s="40">
         <v>41081</v>
       </c>
-      <c r="O67" s="44"/>
-      <c r="P67" s="45"/>
-      <c r="Q67" t="s" s="2">
+      <c r="K67" s="44"/>
+      <c r="L67" s="45"/>
+      <c r="M67" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="R67" s="44"/>
+      <c r="N67" s="44"/>
+      <c r="O67" s="37"/>
+      <c r="P67" s="37"/>
+      <c r="Q67" s="37"/>
+      <c r="R67" s="37"/>
       <c r="S67" s="37"/>
       <c r="T67" s="37"/>
-      <c r="U67" s="37"/>
-      <c r="V67" s="37"/>
-      <c r="W67" s="37"/>
-      <c r="X67" s="37"/>
-      <c r="Y67" s="37"/>
-      <c r="Z67" s="37"/>
-      <c r="AA67" s="37"/>
-      <c r="AB67" s="37"/>
-      <c r="AC67" s="45"/>
+      <c r="U67" s="45"/>
     </row>
     <row r="68" ht="13.65" customHeight="1">
       <c r="A68" t="s" s="2">
         <v>199</v>
       </c>
       <c r="B68" s="44"/>
-      <c r="C68" s="45"/>
-      <c r="D68" t="s" s="34">
-        <v>192</v>
-      </c>
+      <c r="C68" t="inlineStr" s="34">
+        <is>
+          <t>Entité archéologique</t>
+        </is>
+      </c>
+      <c r="D68" s="37"/>
       <c r="E68" s="37"/>
-      <c r="F68" s="37"/>
-      <c r="G68" s="37"/>
-      <c r="H68" s="37"/>
-      <c r="I68" s="37"/>
-      <c r="J68" s="45"/>
-      <c r="K68" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="L68" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="M68" s="8"/>
-      <c r="N68" s="40">
+      <c r="F68" s="45"/>
+      <c r="G68" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I68" s="8"/>
+      <c r="J68" s="40">
         <v>41081</v>
       </c>
-      <c r="O68" s="44"/>
-      <c r="P68" s="45"/>
-      <c r="Q68" t="s" s="2">
+      <c r="K68" s="44"/>
+      <c r="L68" s="45"/>
+      <c r="M68" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="R68" s="44"/>
+      <c r="N68" s="44"/>
+      <c r="O68" s="37"/>
+      <c r="P68" s="37"/>
+      <c r="Q68" s="37"/>
+      <c r="R68" s="37"/>
       <c r="S68" s="37"/>
       <c r="T68" s="37"/>
-      <c r="U68" s="37"/>
-      <c r="V68" s="37"/>
-      <c r="W68" s="37"/>
-      <c r="X68" s="37"/>
-      <c r="Y68" s="37"/>
-      <c r="Z68" s="37"/>
-      <c r="AA68" s="37"/>
-      <c r="AB68" s="37"/>
-      <c r="AC68" s="45"/>
+      <c r="U68" s="45"/>
     </row>
     <row r="69" ht="13.65" customHeight="1">
       <c r="A69" t="s" s="2">
         <v>200</v>
       </c>
       <c r="B69" s="44"/>
-      <c r="C69" s="45"/>
-      <c r="D69" t="s" s="34">
-        <v>192</v>
-      </c>
+      <c r="C69" t="inlineStr" s="34">
+        <is>
+          <t>Entité archéologique</t>
+        </is>
+      </c>
+      <c r="D69" s="37"/>
       <c r="E69" s="37"/>
-      <c r="F69" s="37"/>
-      <c r="G69" s="37"/>
-      <c r="H69" s="37"/>
-      <c r="I69" s="37"/>
-      <c r="J69" s="45"/>
-      <c r="K69" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="L69" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="M69" s="8"/>
-      <c r="N69" s="40">
+      <c r="F69" s="45"/>
+      <c r="G69" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I69" s="8"/>
+      <c r="J69" s="40">
         <v>41081</v>
       </c>
-      <c r="O69" s="44"/>
-      <c r="P69" s="45"/>
-      <c r="Q69" t="s" s="2">
+      <c r="K69" s="44"/>
+      <c r="L69" s="45"/>
+      <c r="M69" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="R69" s="44"/>
+      <c r="N69" s="44"/>
+      <c r="O69" s="37"/>
+      <c r="P69" s="37"/>
+      <c r="Q69" s="37"/>
+      <c r="R69" s="37"/>
       <c r="S69" s="37"/>
       <c r="T69" s="37"/>
-      <c r="U69" s="37"/>
-      <c r="V69" s="37"/>
-      <c r="W69" s="37"/>
-      <c r="X69" s="37"/>
-      <c r="Y69" s="37"/>
-      <c r="Z69" s="37"/>
-      <c r="AA69" s="37"/>
-      <c r="AB69" s="37"/>
-      <c r="AC69" s="45"/>
+      <c r="U69" s="45"/>
     </row>
     <row r="70" ht="13.65" customHeight="1">
       <c r="A70" t="s" s="2">
         <v>201</v>
       </c>
       <c r="B70" s="44"/>
-      <c r="C70" s="45"/>
-      <c r="D70" t="s" s="34">
-        <v>192</v>
-      </c>
+      <c r="C70" t="inlineStr" s="34">
+        <is>
+          <t>Entité archéologique</t>
+        </is>
+      </c>
+      <c r="D70" s="37"/>
       <c r="E70" s="37"/>
-      <c r="F70" s="37"/>
-      <c r="G70" s="37"/>
-      <c r="H70" s="37"/>
-      <c r="I70" s="37"/>
-      <c r="J70" s="45"/>
-      <c r="K70" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="L70" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="M70" s="8"/>
-      <c r="N70" s="40">
+      <c r="F70" s="45"/>
+      <c r="G70" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I70" s="8"/>
+      <c r="J70" s="40">
         <v>41081</v>
       </c>
-      <c r="O70" s="44"/>
-      <c r="P70" s="45"/>
-      <c r="Q70" t="s" s="2">
+      <c r="K70" s="44"/>
+      <c r="L70" s="45"/>
+      <c r="M70" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="R70" s="44"/>
+      <c r="N70" s="44"/>
+      <c r="O70" s="37"/>
+      <c r="P70" s="37"/>
+      <c r="Q70" s="37"/>
+      <c r="R70" s="37"/>
       <c r="S70" s="37"/>
       <c r="T70" s="37"/>
-      <c r="U70" s="37"/>
-      <c r="V70" s="37"/>
-      <c r="W70" s="37"/>
-      <c r="X70" s="37"/>
-      <c r="Y70" s="37"/>
-      <c r="Z70" s="37"/>
-      <c r="AA70" s="37"/>
-      <c r="AB70" s="37"/>
-      <c r="AC70" s="45"/>
+      <c r="U70" s="45"/>
     </row>
     <row r="71" ht="13.65" customHeight="1">
       <c r="A71" t="s" s="2">
         <v>202</v>
       </c>
       <c r="B71" s="44"/>
-      <c r="C71" s="45"/>
-      <c r="D71" t="s" s="34">
-        <v>192</v>
-      </c>
+      <c r="C71" t="inlineStr" s="34">
+        <is>
+          <t>Entité archéologique</t>
+        </is>
+      </c>
+      <c r="D71" s="37"/>
       <c r="E71" s="37"/>
-      <c r="F71" s="37"/>
-      <c r="G71" s="37"/>
-      <c r="H71" s="37"/>
-      <c r="I71" s="37"/>
-      <c r="J71" s="45"/>
-      <c r="K71" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="L71" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="M71" s="8"/>
-      <c r="N71" s="40">
+      <c r="F71" s="45"/>
+      <c r="G71" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I71" s="8"/>
+      <c r="J71" s="40">
         <v>41081</v>
       </c>
-      <c r="O71" s="44"/>
-      <c r="P71" s="45"/>
-      <c r="Q71" t="s" s="2">
+      <c r="K71" s="44"/>
+      <c r="L71" s="45"/>
+      <c r="M71" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="R71" s="44"/>
+      <c r="N71" s="44"/>
+      <c r="O71" s="37"/>
+      <c r="P71" s="37"/>
+      <c r="Q71" s="37"/>
+      <c r="R71" s="37"/>
       <c r="S71" s="37"/>
       <c r="T71" s="37"/>
-      <c r="U71" s="37"/>
-      <c r="V71" s="37"/>
-      <c r="W71" s="37"/>
-      <c r="X71" s="37"/>
-      <c r="Y71" s="37"/>
-      <c r="Z71" s="37"/>
-      <c r="AA71" s="37"/>
-      <c r="AB71" s="37"/>
-      <c r="AC71" s="45"/>
+      <c r="U71" s="45"/>
     </row>
     <row r="72" ht="13.65" customHeight="1">
       <c r="A72" t="s" s="2">
         <v>203</v>
       </c>
       <c r="B72" s="44"/>
-      <c r="C72" s="45"/>
-      <c r="D72" t="s" s="34">
-        <v>192</v>
-      </c>
+      <c r="C72" t="inlineStr" s="34">
+        <is>
+          <t>Entité archéologique</t>
+        </is>
+      </c>
+      <c r="D72" s="37"/>
       <c r="E72" s="37"/>
-      <c r="F72" s="37"/>
-      <c r="G72" s="37"/>
-      <c r="H72" s="37"/>
-      <c r="I72" s="37"/>
-      <c r="J72" s="45"/>
-      <c r="K72" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="L72" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="M72" s="8"/>
-      <c r="N72" s="40">
+      <c r="F72" s="45"/>
+      <c r="G72" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I72" s="8"/>
+      <c r="J72" s="40">
         <v>41081</v>
       </c>
-      <c r="O72" s="44"/>
-      <c r="P72" s="45"/>
-      <c r="Q72" t="s" s="2">
+      <c r="K72" s="44"/>
+      <c r="L72" s="45"/>
+      <c r="M72" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="R72" s="44"/>
+      <c r="N72" s="44"/>
+      <c r="O72" s="37"/>
+      <c r="P72" s="37"/>
+      <c r="Q72" s="37"/>
+      <c r="R72" s="37"/>
       <c r="S72" s="37"/>
       <c r="T72" s="37"/>
-      <c r="U72" s="37"/>
-      <c r="V72" s="37"/>
-      <c r="W72" s="37"/>
-      <c r="X72" s="37"/>
-      <c r="Y72" s="37"/>
-      <c r="Z72" s="37"/>
-      <c r="AA72" s="37"/>
-      <c r="AB72" s="37"/>
-      <c r="AC72" s="45"/>
+      <c r="U72" s="45"/>
     </row>
     <row r="73" ht="13.65" customHeight="1">
       <c r="A73" t="s" s="2">
         <v>204</v>
       </c>
       <c r="B73" s="44"/>
-      <c r="C73" s="45"/>
-      <c r="D73" t="s" s="34">
-        <v>192</v>
-      </c>
+      <c r="C73" t="inlineStr" s="34">
+        <is>
+          <t>Entité archéologique</t>
+        </is>
+      </c>
+      <c r="D73" s="37"/>
       <c r="E73" s="37"/>
-      <c r="F73" s="37"/>
-      <c r="G73" s="37"/>
-      <c r="H73" s="37"/>
-      <c r="I73" s="37"/>
-      <c r="J73" s="45"/>
-      <c r="K73" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="M73" s="8"/>
-      <c r="N73" s="40">
+      <c r="F73" s="45"/>
+      <c r="G73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I73" s="8"/>
+      <c r="J73" s="40">
         <v>41081</v>
       </c>
-      <c r="O73" s="44"/>
-      <c r="P73" s="45"/>
-      <c r="Q73" t="s" s="2">
+      <c r="K73" s="44"/>
+      <c r="L73" s="45"/>
+      <c r="M73" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="R73" s="44"/>
+      <c r="N73" s="44"/>
+      <c r="O73" s="37"/>
+      <c r="P73" s="37"/>
+      <c r="Q73" s="37"/>
+      <c r="R73" s="37"/>
       <c r="S73" s="37"/>
       <c r="T73" s="37"/>
-      <c r="U73" s="37"/>
-      <c r="V73" s="37"/>
-      <c r="W73" s="37"/>
-      <c r="X73" s="37"/>
-      <c r="Y73" s="37"/>
-      <c r="Z73" s="37"/>
-      <c r="AA73" s="37"/>
-      <c r="AB73" s="37"/>
-      <c r="AC73" s="45"/>
+      <c r="U73" s="45"/>
     </row>
     <row r="74" ht="13.65" customHeight="1">
       <c r="A74" t="s" s="2">
         <v>205</v>
       </c>
       <c r="B74" s="44"/>
-      <c r="C74" s="45"/>
-      <c r="D74" t="s" s="34">
-        <v>206</v>
-      </c>
+      <c r="C74" t="inlineStr" s="34">
+        <is>
+          <t>Entité archéologique structurée</t>
+        </is>
+      </c>
+      <c r="D74" s="37"/>
       <c r="E74" s="37"/>
-      <c r="F74" s="37"/>
-      <c r="G74" s="37"/>
-      <c r="H74" s="37"/>
-      <c r="I74" s="37"/>
-      <c r="J74" s="45"/>
-      <c r="K74" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="M74" s="8"/>
-      <c r="N74" s="40">
+      <c r="F74" s="45"/>
+      <c r="G74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I74" s="8"/>
+      <c r="J74" s="40">
         <v>41081</v>
       </c>
-      <c r="O74" s="44"/>
-      <c r="P74" s="45"/>
-      <c r="Q74" t="s" s="2">
+      <c r="K74" s="44"/>
+      <c r="L74" s="45"/>
+      <c r="M74" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="R74" s="44"/>
+      <c r="N74" s="44"/>
+      <c r="O74" s="37"/>
+      <c r="P74" s="37"/>
+      <c r="Q74" s="37"/>
+      <c r="R74" s="37"/>
       <c r="S74" s="37"/>
       <c r="T74" s="37"/>
-      <c r="U74" s="37"/>
-      <c r="V74" s="37"/>
-      <c r="W74" s="37"/>
-      <c r="X74" s="37"/>
-      <c r="Y74" s="37"/>
-      <c r="Z74" s="37"/>
-      <c r="AA74" s="37"/>
-      <c r="AB74" s="37"/>
-      <c r="AC74" s="45"/>
+      <c r="U74" s="45"/>
     </row>
     <row r="75" ht="13.65" customHeight="1">
       <c r="A75" t="s" s="2">
         <v>207</v>
       </c>
       <c r="B75" s="44"/>
-      <c r="C75" s="45"/>
-      <c r="D75" t="s" s="34">
-        <v>206</v>
-      </c>
+      <c r="C75" t="inlineStr" s="34">
+        <is>
+          <t>Entité archéologique structurée</t>
+        </is>
+      </c>
+      <c r="D75" s="37"/>
       <c r="E75" s="37"/>
-      <c r="F75" s="37"/>
-      <c r="G75" s="37"/>
-      <c r="H75" s="37"/>
-      <c r="I75" s="37"/>
-      <c r="J75" s="45"/>
-      <c r="K75" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="L75" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="M75" s="8"/>
-      <c r="N75" s="40">
+      <c r="F75" s="45"/>
+      <c r="G75" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I75" s="8"/>
+      <c r="J75" s="40">
         <v>41081</v>
       </c>
-      <c r="O75" s="44"/>
-      <c r="P75" s="45"/>
-      <c r="Q75" t="s" s="2">
+      <c r="K75" s="44"/>
+      <c r="L75" s="45"/>
+      <c r="M75" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="R75" s="44"/>
+      <c r="N75" s="44"/>
+      <c r="O75" s="37"/>
+      <c r="P75" s="37"/>
+      <c r="Q75" s="37"/>
+      <c r="R75" s="37"/>
       <c r="S75" s="37"/>
       <c r="T75" s="37"/>
-      <c r="U75" s="37"/>
-      <c r="V75" s="37"/>
-      <c r="W75" s="37"/>
-      <c r="X75" s="37"/>
-      <c r="Y75" s="37"/>
-      <c r="Z75" s="37"/>
-      <c r="AA75" s="37"/>
-      <c r="AB75" s="37"/>
-      <c r="AC75" s="45"/>
+      <c r="U75" s="45"/>
     </row>
     <row r="76" ht="13.65" customHeight="1">
       <c r="A76" t="s" s="2">
         <v>208</v>
       </c>
       <c r="B76" s="44"/>
-      <c r="C76" s="45"/>
-      <c r="D76" t="s" s="34">
-        <v>206</v>
-      </c>
+      <c r="C76" t="inlineStr" s="34">
+        <is>
+          <t>Entité archéologique structurée</t>
+        </is>
+      </c>
+      <c r="D76" s="37"/>
       <c r="E76" s="37"/>
-      <c r="F76" s="37"/>
-      <c r="G76" s="37"/>
-      <c r="H76" s="37"/>
-      <c r="I76" s="37"/>
-      <c r="J76" s="45"/>
-      <c r="K76" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="L76" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="M76" s="8"/>
-      <c r="N76" s="40">
+      <c r="F76" s="45"/>
+      <c r="G76" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I76" s="8"/>
+      <c r="J76" s="40">
         <v>41081</v>
       </c>
-      <c r="O76" s="44"/>
-      <c r="P76" s="45"/>
-      <c r="Q76" t="s" s="2">
+      <c r="K76" s="44"/>
+      <c r="L76" s="45"/>
+      <c r="M76" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="R76" s="44"/>
+      <c r="N76" s="44"/>
+      <c r="O76" s="37"/>
+      <c r="P76" s="37"/>
+      <c r="Q76" s="37"/>
+      <c r="R76" s="37"/>
       <c r="S76" s="37"/>
       <c r="T76" s="37"/>
-      <c r="U76" s="37"/>
-      <c r="V76" s="37"/>
-      <c r="W76" s="37"/>
-      <c r="X76" s="37"/>
-      <c r="Y76" s="37"/>
-      <c r="Z76" s="37"/>
-      <c r="AA76" s="37"/>
-      <c r="AB76" s="37"/>
-      <c r="AC76" s="45"/>
+      <c r="U76" s="45"/>
     </row>
     <row r="77" ht="13.65" customHeight="1">
       <c r="A77" t="s" s="2">
         <v>209</v>
       </c>
       <c r="B77" s="44"/>
-      <c r="C77" s="45"/>
-      <c r="D77" t="s" s="34">
-        <v>206</v>
-      </c>
+      <c r="C77" t="inlineStr" s="34">
+        <is>
+          <t>Entité archéologique structurée</t>
+        </is>
+      </c>
+      <c r="D77" s="37"/>
       <c r="E77" s="37"/>
-      <c r="F77" s="37"/>
-      <c r="G77" s="37"/>
-      <c r="H77" s="37"/>
-      <c r="I77" s="37"/>
-      <c r="J77" s="45"/>
-      <c r="K77" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="L77" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="M77" s="8"/>
-      <c r="N77" s="40">
+      <c r="F77" s="45"/>
+      <c r="G77" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I77" s="8"/>
+      <c r="J77" s="40">
         <v>41081</v>
       </c>
-      <c r="O77" s="44"/>
-      <c r="P77" s="45"/>
-      <c r="Q77" t="s" s="2">
+      <c r="K77" s="44"/>
+      <c r="L77" s="45"/>
+      <c r="M77" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="R77" s="44"/>
+      <c r="N77" s="44"/>
+      <c r="O77" s="37"/>
+      <c r="P77" s="37"/>
+      <c r="Q77" s="37"/>
+      <c r="R77" s="37"/>
       <c r="S77" s="37"/>
       <c r="T77" s="37"/>
-      <c r="U77" s="37"/>
-      <c r="V77" s="37"/>
-      <c r="W77" s="37"/>
-      <c r="X77" s="37"/>
-      <c r="Y77" s="37"/>
-      <c r="Z77" s="37"/>
-      <c r="AA77" s="37"/>
-      <c r="AB77" s="37"/>
-      <c r="AC77" s="45"/>
+      <c r="U77" s="45"/>
     </row>
     <row r="78" ht="13.65" customHeight="1">
       <c r="A78" t="s" s="2">
         <v>210</v>
       </c>
       <c r="B78" s="44"/>
-      <c r="C78" s="45"/>
-      <c r="D78" t="s" s="34">
-        <v>206</v>
-      </c>
+      <c r="C78" t="inlineStr" s="34">
+        <is>
+          <t>Entité archéologique structurée</t>
+        </is>
+      </c>
+      <c r="D78" s="37"/>
       <c r="E78" s="37"/>
-      <c r="F78" s="37"/>
-      <c r="G78" s="37"/>
-      <c r="H78" s="37"/>
-      <c r="I78" s="37"/>
-      <c r="J78" s="45"/>
-      <c r="K78" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="L78" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="M78" s="8"/>
-      <c r="N78" s="40">
+      <c r="F78" s="45"/>
+      <c r="G78" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I78" s="8"/>
+      <c r="J78" s="40">
         <v>41081</v>
       </c>
-      <c r="O78" s="44"/>
-      <c r="P78" s="45"/>
-      <c r="Q78" t="s" s="2">
+      <c r="K78" s="44"/>
+      <c r="L78" s="45"/>
+      <c r="M78" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="R78" s="44"/>
+      <c r="N78" s="44"/>
+      <c r="O78" s="37"/>
+      <c r="P78" s="37"/>
+      <c r="Q78" s="37"/>
+      <c r="R78" s="37"/>
       <c r="S78" s="37"/>
       <c r="T78" s="37"/>
-      <c r="U78" s="37"/>
-      <c r="V78" s="37"/>
-      <c r="W78" s="37"/>
-      <c r="X78" s="37"/>
-      <c r="Y78" s="37"/>
-      <c r="Z78" s="37"/>
-      <c r="AA78" s="37"/>
-      <c r="AB78" s="37"/>
-      <c r="AC78" s="45"/>
+      <c r="U78" s="45"/>
     </row>
     <row r="79" ht="13.65" customHeight="1">
       <c r="A79" t="s" s="2">
         <v>211</v>
       </c>
       <c r="B79" s="44"/>
-      <c r="C79" s="45"/>
-      <c r="D79" t="s" s="34">
-        <v>206</v>
-      </c>
+      <c r="C79" t="inlineStr" s="34">
+        <is>
+          <t>Entité archéologique structurée</t>
+        </is>
+      </c>
+      <c r="D79" s="37"/>
       <c r="E79" s="37"/>
-      <c r="F79" s="37"/>
-      <c r="G79" s="37"/>
-      <c r="H79" s="37"/>
-      <c r="I79" s="37"/>
-      <c r="J79" s="45"/>
-      <c r="K79" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="L79" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="M79" s="8"/>
-      <c r="N79" s="40">
+      <c r="F79" s="45"/>
+      <c r="G79" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I79" s="8"/>
+      <c r="J79" s="40">
         <v>41081</v>
       </c>
-      <c r="O79" s="44"/>
-      <c r="P79" s="45"/>
-      <c r="Q79" t="s" s="2">
+      <c r="K79" s="44"/>
+      <c r="L79" s="45"/>
+      <c r="M79" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="R79" s="44"/>
+      <c r="N79" s="44"/>
+      <c r="O79" s="37"/>
+      <c r="P79" s="37"/>
+      <c r="Q79" s="37"/>
+      <c r="R79" s="37"/>
       <c r="S79" s="37"/>
       <c r="T79" s="37"/>
-      <c r="U79" s="37"/>
-      <c r="V79" s="37"/>
-      <c r="W79" s="37"/>
-      <c r="X79" s="37"/>
-      <c r="Y79" s="37"/>
-      <c r="Z79" s="37"/>
-      <c r="AA79" s="37"/>
-      <c r="AB79" s="37"/>
-      <c r="AC79" s="45"/>
+      <c r="U79" s="45"/>
     </row>
     <row r="80" ht="13.65" customHeight="1">
       <c r="A80" t="s" s="2">
         <v>212</v>
       </c>
       <c r="B80" s="51"/>
-      <c r="C80" s="52"/>
-      <c r="D80" t="s" s="53">
-        <v>206</v>
-      </c>
+      <c r="C80" t="inlineStr" s="53">
+        <is>
+          <t>Entité archéologique structurée</t>
+        </is>
+      </c>
+      <c r="D80" s="54"/>
       <c r="E80" s="54"/>
-      <c r="F80" s="54"/>
-      <c r="G80" s="54"/>
-      <c r="H80" s="54"/>
-      <c r="I80" s="54"/>
-      <c r="J80" s="52"/>
-      <c r="K80" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="L80" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="M80" s="10"/>
-      <c r="N80" s="40">
+      <c r="F80" s="52"/>
+      <c r="G80" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="I80" s="10"/>
+      <c r="J80" s="40">
         <v>41081</v>
       </c>
-      <c r="O80" s="51"/>
-      <c r="P80" s="52"/>
-      <c r="Q80" t="s" s="2">
+      <c r="K80" s="51"/>
+      <c r="L80" s="52"/>
+      <c r="M80" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="R80" s="51"/>
+      <c r="N80" s="51"/>
+      <c r="O80" s="54"/>
+      <c r="P80" s="54"/>
+      <c r="Q80" s="54"/>
+      <c r="R80" s="54"/>
       <c r="S80" s="54"/>
       <c r="T80" s="54"/>
-      <c r="U80" s="54"/>
-      <c r="V80" s="54"/>
-      <c r="W80" s="54"/>
-      <c r="X80" s="54"/>
-      <c r="Y80" s="54"/>
-      <c r="Z80" s="54"/>
-      <c r="AA80" s="54"/>
-      <c r="AB80" s="54"/>
-      <c r="AC80" s="52"/>
+      <c r="U80" s="52"/>
     </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
@@ -7576,105 +7131,81 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AA10"/>
+  <dimension ref="A1:T10"/>
   <sheetFormatPr defaultColWidth="12.6667" defaultRowHeight="15.75" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="19.6719" style="55" customWidth="1"/>
-    <col min="2" max="2" width="50.8516" style="55" customWidth="1"/>
-    <col min="3" max="3" width="45.8516" style="55" customWidth="1"/>
-    <col min="4" max="4" width="48.5" style="55" customWidth="1"/>
-    <col min="5" max="5" width="21" style="55" customWidth="1"/>
-    <col min="6" max="6" width="23" style="55" customWidth="1"/>
-    <col min="7" max="7" width="26.3516" style="55" customWidth="1"/>
-    <col min="8" max="8" width="26.5" style="55" customWidth="1"/>
-    <col min="9" max="27" width="12.6719" style="55" customWidth="1"/>
-    <col min="28" max="16384" width="12.6719" style="55" customWidth="1"/>
+    <col min="2" max="2" width="45.8516" style="55" customWidth="1"/>
+    <col min="3" max="3" width="21" style="55" customWidth="1"/>
+    <col min="4" max="4" width="26.3516" style="55" customWidth="1"/>
+    <col min="5" max="5" width="26.5" style="55" customWidth="1"/>
+    <col min="6" max="20" width="12.6719" style="55" customWidth="1"/>
+    <col min="21" max="16377" width="12.6719" style="55" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="13.65" customHeight="1">
       <c r="A1" t="s" s="46">
         <v>40</v>
       </c>
-      <c r="B1" t="s" s="46">
-        <v>213</v>
+      <c r="B1" t="s" s="4">
+        <v>214</v>
       </c>
       <c r="C1" t="s" s="4">
-        <v>214</v>
-      </c>
-      <c r="D1" t="s" s="46">
-        <v>215</v>
-      </c>
-      <c r="E1" t="s" s="4">
         <v>216</v>
       </c>
-      <c r="F1" t="s" s="46">
-        <v>217</v>
-      </c>
-      <c r="G1" t="s" s="4">
+      <c r="D1" t="s" s="4">
         <v>218</v>
       </c>
+      <c r="E1" t="s" s="46">
+        <v>49</v>
+      </c>
+      <c r="F1" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="G1" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="H1" t="s" s="46">
-        <v>49</v>
-      </c>
-      <c r="I1" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="J1" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
+      </c>
+      <c r="I1" t="s" s="46">
+        <v>37</v>
+      </c>
+      <c r="J1" t="s" s="46">
+        <v>56</v>
       </c>
       <c r="K1" t="s" s="46">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L1" t="s" s="46">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="M1" t="s" s="46">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="N1" t="s" s="46">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O1" t="s" s="46">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="P1" t="s" s="46">
-        <v>58</v>
+        <v>224</v>
       </c>
       <c r="Q1" t="s" s="46">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="R1" t="s" s="46">
-        <v>65</v>
+        <v>227</v>
       </c>
       <c r="S1" t="s" s="46">
-        <v>66</v>
+        <v>229</v>
       </c>
       <c r="T1" t="s" s="46">
-        <v>224</v>
-      </c>
-      <c r="U1" t="s" s="46">
-        <v>225</v>
-      </c>
-      <c r="V1" t="s" s="46">
-        <v>226</v>
-      </c>
-      <c r="W1" t="s" s="46">
-        <v>227</v>
-      </c>
-      <c r="X1" t="s" s="46">
-        <v>228</v>
-      </c>
-      <c r="Y1" t="s" s="46">
-        <v>229</v>
-      </c>
-      <c r="Z1" t="s" s="46">
-        <v>230</v>
-      </c>
-      <c r="AA1" t="s" s="46">
         <v>231</v>
       </c>
     </row>
@@ -7682,31 +7213,37 @@
       <c r="A2" t="s" s="47">
         <v>232</v>
       </c>
-      <c r="B2" t="s" s="56">
-        <v>233</v>
-      </c>
-      <c r="C2" s="57"/>
-      <c r="D2" t="s" s="58">
-        <v>234</v>
-      </c>
-      <c r="E2" s="57"/>
-      <c r="F2" t="s" s="56">
-        <v>235</v>
-      </c>
-      <c r="G2" s="57"/>
-      <c r="H2" t="s" s="59">
-        <v>6</v>
-      </c>
-      <c r="I2" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J2" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K2" t="s" s="60">
+      <c r="B2" s="57" t="inlineStr">
+        <is>
+          <t>Faune</t>
+        </is>
+      </c>
+      <c r="C2" s="57" t="inlineStr">
+        <is>
+          <t>organique</t>
+        </is>
+      </c>
+      <c r="D2" s="57" t="inlineStr">
+        <is>
+          <t>coquille d'huître</t>
+        </is>
+      </c>
+      <c r="E2" t="s" s="59">
+        <v>6</v>
+      </c>
+      <c r="F2" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="G2" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="H2" t="s" s="60">
         <v>111</v>
       </c>
-      <c r="L2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="61"/>
+      <c r="L2" s="61"/>
       <c r="M2" s="61"/>
       <c r="N2" s="61"/>
       <c r="O2" s="61"/>
@@ -7714,44 +7251,43 @@
       <c r="Q2" s="61"/>
       <c r="R2" s="61"/>
       <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="61"/>
-      <c r="W2" s="61"/>
-      <c r="X2" s="61"/>
-      <c r="Y2" s="61"/>
-      <c r="Z2" s="61"/>
-      <c r="AA2" s="62"/>
+      <c r="T2" s="62"/>
     </row>
     <row r="3" ht="14.7" customHeight="1">
       <c r="A3" t="s" s="47">
         <v>236</v>
       </c>
-      <c r="B3" t="s" s="56">
-        <v>233</v>
-      </c>
-      <c r="C3" s="57"/>
-      <c r="D3" t="s" s="56">
-        <v>237</v>
-      </c>
-      <c r="E3" s="57"/>
-      <c r="F3" t="s" s="56">
-        <v>238</v>
-      </c>
-      <c r="G3" s="57"/>
-      <c r="H3" t="s" s="59">
-        <v>6</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J3" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K3" t="s" s="60">
+      <c r="B3" s="57" t="inlineStr">
+        <is>
+          <t>Faune</t>
+        </is>
+      </c>
+      <c r="C3" s="57" t="inlineStr">
+        <is>
+          <t>organique</t>
+        </is>
+      </c>
+      <c r="D3" s="57" t="inlineStr">
+        <is>
+          <t>os animal</t>
+        </is>
+      </c>
+      <c r="E3" t="s" s="59">
+        <v>6</v>
+      </c>
+      <c r="F3" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="G3" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="H3" t="s" s="60">
         <v>176</v>
       </c>
-      <c r="L3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="37"/>
+      <c r="K3" s="37"/>
+      <c r="L3" s="37"/>
       <c r="M3" s="37"/>
       <c r="N3" s="37"/>
       <c r="O3" s="37"/>
@@ -7759,44 +7295,43 @@
       <c r="Q3" s="37"/>
       <c r="R3" s="37"/>
       <c r="S3" s="37"/>
-      <c r="T3" s="37"/>
-      <c r="U3" s="37"/>
-      <c r="V3" s="37"/>
-      <c r="W3" s="37"/>
-      <c r="X3" s="37"/>
-      <c r="Y3" s="37"/>
-      <c r="Z3" s="37"/>
-      <c r="AA3" s="45"/>
+      <c r="T3" s="45"/>
     </row>
     <row r="4" ht="14.7" customHeight="1">
       <c r="A4" t="s" s="47">
         <v>239</v>
       </c>
-      <c r="B4" t="s" s="56">
-        <v>240</v>
-      </c>
-      <c r="C4" s="57"/>
-      <c r="D4" t="s" s="56">
-        <v>241</v>
-      </c>
-      <c r="E4" s="57"/>
-      <c r="F4" t="s" s="56">
-        <v>242</v>
-      </c>
-      <c r="G4" s="57"/>
-      <c r="H4" t="s" s="59">
-        <v>6</v>
-      </c>
-      <c r="I4" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J4" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K4" t="s" s="60">
+      <c r="B4" s="57" t="inlineStr">
+        <is>
+          <t>Métal</t>
+        </is>
+      </c>
+      <c r="C4" s="57" t="inlineStr">
+        <is>
+          <t>métal</t>
+        </is>
+      </c>
+      <c r="D4" s="57" t="inlineStr">
+        <is>
+          <t>Clou</t>
+        </is>
+      </c>
+      <c r="E4" t="s" s="59">
+        <v>6</v>
+      </c>
+      <c r="F4" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="G4" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="H4" t="s" s="60">
         <v>176</v>
       </c>
-      <c r="L4" s="49"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="37"/>
+      <c r="K4" s="37"/>
+      <c r="L4" s="37"/>
       <c r="M4" s="37"/>
       <c r="N4" s="37"/>
       <c r="O4" s="37"/>
@@ -7804,27 +7339,20 @@
       <c r="Q4" s="37"/>
       <c r="R4" s="37"/>
       <c r="S4" s="37"/>
-      <c r="T4" s="37"/>
-      <c r="U4" s="37"/>
-      <c r="V4" s="37"/>
-      <c r="W4" s="37"/>
-      <c r="X4" s="37"/>
-      <c r="Y4" s="37"/>
-      <c r="Z4" s="37"/>
-      <c r="AA4" s="45"/>
+      <c r="T4" s="45"/>
     </row>
     <row r="5" ht="13.65" customHeight="1">
       <c r="A5" s="63"/>
-      <c r="B5" s="61"/>
+      <c r="B5" s="37"/>
       <c r="C5" s="37"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="37"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="35"/>
       <c r="H5" s="61"/>
-      <c r="I5" s="35"/>
-      <c r="J5" s="35"/>
-      <c r="K5" s="61"/>
+      <c r="I5" s="37"/>
+      <c r="J5" s="37"/>
+      <c r="K5" s="37"/>
       <c r="L5" s="37"/>
       <c r="M5" s="37"/>
       <c r="N5" s="37"/>
@@ -7833,14 +7361,7 @@
       <c r="Q5" s="37"/>
       <c r="R5" s="37"/>
       <c r="S5" s="37"/>
-      <c r="T5" s="37"/>
-      <c r="U5" s="37"/>
-      <c r="V5" s="37"/>
-      <c r="W5" s="37"/>
-      <c r="X5" s="37"/>
-      <c r="Y5" s="37"/>
-      <c r="Z5" s="37"/>
-      <c r="AA5" s="45"/>
+      <c r="T5" s="45"/>
     </row>
     <row r="6" ht="13.65" customHeight="1">
       <c r="A6" s="44"/>
@@ -7862,14 +7383,7 @@
       <c r="Q6" s="37"/>
       <c r="R6" s="37"/>
       <c r="S6" s="37"/>
-      <c r="T6" s="37"/>
-      <c r="U6" s="37"/>
-      <c r="V6" s="37"/>
-      <c r="W6" s="37"/>
-      <c r="X6" s="37"/>
-      <c r="Y6" s="37"/>
-      <c r="Z6" s="37"/>
-      <c r="AA6" s="45"/>
+      <c r="T6" s="45"/>
     </row>
     <row r="7" ht="13.65" customHeight="1">
       <c r="A7" s="44"/>
@@ -7891,14 +7405,7 @@
       <c r="Q7" s="37"/>
       <c r="R7" s="37"/>
       <c r="S7" s="37"/>
-      <c r="T7" s="37"/>
-      <c r="U7" s="37"/>
-      <c r="V7" s="37"/>
-      <c r="W7" s="37"/>
-      <c r="X7" s="37"/>
-      <c r="Y7" s="37"/>
-      <c r="Z7" s="37"/>
-      <c r="AA7" s="45"/>
+      <c r="T7" s="45"/>
     </row>
     <row r="8" ht="13.65" customHeight="1">
       <c r="A8" s="44"/>
@@ -7920,14 +7427,7 @@
       <c r="Q8" s="37"/>
       <c r="R8" s="37"/>
       <c r="S8" s="37"/>
-      <c r="T8" s="37"/>
-      <c r="U8" s="37"/>
-      <c r="V8" s="37"/>
-      <c r="W8" s="37"/>
-      <c r="X8" s="37"/>
-      <c r="Y8" s="37"/>
-      <c r="Z8" s="37"/>
-      <c r="AA8" s="45"/>
+      <c r="T8" s="45"/>
     </row>
     <row r="9" ht="13.65" customHeight="1">
       <c r="A9" s="44"/>
@@ -7949,14 +7449,7 @@
       <c r="Q9" s="37"/>
       <c r="R9" s="37"/>
       <c r="S9" s="37"/>
-      <c r="T9" s="37"/>
-      <c r="U9" s="37"/>
-      <c r="V9" s="37"/>
-      <c r="W9" s="37"/>
-      <c r="X9" s="37"/>
-      <c r="Y9" s="37"/>
-      <c r="Z9" s="37"/>
-      <c r="AA9" s="45"/>
+      <c r="T9" s="45"/>
     </row>
     <row r="10" ht="13.65" customHeight="1">
       <c r="A10" s="51"/>
@@ -7978,24 +7471,9 @@
       <c r="Q10" s="54"/>
       <c r="R10" s="54"/>
       <c r="S10" s="54"/>
-      <c r="T10" s="54"/>
-      <c r="U10" s="54"/>
-      <c r="V10" s="54"/>
-      <c r="W10" s="54"/>
-      <c r="X10" s="54"/>
-      <c r="Y10" s="54"/>
-      <c r="Z10" s="54"/>
-      <c r="AA10" s="52"/>
+      <c r="T10" s="52"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4290921&amp;idt=th252"/>
-    <hyperlink ref="D2" r:id="rId2" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287991&amp;idt=th252"/>
-    <hyperlink ref="B3" r:id="rId3" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4290921&amp;idt=th252"/>
-    <hyperlink ref="D3" r:id="rId4" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287991&amp;idt=th252"/>
-    <hyperlink ref="B4" r:id="rId5" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4290922&amp;idt=th252"/>
-    <hyperlink ref="D4" r:id="rId6" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4290976&amp;idt=th252"/>
-  </hyperlinks>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
   <headerFooter>
@@ -8825,462 +8303,373 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="13.45" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="19.6719" style="70" customWidth="1"/>
-    <col min="2" max="2" width="38" style="70" customWidth="1"/>
-    <col min="3" max="3" width="12.5" style="70" customWidth="1"/>
-    <col min="4" max="4" width="19.8516" style="70" customWidth="1"/>
-    <col min="5" max="7" width="16.3516" style="70" customWidth="1"/>
-    <col min="8" max="16384" width="16.3516" style="70" customWidth="1"/>
+    <col min="2" max="2" width="12.5" style="70" customWidth="1"/>
+    <col min="3" max="4" width="16.3516" style="70" customWidth="1"/>
+    <col min="5" max="16381" width="16.3516" style="70" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="13.2" customHeight="1">
       <c r="A1" t="s" s="71">
         <v>245</v>
       </c>
-      <c r="B1" t="s" s="72">
-        <v>246</v>
-      </c>
-      <c r="C1" t="s" s="73">
+      <c r="B1" t="s" s="73">
         <v>247</v>
       </c>
+      <c r="C1" t="s" s="14">
+        <v>249</v>
+      </c>
       <c r="D1" t="s" s="14">
-        <v>248</v>
-      </c>
-      <c r="E1" t="s" s="14">
-        <v>249</v>
-      </c>
-      <c r="F1" t="s" s="14">
         <v>250</v>
       </c>
-      <c r="G1" t="s" s="74">
-        <v>251</v>
-      </c>
     </row>
     <row r="2" ht="13.2" customHeight="1">
-      <c r="A2" t="s" s="75">
-        <v>67</v>
-      </c>
-      <c r="B2" s="76"/>
-      <c r="C2" t="s" s="76">
-        <v>75</v>
-      </c>
-      <c r="D2" t="s" s="77">
+      <c r="A2" t="inlineStr" s="75">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr" s="76">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C2" t="s" s="77">
+        <v>253</v>
+      </c>
+      <c r="D2" t="s" s="78">
         <v>252</v>
       </c>
-      <c r="E2" t="s" s="77">
+    </row>
+    <row r="3" ht="13" customHeight="1">
+      <c r="A3" t="inlineStr" s="75">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr" s="76">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C3" t="s" s="36">
         <v>253</v>
       </c>
-      <c r="F2" t="s" s="78">
+      <c r="D3" t="s" s="79">
         <v>252</v>
       </c>
-      <c r="G2" t="s" s="9">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="3" ht="13" customHeight="1">
-      <c r="A3" t="s" s="75">
-        <v>67</v>
-      </c>
-      <c r="B3" s="76"/>
-      <c r="C3" t="s" s="76">
-        <v>77</v>
-      </c>
-      <c r="D3" t="s" s="36">
+    </row>
+    <row r="4" ht="13" customHeight="1">
+      <c r="A4" t="inlineStr" s="75">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr" s="76">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C4" t="s" s="36">
+        <v>253</v>
+      </c>
+      <c r="D4" t="s" s="79">
         <v>252</v>
       </c>
-      <c r="E3" t="s" s="36">
+    </row>
+    <row r="5" ht="13" customHeight="1">
+      <c r="A5" t="inlineStr" s="75">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr" s="76">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C5" t="s" s="36">
         <v>253</v>
       </c>
-      <c r="F3" t="s" s="79">
+      <c r="D5" t="s" s="79">
         <v>252</v>
       </c>
-      <c r="G3" t="s" s="9">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="4" ht="13" customHeight="1">
-      <c r="A4" t="s" s="75">
-        <v>67</v>
-      </c>
-      <c r="B4" s="76"/>
-      <c r="C4" t="s" s="76">
-        <v>79</v>
-      </c>
-      <c r="D4" t="s" s="36">
+    </row>
+    <row r="6" ht="13" customHeight="1">
+      <c r="A6" t="inlineStr" s="75">
+        <is>
+          <t>1019</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr" s="76">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C6" t="s" s="36">
+        <v>253</v>
+      </c>
+      <c r="D6" t="s" s="79">
         <v>252</v>
       </c>
-      <c r="E4" t="s" s="36">
+    </row>
+    <row r="7" ht="13" customHeight="1">
+      <c r="A7" t="inlineStr" s="75">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr" s="76">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C7" t="s" s="36">
         <v>253</v>
       </c>
-      <c r="F4" t="s" s="79">
+      <c r="D7" t="s" s="79">
         <v>252</v>
       </c>
-      <c r="G4" t="s" s="9">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="5" ht="13" customHeight="1">
-      <c r="A5" t="s" s="75">
-        <v>67</v>
-      </c>
-      <c r="B5" s="76"/>
-      <c r="C5" t="s" s="76">
-        <v>111</v>
-      </c>
-      <c r="D5" t="s" s="36">
+    </row>
+    <row r="8" ht="13" customHeight="1">
+      <c r="A8" t="inlineStr" s="75">
+        <is>
+          <t>1016</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr" s="76">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C8" t="s" s="36">
+        <v>253</v>
+      </c>
+      <c r="D8" t="s" s="79">
         <v>252</v>
       </c>
-      <c r="E5" t="s" s="36">
+    </row>
+    <row r="9" ht="13" customHeight="1">
+      <c r="A9" t="inlineStr" s="75">
+        <is>
+          <t>1022</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr" s="76">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C9" t="s" s="36">
         <v>253</v>
       </c>
-      <c r="F5" t="s" s="79">
+      <c r="D9" t="s" s="79">
         <v>252</v>
       </c>
-      <c r="G5" t="s" s="9">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="6" ht="13" customHeight="1">
-      <c r="A6" t="s" s="75">
-        <v>67</v>
-      </c>
-      <c r="B6" s="76"/>
-      <c r="C6" t="s" s="76">
-        <v>120</v>
-      </c>
-      <c r="D6" t="s" s="36">
+    </row>
+    <row r="10" ht="13" customHeight="1">
+      <c r="A10" t="inlineStr" s="75">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr" s="76">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C10" t="s" s="36">
+        <v>253</v>
+      </c>
+      <c r="D10" t="s" s="79">
         <v>252</v>
       </c>
-      <c r="E6" t="s" s="36">
+    </row>
+    <row r="11" ht="13" customHeight="1">
+      <c r="A11" t="inlineStr" s="75">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr" s="76">
+        <is>
+          <t>1026</t>
+        </is>
+      </c>
+      <c r="C11" t="s" s="36">
         <v>253</v>
       </c>
-      <c r="F6" t="s" s="79">
+      <c r="D11" t="s" s="79">
         <v>252</v>
       </c>
-      <c r="G6" t="s" s="9">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="7" ht="13" customHeight="1">
-      <c r="A7" t="s" s="75">
-        <v>67</v>
-      </c>
-      <c r="B7" s="76"/>
-      <c r="C7" t="s" s="76">
-        <v>176</v>
-      </c>
-      <c r="D7" t="s" s="36">
+    </row>
+    <row r="12" ht="13" customHeight="1">
+      <c r="A12" t="inlineStr" s="75">
+        <is>
+          <t>1028</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr" s="76">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C12" t="s" s="36">
+        <v>253</v>
+      </c>
+      <c r="D12" t="s" s="79">
         <v>252</v>
       </c>
-      <c r="E7" t="s" s="36">
+    </row>
+    <row r="13" ht="13" customHeight="1">
+      <c r="A13" t="inlineStr" s="75">
+        <is>
+          <t>1036</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr" s="76">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C13" t="s" s="36">
         <v>253</v>
       </c>
-      <c r="F7" t="s" s="79">
+      <c r="D13" t="s" s="79">
         <v>252</v>
       </c>
-      <c r="G7" t="s" s="9">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="8" ht="13" customHeight="1">
-      <c r="A8" t="s" s="75">
-        <v>67</v>
-      </c>
-      <c r="B8" s="76"/>
-      <c r="C8" t="s" s="76">
-        <v>113</v>
-      </c>
-      <c r="D8" t="s" s="36">
+    </row>
+    <row r="14" ht="13" customHeight="1">
+      <c r="A14" t="inlineStr" s="75">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr" s="76">
+        <is>
+          <t>1011</t>
+        </is>
+      </c>
+      <c r="C14" t="s" s="36">
+        <v>253</v>
+      </c>
+      <c r="D14" t="s" s="79">
         <v>252</v>
       </c>
-      <c r="E8" t="s" s="36">
+    </row>
+    <row r="15" ht="13" customHeight="1">
+      <c r="A15" t="inlineStr" s="75">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr" s="76">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="C15" t="s" s="36">
         <v>253</v>
       </c>
-      <c r="F8" t="s" s="79">
+      <c r="D15" t="s" s="79">
         <v>252</v>
       </c>
-      <c r="G8" t="s" s="9">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="9" ht="13" customHeight="1">
-      <c r="A9" t="s" s="75">
-        <v>67</v>
-      </c>
-      <c r="B9" s="76"/>
-      <c r="C9" t="s" s="76">
-        <v>127</v>
-      </c>
-      <c r="D9" t="s" s="36">
+    </row>
+    <row r="16" ht="13" customHeight="1">
+      <c r="A16" t="inlineStr" s="75">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr" s="76">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="C16" t="s" s="36">
+        <v>253</v>
+      </c>
+      <c r="D16" t="s" s="79">
         <v>252</v>
       </c>
-      <c r="E9" t="s" s="36">
+    </row>
+    <row r="17" ht="13" customHeight="1">
+      <c r="A17" t="inlineStr" s="75">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr" s="76">
+        <is>
+          <t>1012</t>
+        </is>
+      </c>
+      <c r="C17" t="s" s="36">
         <v>253</v>
       </c>
-      <c r="F9" t="s" s="79">
+      <c r="D17" t="s" s="79">
         <v>252</v>
       </c>
-      <c r="G9" t="s" s="9">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="10" ht="13" customHeight="1">
-      <c r="A10" t="s" s="75">
-        <v>67</v>
-      </c>
-      <c r="B10" s="76"/>
-      <c r="C10" t="s" s="76">
-        <v>129</v>
-      </c>
-      <c r="D10" t="s" s="36">
+    </row>
+    <row r="18" ht="13" customHeight="1">
+      <c r="A18" t="inlineStr" s="75">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr" s="76">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="C18" t="s" s="36">
+        <v>253</v>
+      </c>
+      <c r="D18" t="s" s="79">
         <v>252</v>
       </c>
-      <c r="E10" t="s" s="36">
+    </row>
+    <row r="19" ht="13" customHeight="1">
+      <c r="A19" t="inlineStr" s="75">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr" s="76">
+        <is>
+          <t>1017</t>
+        </is>
+      </c>
+      <c r="C19" t="s" s="36">
         <v>253</v>
       </c>
-      <c r="F10" t="s" s="79">
+      <c r="D19" t="s" s="79">
         <v>252</v>
       </c>
-      <c r="G10" t="s" s="9">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="11" ht="13" customHeight="1">
-      <c r="A11" t="s" s="75">
-        <v>135</v>
-      </c>
-      <c r="B11" s="76"/>
-      <c r="C11" t="s" s="76">
-        <v>67</v>
-      </c>
-      <c r="D11" t="s" s="36">
+    </row>
+    <row r="20" ht="13" customHeight="1">
+      <c r="A20" t="inlineStr" s="80">
+        <is>
+          <t>1042</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr" s="81">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="C20" t="s" s="82">
         <v>253</v>
       </c>
-      <c r="E11" t="s" s="36">
-        <v>253</v>
-      </c>
-      <c r="F11" t="s" s="79">
+      <c r="D20" t="s" s="83">
         <v>252</v>
-      </c>
-      <c r="G11" t="s" s="9">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="12" ht="13" customHeight="1">
-      <c r="A12" t="s" s="75">
-        <v>67</v>
-      </c>
-      <c r="B12" s="76"/>
-      <c r="C12" t="s" s="76">
-        <v>139</v>
-      </c>
-      <c r="D12" t="s" s="36">
-        <v>252</v>
-      </c>
-      <c r="E12" t="s" s="36">
-        <v>253</v>
-      </c>
-      <c r="F12" t="s" s="79">
-        <v>252</v>
-      </c>
-      <c r="G12" t="s" s="9">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="13" ht="13" customHeight="1">
-      <c r="A13" t="s" s="75">
-        <v>67</v>
-      </c>
-      <c r="B13" s="76"/>
-      <c r="C13" t="s" s="76">
-        <v>156</v>
-      </c>
-      <c r="D13" t="s" s="36">
-        <v>252</v>
-      </c>
-      <c r="E13" t="s" s="36">
-        <v>253</v>
-      </c>
-      <c r="F13" t="s" s="79">
-        <v>252</v>
-      </c>
-      <c r="G13" t="s" s="9">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="14" ht="13" customHeight="1">
-      <c r="A14" t="s" s="75">
-        <v>100</v>
-      </c>
-      <c r="B14" s="76"/>
-      <c r="C14" t="s" s="76">
-        <v>75</v>
-      </c>
-      <c r="D14" t="s" s="36">
-        <v>253</v>
-      </c>
-      <c r="E14" t="s" s="36">
-        <v>253</v>
-      </c>
-      <c r="F14" t="s" s="79">
-        <v>252</v>
-      </c>
-      <c r="G14" t="s" s="9">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="15" ht="13" customHeight="1">
-      <c r="A15" t="s" s="75">
-        <v>67</v>
-      </c>
-      <c r="B15" s="76"/>
-      <c r="C15" t="s" s="76">
-        <v>75</v>
-      </c>
-      <c r="D15" t="s" s="36">
-        <v>252</v>
-      </c>
-      <c r="E15" t="s" s="36">
-        <v>253</v>
-      </c>
-      <c r="F15" t="s" s="79">
-        <v>252</v>
-      </c>
-      <c r="G15" t="s" s="9">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="16" ht="13" customHeight="1">
-      <c r="A16" t="s" s="75">
-        <v>77</v>
-      </c>
-      <c r="B16" s="76"/>
-      <c r="C16" t="s" s="76">
-        <v>75</v>
-      </c>
-      <c r="D16" t="s" s="36">
-        <v>253</v>
-      </c>
-      <c r="E16" t="s" s="36">
-        <v>253</v>
-      </c>
-      <c r="F16" t="s" s="79">
-        <v>252</v>
-      </c>
-      <c r="G16" t="s" s="9">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="17" ht="13" customHeight="1">
-      <c r="A17" t="s" s="75">
-        <v>79</v>
-      </c>
-      <c r="B17" s="76"/>
-      <c r="C17" t="s" s="76">
-        <v>75</v>
-      </c>
-      <c r="D17" t="s" s="36">
-        <v>253</v>
-      </c>
-      <c r="E17" t="s" s="36">
-        <v>253</v>
-      </c>
-      <c r="F17" t="s" s="79">
-        <v>252</v>
-      </c>
-      <c r="G17" t="s" s="9">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="18" ht="13" customHeight="1">
-      <c r="A18" t="s" s="75">
-        <v>102</v>
-      </c>
-      <c r="B18" s="76"/>
-      <c r="C18" t="s" s="76">
-        <v>75</v>
-      </c>
-      <c r="D18" t="s" s="36">
-        <v>253</v>
-      </c>
-      <c r="E18" t="s" s="36">
-        <v>253</v>
-      </c>
-      <c r="F18" t="s" s="79">
-        <v>252</v>
-      </c>
-      <c r="G18" t="s" s="9">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="19" ht="13" customHeight="1">
-      <c r="A19" t="s" s="75">
-        <v>111</v>
-      </c>
-      <c r="B19" s="76"/>
-      <c r="C19" t="s" s="76">
-        <v>75</v>
-      </c>
-      <c r="D19" t="s" s="36">
-        <v>253</v>
-      </c>
-      <c r="E19" t="s" s="36">
-        <v>253</v>
-      </c>
-      <c r="F19" t="s" s="79">
-        <v>252</v>
-      </c>
-      <c r="G19" t="s" s="9">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="20" ht="13" customHeight="1">
-      <c r="A20" t="s" s="75">
-        <v>115</v>
-      </c>
-      <c r="B20" s="76"/>
-      <c r="C20" t="s" s="76">
-        <v>75</v>
-      </c>
-      <c r="D20" t="s" s="36">
-        <v>252</v>
-      </c>
-      <c r="E20" t="s" s="36">
-        <v>253</v>
-      </c>
-      <c r="F20" t="s" s="79">
-        <v>252</v>
-      </c>
-      <c r="G20" t="s" s="9">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="21" ht="13" customHeight="1">
-      <c r="A21" t="s" s="80">
-        <v>75</v>
-      </c>
-      <c r="B21" s="81"/>
-      <c r="C21" t="s" s="81">
-        <v>168</v>
-      </c>
-      <c r="D21" t="s" s="82">
-        <v>252</v>
-      </c>
-      <c r="E21" t="s" s="82">
-        <v>253</v>
-      </c>
-      <c r="F21" t="s" s="83">
-        <v>252</v>
-      </c>
-      <c r="G21" t="s" s="11">
-        <v>254</v>
       </c>
     </row>
   </sheetData>
@@ -9293,17 +8682,16 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="13.45" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="3" width="16.3516" style="84" customWidth="1"/>
-    <col min="4" max="4" width="43" style="84" customWidth="1"/>
-    <col min="5" max="14" width="16.3516" style="84" customWidth="1"/>
-    <col min="15" max="16384" width="16.3516" style="84" customWidth="1"/>
+    <col min="4" max="11" width="16.3516" style="84" customWidth="1"/>
+    <col min="12" max="16381" width="16.3516" style="84" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="13.45" customHeight="1">
@@ -9317,36 +8705,27 @@
         <v>257</v>
       </c>
       <c r="D1" t="s" s="86">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="E1" t="s" s="86">
-        <v>258</v>
+        <v>37</v>
       </c>
       <c r="F1" t="s" s="86">
-        <v>37</v>
+        <v>259</v>
       </c>
       <c r="G1" t="s" s="86">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H1" t="s" s="86">
-        <v>260</v>
-      </c>
-      <c r="I1" t="s" s="86">
         <v>261</v>
       </c>
+      <c r="I1" t="s" s="85">
+        <v>4</v>
+      </c>
       <c r="J1" t="s" s="85">
-        <v>4</v>
+        <v>263</v>
       </c>
       <c r="K1" t="s" s="85">
-        <v>262</v>
-      </c>
-      <c r="L1" t="s" s="85">
-        <v>263</v>
-      </c>
-      <c r="M1" t="s" s="85">
-        <v>264</v>
-      </c>
-      <c r="N1" t="s" s="85">
         <v>265</v>
       </c>
     </row>
@@ -9361,28 +8740,27 @@
         <v>1</v>
       </c>
       <c r="D2" t="s" s="89">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E2" t="s" s="89">
-        <v>268</v>
-      </c>
-      <c r="F2" t="s" s="89">
         <v>269</v>
       </c>
+      <c r="F2" s="88">
+        <v>-150</v>
+      </c>
       <c r="G2" s="88">
-        <v>-150</v>
-      </c>
-      <c r="H2" s="88">
         <v>10</v>
       </c>
-      <c r="I2" t="s" s="89">
-        <v>72</v>
-      </c>
-      <c r="J2" s="90"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="35"/>
-      <c r="N2" s="42"/>
+      <c r="H2" t="s" s="89">
+        <v>72</v>
+      </c>
+      <c r="I2" s="90" t="inlineStr">
+        <is>
+          <t>Phase d'occupation</t>
+        </is>
+      </c>
+      <c r="J2" s="35"/>
+      <c r="K2" s="42"/>
     </row>
     <row r="3" ht="13.65" customHeight="1">
       <c r="A3" t="s" s="2">
@@ -9395,28 +8773,27 @@
         <v>2</v>
       </c>
       <c r="D3" t="s" s="93">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="E3" t="s" s="93">
-        <v>271</v>
-      </c>
-      <c r="F3" t="s" s="93">
         <v>272</v>
       </c>
+      <c r="F3" s="92">
+        <v>-10</v>
+      </c>
       <c r="G3" s="92">
-        <v>-10</v>
-      </c>
-      <c r="H3" s="92">
         <v>30</v>
       </c>
-      <c r="I3" t="s" s="93">
-        <v>72</v>
-      </c>
-      <c r="J3" s="94"/>
-      <c r="K3" s="37"/>
-      <c r="L3" s="37"/>
-      <c r="M3" s="37"/>
-      <c r="N3" s="45"/>
+      <c r="H3" t="s" s="93">
+        <v>72</v>
+      </c>
+      <c r="I3" s="94" t="inlineStr">
+        <is>
+          <t>Phase d'occupation</t>
+        </is>
+      </c>
+      <c r="J3" s="37"/>
+      <c r="K3" s="45"/>
     </row>
     <row r="4" ht="13.65" customHeight="1">
       <c r="A4" t="s" s="2">
@@ -9429,28 +8806,27 @@
         <v>3</v>
       </c>
       <c r="D4" t="s" s="93">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="E4" t="s" s="93">
-        <v>274</v>
-      </c>
-      <c r="F4" t="s" s="93">
         <v>275</v>
       </c>
+      <c r="F4" s="92">
+        <v>15</v>
+      </c>
       <c r="G4" s="92">
-        <v>15</v>
-      </c>
-      <c r="H4" s="92">
         <v>60</v>
       </c>
-      <c r="I4" t="s" s="93">
-        <v>72</v>
-      </c>
-      <c r="J4" s="94"/>
-      <c r="K4" s="37"/>
-      <c r="L4" s="37"/>
-      <c r="M4" s="37"/>
-      <c r="N4" s="45"/>
+      <c r="H4" t="s" s="93">
+        <v>72</v>
+      </c>
+      <c r="I4" s="94" t="inlineStr">
+        <is>
+          <t>Phase d'occupation</t>
+        </is>
+      </c>
+      <c r="J4" s="37"/>
+      <c r="K4" s="45"/>
     </row>
     <row r="5" ht="13.65" customHeight="1">
       <c r="A5" t="s" s="2">
@@ -9463,28 +8839,27 @@
         <v>4</v>
       </c>
       <c r="D5" t="s" s="93">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="E5" t="s" s="93">
-        <v>277</v>
-      </c>
-      <c r="F5" t="s" s="93">
         <v>278</v>
       </c>
+      <c r="F5" s="92">
+        <v>50</v>
+      </c>
       <c r="G5" s="92">
-        <v>50</v>
-      </c>
-      <c r="H5" s="92">
         <v>90</v>
       </c>
-      <c r="I5" t="s" s="93">
-        <v>72</v>
-      </c>
-      <c r="J5" s="94"/>
-      <c r="K5" s="37"/>
-      <c r="L5" s="37"/>
-      <c r="M5" s="37"/>
-      <c r="N5" s="45"/>
+      <c r="H5" t="s" s="93">
+        <v>72</v>
+      </c>
+      <c r="I5" s="94" t="inlineStr">
+        <is>
+          <t>Phase d'occupation</t>
+        </is>
+      </c>
+      <c r="J5" s="37"/>
+      <c r="K5" s="45"/>
     </row>
     <row r="6" ht="13.65" customHeight="1">
       <c r="A6" t="s" s="2">
@@ -9497,28 +8872,27 @@
         <v>5</v>
       </c>
       <c r="D6" t="s" s="93">
-        <v>267</v>
+        <v>280</v>
       </c>
       <c r="E6" t="s" s="93">
-        <v>280</v>
-      </c>
-      <c r="F6" t="s" s="93">
         <v>281</v>
       </c>
+      <c r="F6" s="92">
+        <v>90</v>
+      </c>
       <c r="G6" s="92">
-        <v>90</v>
-      </c>
-      <c r="H6" s="92">
         <v>150</v>
       </c>
-      <c r="I6" t="s" s="93">
+      <c r="H6" t="s" s="93">
         <v>282</v>
       </c>
-      <c r="J6" s="94"/>
-      <c r="K6" s="37"/>
-      <c r="L6" s="37"/>
-      <c r="M6" s="37"/>
-      <c r="N6" s="45"/>
+      <c r="I6" s="94" t="inlineStr">
+        <is>
+          <t>Phase d'occupation</t>
+        </is>
+      </c>
+      <c r="J6" s="37"/>
+      <c r="K6" s="45"/>
     </row>
     <row r="7" ht="13.65" customHeight="1">
       <c r="A7" t="s" s="2">
@@ -9531,28 +8905,27 @@
         <v>6</v>
       </c>
       <c r="D7" t="s" s="93">
-        <v>267</v>
+        <v>284</v>
       </c>
       <c r="E7" t="s" s="93">
-        <v>284</v>
-      </c>
-      <c r="F7" t="s" s="93">
         <v>285</v>
       </c>
+      <c r="F7" s="92">
+        <v>140</v>
+      </c>
       <c r="G7" s="92">
-        <v>140</v>
-      </c>
-      <c r="H7" s="92">
         <v>350</v>
       </c>
-      <c r="I7" t="s" s="93">
-        <v>72</v>
-      </c>
-      <c r="J7" s="94"/>
-      <c r="K7" s="37"/>
-      <c r="L7" s="37"/>
-      <c r="M7" s="37"/>
-      <c r="N7" s="45"/>
+      <c r="H7" t="s" s="93">
+        <v>72</v>
+      </c>
+      <c r="I7" s="94" t="inlineStr">
+        <is>
+          <t>Phase d'occupation</t>
+        </is>
+      </c>
+      <c r="J7" s="37"/>
+      <c r="K7" s="45"/>
     </row>
     <row r="8" ht="13.65" customHeight="1">
       <c r="A8" t="s" s="2">
@@ -9565,28 +8938,27 @@
         <v>7</v>
       </c>
       <c r="D8" t="s" s="93">
-        <v>267</v>
+        <v>287</v>
       </c>
       <c r="E8" t="s" s="93">
-        <v>287</v>
-      </c>
-      <c r="F8" t="s" s="93">
         <v>288</v>
       </c>
+      <c r="F8" s="92">
+        <v>501</v>
+      </c>
       <c r="G8" s="92">
-        <v>501</v>
-      </c>
-      <c r="H8" s="92">
         <v>1400</v>
       </c>
-      <c r="I8" t="s" s="93">
-        <v>72</v>
-      </c>
-      <c r="J8" s="94"/>
-      <c r="K8" s="37"/>
-      <c r="L8" s="37"/>
-      <c r="M8" s="37"/>
-      <c r="N8" s="45"/>
+      <c r="H8" t="s" s="93">
+        <v>72</v>
+      </c>
+      <c r="I8" s="94" t="inlineStr">
+        <is>
+          <t>Phase d'occupation</t>
+        </is>
+      </c>
+      <c r="J8" s="37"/>
+      <c r="K8" s="45"/>
     </row>
     <row r="9" ht="13.65" customHeight="1">
       <c r="A9" t="s" s="2">
@@ -9599,28 +8971,27 @@
         <v>8</v>
       </c>
       <c r="D9" t="s" s="93">
-        <v>267</v>
+        <v>290</v>
       </c>
       <c r="E9" t="s" s="93">
-        <v>290</v>
-      </c>
-      <c r="F9" t="s" s="93">
         <v>291</v>
       </c>
+      <c r="F9" s="92">
+        <v>1500</v>
+      </c>
       <c r="G9" s="92">
-        <v>1500</v>
-      </c>
-      <c r="H9" s="92">
         <v>1800</v>
       </c>
-      <c r="I9" t="s" s="93">
-        <v>72</v>
-      </c>
-      <c r="J9" s="94"/>
-      <c r="K9" s="37"/>
-      <c r="L9" s="37"/>
-      <c r="M9" s="37"/>
-      <c r="N9" s="45"/>
+      <c r="H9" t="s" s="93">
+        <v>72</v>
+      </c>
+      <c r="I9" s="94" t="inlineStr">
+        <is>
+          <t>Phase d'occupation</t>
+        </is>
+      </c>
+      <c r="J9" s="37"/>
+      <c r="K9" s="45"/>
     </row>
     <row r="10" ht="13.65" customHeight="1">
       <c r="A10" t="s" s="2">
@@ -9633,41 +9004,29 @@
         <v>9</v>
       </c>
       <c r="D10" t="s" s="93">
-        <v>267</v>
+        <v>293</v>
       </c>
       <c r="E10" t="s" s="93">
-        <v>293</v>
-      </c>
-      <c r="F10" t="s" s="93">
         <v>294</v>
       </c>
+      <c r="F10" s="92">
+        <v>1828</v>
+      </c>
       <c r="G10" s="92">
-        <v>1828</v>
-      </c>
-      <c r="H10" s="92">
         <v>2015</v>
       </c>
-      <c r="I10" t="s" s="93">
-        <v>72</v>
-      </c>
-      <c r="J10" s="95"/>
-      <c r="K10" s="54"/>
-      <c r="L10" s="54"/>
-      <c r="M10" s="54"/>
-      <c r="N10" s="52"/>
+      <c r="H10" t="s" s="93">
+        <v>72</v>
+      </c>
+      <c r="I10" s="95" t="inlineStr">
+        <is>
+          <t>Phase d'occupation</t>
+        </is>
+      </c>
+      <c r="J10" s="54"/>
+      <c r="K10" s="52"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4290852&amp;idt=th252"/>
-    <hyperlink ref="D3" r:id="rId2" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4290852&amp;idt=th252"/>
-    <hyperlink ref="D4" r:id="rId3" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4290852&amp;idt=th252"/>
-    <hyperlink ref="D5" r:id="rId4" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4290852&amp;idt=th252"/>
-    <hyperlink ref="D6" r:id="rId5" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4290852&amp;idt=th252"/>
-    <hyperlink ref="D7" r:id="rId6" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4290852&amp;idt=th252"/>
-    <hyperlink ref="D8" r:id="rId7" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4290852&amp;idt=th252"/>
-    <hyperlink ref="D9" r:id="rId8" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4290852&amp;idt=th252"/>
-    <hyperlink ref="D10" r:id="rId9" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4290852&amp;idt=th252"/>
-  </hyperlinks>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
   <headerFooter>

--- a/src/main/resources/datasets/Import_Chartres_Projet.xlsx
+++ b/src/main/resources/datasets/Import_Chartres_Projet.xlsx
@@ -3659,7 +3659,7 @@
       </c>
       <c r="C2" t="inlineStr" s="34">
         <is>
-          <t>US</t>
+          <t>Type inexistant TEST</t>
         </is>
       </c>
       <c r="D2" t="inlineStr" s="36">
@@ -3815,8 +3815,10 @@
         </is>
       </c>
       <c r="E5" s="37"/>
-      <c r="F5" t="s" s="39">
-        <v>81</v>
+      <c r="F5" t="inlineStr" s="39">
+        <is>
+          <t>Interprétation inexistante TEST</t>
+        </is>
       </c>
       <c r="G5" t="s" s="6">
         <v>72</v>
